--- a/deliverables/05-electrical/CFU-000-EL-CBL-001_Cable-Schedule.xlsx
+++ b/deliverables/05-electrical/CFU-000-EL-CBL-001_Cable-Schedule.xlsx
@@ -468,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V119"/>
+  <dimension ref="A1:V123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -824,7 +824,7 @@
       <c r="P7" s="4" t="n"/>
       <c r="Q7" s="4" t="n"/>
       <c r="R7" s="7" t="n">
-        <v>78.09999999999999</v>
+        <v>78.5</v>
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
       <c r="P8" s="4" t="n"/>
       <c r="Q8" s="4" t="n"/>
       <c r="R8" s="7" t="n">
-        <v>78.09999999999999</v>
+        <v>78.5</v>
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
       <c r="P12" s="4" t="n"/>
       <c r="Q12" s="4" t="n"/>
       <c r="R12" s="7" t="n">
-        <v>78.09999999999999</v>
+        <v>78.5</v>
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
       <c r="P13" s="4" t="n"/>
       <c r="Q13" s="4" t="n"/>
       <c r="R13" s="7" t="n">
-        <v>78.09999999999999</v>
+        <v>78.5</v>
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
         <v>5.88</v>
       </c>
       <c r="R15" s="7" t="n">
-        <v>55.2</v>
+        <v>55.5</v>
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>5.84</v>
       </c>
       <c r="R16" s="7" t="n">
-        <v>55.2</v>
+        <v>55.5</v>
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
         <v>5.81</v>
       </c>
       <c r="R17" s="7" t="n">
-        <v>55.2</v>
+        <v>55.5</v>
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
@@ -1640,13 +1640,13 @@
         <v>0.52</v>
       </c>
       <c r="P18" s="5" t="n">
-        <v>5.34</v>
+        <v>5.33</v>
       </c>
       <c r="Q18" s="5" t="n">
-        <v>5.86</v>
+        <v>5.85</v>
       </c>
       <c r="R18" s="7" t="n">
-        <v>55.2</v>
+        <v>55.5</v>
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>4.16</v>
       </c>
       <c r="G19" s="7" t="n">
-        <v>41.8</v>
+        <v>52.6</v>
       </c>
       <c r="H19" s="6" t="n">
         <v>155</v>
@@ -1718,19 +1718,19 @@
         <v>185.6</v>
       </c>
       <c r="N19" s="5" t="n">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="O19" s="5" t="n">
-        <v>0.31</v>
+        <v>0.39</v>
       </c>
       <c r="P19" s="5" t="n">
-        <v>2</v>
+        <v>2.51</v>
       </c>
       <c r="Q19" s="5" t="n">
-        <v>2.31</v>
+        <v>2.9</v>
       </c>
       <c r="R19" s="7" t="n">
-        <v>55.2</v>
+        <v>55.5</v>
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>4.16</v>
       </c>
       <c r="G20" s="7" t="n">
-        <v>41.8</v>
+        <v>52.6</v>
       </c>
       <c r="H20" s="6" t="n">
         <v>160</v>
@@ -1802,19 +1802,19 @@
         <v>185.6</v>
       </c>
       <c r="N20" s="5" t="n">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="O20" s="5" t="n">
-        <v>0.32</v>
+        <v>0.4</v>
       </c>
       <c r="P20" s="5" t="n">
-        <v>2.01</v>
+        <v>2.51</v>
       </c>
       <c r="Q20" s="5" t="n">
-        <v>2.32</v>
+        <v>2.92</v>
       </c>
       <c r="R20" s="7" t="n">
-        <v>55.2</v>
+        <v>55.5</v>
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
@@ -1898,7 +1898,7 @@
         <v>2.01</v>
       </c>
       <c r="R21" s="7" t="n">
-        <v>55.2</v>
+        <v>55.5</v>
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         <v>2.01</v>
       </c>
       <c r="R22" s="7" t="n">
-        <v>55.2</v>
+        <v>55.5</v>
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
       <c r="P23" s="4" t="n"/>
       <c r="Q23" s="4" t="n"/>
       <c r="R23" s="7" t="n">
-        <v>55.2</v>
+        <v>55.5</v>
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
       <c r="P24" s="4" t="n"/>
       <c r="Q24" s="4" t="n"/>
       <c r="R24" s="7" t="n">
-        <v>55.2</v>
+        <v>55.5</v>
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
@@ -5142,14 +5142,14 @@
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>Atm. overhead condenser - fan motor 1/4 (VFD)</t>
+          <t>Atm. overhead condenser - fan motor 1/6 (VFD)</t>
         </is>
       </c>
       <c r="F64" s="5" t="n">
         <v>0.48</v>
       </c>
-      <c r="G64" s="6" t="n">
-        <v>134.6</v>
+      <c r="G64" s="7" t="n">
+        <v>82.3</v>
       </c>
       <c r="H64" s="6" t="n">
         <v>140</v>
@@ -5161,30 +5161,30 @@
       </c>
       <c r="J64" s="4" t="inlineStr">
         <is>
-          <t>3C x 70 + 3E x 16 mm2 Cu/XLPE/CWS/SWA/PVC 0.6/1 kV, symmetrical VFD cable</t>
+          <t>3C x 35 + 3E x 11.6667 mm2 Cu/XLPE/CWS/SWA/PVC 0.6/1 kV, symmetrical VFD cable</t>
         </is>
       </c>
       <c r="K64" s="4" t="n">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="L64" s="4" t="n">
         <v>1</v>
       </c>
       <c r="M64" s="6" t="n">
-        <v>179.1</v>
+        <v>115</v>
       </c>
       <c r="N64" s="5" t="n">
-        <v>2.28</v>
+        <v>2.58</v>
       </c>
       <c r="O64" s="4" t="n"/>
       <c r="P64" s="4" t="n"/>
       <c r="Q64" s="4" t="n"/>
       <c r="R64" s="7" t="n">
-        <v>8.6</v>
+        <v>4.9</v>
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>MCCB 175 A (250 AF) + VFD (6-pulse + harmonic filter)</t>
+          <t>MCCB 100 A (125 AF) + VFD (6-pulse + harmonic filter)</t>
         </is>
       </c>
       <c r="T64" s="4" t="inlineStr"/>
@@ -5212,14 +5212,14 @@
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>Atm. overhead condenser - fan motor 2/4 (VFD)</t>
+          <t>Atm. overhead condenser - fan motor 2/6 (VFD)</t>
         </is>
       </c>
       <c r="F65" s="5" t="n">
         <v>0.48</v>
       </c>
-      <c r="G65" s="6" t="n">
-        <v>134.6</v>
+      <c r="G65" s="7" t="n">
+        <v>82.3</v>
       </c>
       <c r="H65" s="6" t="n">
         <v>140</v>
@@ -5231,30 +5231,30 @@
       </c>
       <c r="J65" s="4" t="inlineStr">
         <is>
-          <t>3C x 70 + 3E x 16 mm2 Cu/XLPE/CWS/SWA/PVC 0.6/1 kV, symmetrical VFD cable</t>
+          <t>3C x 35 + 3E x 11.6667 mm2 Cu/XLPE/CWS/SWA/PVC 0.6/1 kV, symmetrical VFD cable</t>
         </is>
       </c>
       <c r="K65" s="4" t="n">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="L65" s="4" t="n">
         <v>1</v>
       </c>
       <c r="M65" s="6" t="n">
-        <v>179.1</v>
+        <v>115</v>
       </c>
       <c r="N65" s="5" t="n">
-        <v>2.28</v>
+        <v>2.58</v>
       </c>
       <c r="O65" s="4" t="n"/>
       <c r="P65" s="4" t="n"/>
       <c r="Q65" s="4" t="n"/>
       <c r="R65" s="7" t="n">
-        <v>8.6</v>
+        <v>4.9</v>
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>MCCB 175 A (250 AF) + VFD (6-pulse + harmonic filter)</t>
+          <t>MCCB 100 A (125 AF) + VFD (6-pulse + harmonic filter)</t>
         </is>
       </c>
       <c r="T65" s="4" t="inlineStr"/>
@@ -5282,14 +5282,14 @@
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>Atm. overhead condenser - fan motor 3/4 (VFD)</t>
+          <t>Atm. overhead condenser - fan motor 3/6 (VFD)</t>
         </is>
       </c>
       <c r="F66" s="5" t="n">
         <v>0.48</v>
       </c>
-      <c r="G66" s="6" t="n">
-        <v>134.6</v>
+      <c r="G66" s="7" t="n">
+        <v>82.3</v>
       </c>
       <c r="H66" s="6" t="n">
         <v>145</v>
@@ -5301,30 +5301,30 @@
       </c>
       <c r="J66" s="4" t="inlineStr">
         <is>
-          <t>3C x 70 + 3E x 16 mm2 Cu/XLPE/CWS/SWA/PVC 0.6/1 kV, symmetrical VFD cable</t>
+          <t>3C x 35 + 3E x 11.6667 mm2 Cu/XLPE/CWS/SWA/PVC 0.6/1 kV, symmetrical VFD cable</t>
         </is>
       </c>
       <c r="K66" s="4" t="n">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="L66" s="4" t="n">
         <v>1</v>
       </c>
       <c r="M66" s="6" t="n">
-        <v>179.1</v>
+        <v>115</v>
       </c>
       <c r="N66" s="5" t="n">
-        <v>2.36</v>
+        <v>2.67</v>
       </c>
       <c r="O66" s="4" t="n"/>
       <c r="P66" s="4" t="n"/>
       <c r="Q66" s="4" t="n"/>
       <c r="R66" s="7" t="n">
-        <v>8.6</v>
+        <v>4.9</v>
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>MCCB 175 A (250 AF) + VFD (6-pulse + harmonic filter)</t>
+          <t>MCCB 100 A (125 AF) + VFD (6-pulse + harmonic filter)</t>
         </is>
       </c>
       <c r="T66" s="4" t="inlineStr"/>
@@ -5352,14 +5352,14 @@
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>Atm. overhead condenser - fan motor 4/4 (VFD)</t>
+          <t>Atm. overhead condenser - fan motor 4/6 (VFD)</t>
         </is>
       </c>
       <c r="F67" s="5" t="n">
         <v>0.48</v>
       </c>
-      <c r="G67" s="6" t="n">
-        <v>134.6</v>
+      <c r="G67" s="7" t="n">
+        <v>82.3</v>
       </c>
       <c r="H67" s="6" t="n">
         <v>145</v>
@@ -5371,30 +5371,30 @@
       </c>
       <c r="J67" s="4" t="inlineStr">
         <is>
-          <t>3C x 70 + 3E x 16 mm2 Cu/XLPE/CWS/SWA/PVC 0.6/1 kV, symmetrical VFD cable</t>
+          <t>3C x 35 + 3E x 11.6667 mm2 Cu/XLPE/CWS/SWA/PVC 0.6/1 kV, symmetrical VFD cable</t>
         </is>
       </c>
       <c r="K67" s="4" t="n">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="L67" s="4" t="n">
         <v>1</v>
       </c>
       <c r="M67" s="6" t="n">
-        <v>179.1</v>
+        <v>115</v>
       </c>
       <c r="N67" s="5" t="n">
-        <v>2.36</v>
+        <v>2.67</v>
       </c>
       <c r="O67" s="4" t="n"/>
       <c r="P67" s="4" t="n"/>
       <c r="Q67" s="4" t="n"/>
       <c r="R67" s="7" t="n">
-        <v>8.6</v>
+        <v>4.9</v>
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>MCCB 175 A (250 AF) + VFD (6-pulse + harmonic filter)</t>
+          <t>MCCB 100 A (125 AF) + VFD (6-pulse + harmonic filter)</t>
         </is>
       </c>
       <c r="T67" s="4" t="inlineStr"/>
@@ -5407,32 +5407,32 @@
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>CBL-A-103-M1</t>
+          <t>CBL-A-101-M5</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>MCC-101A</t>
+          <t>VFD-A-101-M5</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>A-103-M1</t>
+          <t>A-101-M5</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>Kero cooler - fan motor 1/2</t>
+          <t>Atm. overhead condenser - fan motor 5/6 (VFD)</t>
         </is>
       </c>
       <c r="F68" s="5" t="n">
         <v>0.48</v>
       </c>
       <c r="G68" s="7" t="n">
-        <v>17.1</v>
+        <v>82.3</v>
       </c>
       <c r="H68" s="6" t="n">
-        <v>175</v>
+        <v>150</v>
       </c>
       <c r="I68" s="4" t="inlineStr">
         <is>
@@ -5441,36 +5441,30 @@
       </c>
       <c r="J68" s="4" t="inlineStr">
         <is>
-          <t>3C x 6 + E6 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
+          <t>3C x 35 + 3E x 11.6667 mm2 Cu/XLPE/CWS/SWA/PVC 0.6/1 kV, symmetrical VFD cable</t>
         </is>
       </c>
       <c r="K68" s="4" t="n">
-        <v>6</v>
+        <v>35</v>
       </c>
       <c r="L68" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M68" s="7" t="n">
-        <v>39.3</v>
+      <c r="M68" s="6" t="n">
+        <v>115</v>
       </c>
       <c r="N68" s="5" t="n">
-        <v>3.67</v>
-      </c>
-      <c r="O68" s="5" t="n">
-        <v>10.25</v>
-      </c>
-      <c r="P68" s="5" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="Q68" s="5" t="n">
-        <v>10.51</v>
-      </c>
+        <v>2.76</v>
+      </c>
+      <c r="O68" s="4" t="n"/>
+      <c r="P68" s="4" t="n"/>
+      <c r="Q68" s="4" t="n"/>
       <c r="R68" s="7" t="n">
-        <v>1.6</v>
+        <v>4.9</v>
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>MCCB 30 A (125 AF) + DOL, NEMA size 1</t>
+          <t>MCCB 100 A (125 AF) + VFD (6-pulse + harmonic filter)</t>
         </is>
       </c>
       <c r="T68" s="4" t="inlineStr"/>
@@ -5483,32 +5477,32 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>CBL-A-103-M2</t>
+          <t>CBL-A-101-M6</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>MCC-101B</t>
+          <t>VFD-A-101-M6</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>A-103-M2</t>
+          <t>A-101-M6</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>Kero cooler - fan motor 2/2</t>
+          <t>Atm. overhead condenser - fan motor 6/6 (VFD)</t>
         </is>
       </c>
       <c r="F69" s="5" t="n">
         <v>0.48</v>
       </c>
       <c r="G69" s="7" t="n">
-        <v>17.1</v>
+        <v>82.3</v>
       </c>
       <c r="H69" s="6" t="n">
-        <v>175</v>
+        <v>150</v>
       </c>
       <c r="I69" s="4" t="inlineStr">
         <is>
@@ -5517,36 +5511,30 @@
       </c>
       <c r="J69" s="4" t="inlineStr">
         <is>
-          <t>3C x 6 + E6 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
+          <t>3C x 35 + 3E x 11.6667 mm2 Cu/XLPE/CWS/SWA/PVC 0.6/1 kV, symmetrical VFD cable</t>
         </is>
       </c>
       <c r="K69" s="4" t="n">
-        <v>6</v>
+        <v>35</v>
       </c>
       <c r="L69" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M69" s="7" t="n">
-        <v>39.3</v>
+      <c r="M69" s="6" t="n">
+        <v>115</v>
       </c>
       <c r="N69" s="5" t="n">
-        <v>3.67</v>
-      </c>
-      <c r="O69" s="5" t="n">
-        <v>10.25</v>
-      </c>
-      <c r="P69" s="5" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="Q69" s="5" t="n">
-        <v>10.51</v>
-      </c>
+        <v>2.76</v>
+      </c>
+      <c r="O69" s="4" t="n"/>
+      <c r="P69" s="4" t="n"/>
+      <c r="Q69" s="4" t="n"/>
       <c r="R69" s="7" t="n">
-        <v>1.6</v>
+        <v>4.9</v>
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>MCCB 30 A (125 AF) + DOL, NEMA size 1</t>
+          <t>MCCB 100 A (125 AF) + VFD (6-pulse + harmonic filter)</t>
         </is>
       </c>
       <c r="T69" s="4" t="inlineStr"/>
@@ -5559,7 +5547,7 @@
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>CBL-A-104-M1</t>
+          <t>CBL-A-103-M1</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
@@ -5569,22 +5557,22 @@
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>A-104-M1</t>
+          <t>A-103-M1</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>Diesel cooler - fan motor 1/2</t>
+          <t>Kero cooler - fan motor 1/2</t>
         </is>
       </c>
       <c r="F70" s="5" t="n">
         <v>0.48</v>
       </c>
       <c r="G70" s="7" t="n">
-        <v>28.8</v>
+        <v>17.1</v>
       </c>
       <c r="H70" s="6" t="n">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="I70" s="4" t="inlineStr">
         <is>
@@ -5593,36 +5581,36 @@
       </c>
       <c r="J70" s="4" t="inlineStr">
         <is>
-          <t>3C x 10 + E10 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
+          <t>3C x 6 + E6 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
         </is>
       </c>
       <c r="K70" s="4" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L70" s="4" t="n">
         <v>1</v>
       </c>
       <c r="M70" s="7" t="n">
-        <v>54.6</v>
+        <v>39.3</v>
       </c>
       <c r="N70" s="5" t="n">
-        <v>3.8</v>
+        <v>3.67</v>
       </c>
       <c r="O70" s="5" t="n">
-        <v>10.92</v>
+        <v>10.25</v>
       </c>
       <c r="P70" s="5" t="n">
-        <v>0.44</v>
+        <v>0.26</v>
       </c>
       <c r="Q70" s="5" t="n">
-        <v>11.37</v>
+        <v>10.51</v>
       </c>
       <c r="R70" s="7" t="n">
-        <v>2.7</v>
+        <v>1.6</v>
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>MCCB 60 A (125 AF) + DOL, NEMA size 2</t>
+          <t>MCCB 30 A (125 AF) + DOL, NEMA size 1</t>
         </is>
       </c>
       <c r="T70" s="4" t="inlineStr"/>
@@ -5635,7 +5623,7 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>CBL-A-104-M2</t>
+          <t>CBL-A-103-M2</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
@@ -5645,22 +5633,22 @@
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>A-104-M2</t>
+          <t>A-103-M2</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>Diesel cooler - fan motor 2/2</t>
+          <t>Kero cooler - fan motor 2/2</t>
         </is>
       </c>
       <c r="F71" s="5" t="n">
         <v>0.48</v>
       </c>
       <c r="G71" s="7" t="n">
-        <v>28.8</v>
+        <v>17.1</v>
       </c>
       <c r="H71" s="6" t="n">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="I71" s="4" t="inlineStr">
         <is>
@@ -5669,36 +5657,36 @@
       </c>
       <c r="J71" s="4" t="inlineStr">
         <is>
-          <t>3C x 10 + E10 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
+          <t>3C x 6 + E6 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
         </is>
       </c>
       <c r="K71" s="4" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L71" s="4" t="n">
         <v>1</v>
       </c>
       <c r="M71" s="7" t="n">
-        <v>54.6</v>
+        <v>39.3</v>
       </c>
       <c r="N71" s="5" t="n">
-        <v>3.8</v>
+        <v>3.67</v>
       </c>
       <c r="O71" s="5" t="n">
-        <v>10.92</v>
+        <v>10.25</v>
       </c>
       <c r="P71" s="5" t="n">
-        <v>0.44</v>
+        <v>0.26</v>
       </c>
       <c r="Q71" s="5" t="n">
-        <v>11.37</v>
+        <v>10.51</v>
       </c>
       <c r="R71" s="7" t="n">
-        <v>2.7</v>
+        <v>1.6</v>
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>MCCB 60 A (125 AF) + DOL, NEMA size 2</t>
+          <t>MCCB 30 A (125 AF) + DOL, NEMA size 1</t>
         </is>
       </c>
       <c r="T71" s="4" t="inlineStr"/>
@@ -5711,7 +5699,7 @@
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>CBL-A-105-M1</t>
+          <t>CBL-A-104-M1</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
@@ -5721,22 +5709,22 @@
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>A-105-M1</t>
+          <t>A-104-M1</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>Ago cooler - fan motor 1/2</t>
+          <t>Diesel cooler - fan motor 1/2</t>
         </is>
       </c>
       <c r="F72" s="5" t="n">
         <v>0.48</v>
       </c>
       <c r="G72" s="7" t="n">
-        <v>46.7</v>
+        <v>28.8</v>
       </c>
       <c r="H72" s="6" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="I72" s="4" t="inlineStr">
         <is>
@@ -5745,36 +5733,36 @@
       </c>
       <c r="J72" s="4" t="inlineStr">
         <is>
-          <t>3C x 16 + E16 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
+          <t>3C x 10 + E10 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
         </is>
       </c>
       <c r="K72" s="4" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="L72" s="4" t="n">
         <v>1</v>
       </c>
       <c r="M72" s="7" t="n">
-        <v>72.8</v>
+        <v>54.6</v>
       </c>
       <c r="N72" s="5" t="n">
-        <v>4.15</v>
+        <v>3.8</v>
       </c>
       <c r="O72" s="5" t="n">
-        <v>12.37</v>
+        <v>10.92</v>
       </c>
       <c r="P72" s="5" t="n">
-        <v>0.71</v>
+        <v>0.44</v>
       </c>
       <c r="Q72" s="5" t="n">
-        <v>13.08</v>
+        <v>11.37</v>
       </c>
       <c r="R72" s="7" t="n">
-        <v>4.9</v>
+        <v>2.7</v>
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>MCCB 90 A (125 AF) + DOL, NEMA size 3</t>
+          <t>MCCB 60 A (125 AF) + DOL, NEMA size 2</t>
         </is>
       </c>
       <c r="T72" s="4" t="inlineStr"/>
@@ -5787,7 +5775,7 @@
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>CBL-A-105-M2</t>
+          <t>CBL-A-104-M2</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
@@ -5797,22 +5785,22 @@
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>A-105-M2</t>
+          <t>A-104-M2</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>Ago cooler - fan motor 2/2</t>
+          <t>Diesel cooler - fan motor 2/2</t>
         </is>
       </c>
       <c r="F73" s="5" t="n">
         <v>0.48</v>
       </c>
       <c r="G73" s="7" t="n">
-        <v>46.7</v>
+        <v>28.8</v>
       </c>
       <c r="H73" s="6" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="I73" s="4" t="inlineStr">
         <is>
@@ -5821,36 +5809,36 @@
       </c>
       <c r="J73" s="4" t="inlineStr">
         <is>
-          <t>3C x 16 + E16 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
+          <t>3C x 10 + E10 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
         </is>
       </c>
       <c r="K73" s="4" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="L73" s="4" t="n">
         <v>1</v>
       </c>
       <c r="M73" s="7" t="n">
-        <v>72.8</v>
+        <v>54.6</v>
       </c>
       <c r="N73" s="5" t="n">
-        <v>4.15</v>
+        <v>3.8</v>
       </c>
       <c r="O73" s="5" t="n">
-        <v>12.37</v>
+        <v>10.92</v>
       </c>
       <c r="P73" s="5" t="n">
-        <v>0.71</v>
+        <v>0.44</v>
       </c>
       <c r="Q73" s="5" t="n">
-        <v>13.08</v>
+        <v>11.37</v>
       </c>
       <c r="R73" s="7" t="n">
-        <v>4.9</v>
+        <v>2.7</v>
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>MCCB 90 A (125 AF) + DOL, NEMA size 3</t>
+          <t>MCCB 60 A (125 AF) + DOL, NEMA size 2</t>
         </is>
       </c>
       <c r="T73" s="4" t="inlineStr"/>
@@ -5863,7 +5851,7 @@
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>CBL-A-106-M1</t>
+          <t>CBL-A-105-M1</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
@@ -5873,22 +5861,22 @@
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>A-106-M1</t>
+          <t>A-105-M1</t>
         </is>
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>Stabiliser overhead condenser - fan motor 1/2</t>
+          <t>Ago cooler - fan motor 1/2</t>
         </is>
       </c>
       <c r="F74" s="5" t="n">
         <v>0.48</v>
       </c>
       <c r="G74" s="7" t="n">
-        <v>17.1</v>
+        <v>46.7</v>
       </c>
       <c r="H74" s="6" t="n">
-        <v>120</v>
+        <v>190</v>
       </c>
       <c r="I74" s="4" t="inlineStr">
         <is>
@@ -5897,36 +5885,36 @@
       </c>
       <c r="J74" s="4" t="inlineStr">
         <is>
-          <t>3C x 4 + E4 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
+          <t>3C x 16 + E16 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
         </is>
       </c>
       <c r="K74" s="4" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="L74" s="4" t="n">
         <v>1</v>
       </c>
       <c r="M74" s="7" t="n">
-        <v>30.6</v>
+        <v>72.8</v>
       </c>
       <c r="N74" s="5" t="n">
-        <v>3.75</v>
+        <v>4.15</v>
       </c>
       <c r="O74" s="5" t="n">
-        <v>10.33</v>
+        <v>12.37</v>
       </c>
       <c r="P74" s="5" t="n">
-        <v>0.26</v>
+        <v>0.71</v>
       </c>
       <c r="Q74" s="5" t="n">
-        <v>10.59</v>
+        <v>13.08</v>
       </c>
       <c r="R74" s="7" t="n">
-        <v>1.6</v>
+        <v>4.9</v>
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>MCCB 30 A (125 AF) + DOL, NEMA size 1</t>
+          <t>MCCB 90 A (125 AF) + DOL, NEMA size 3</t>
         </is>
       </c>
       <c r="T74" s="4" t="inlineStr"/>
@@ -5939,7 +5927,7 @@
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>CBL-A-106-M2</t>
+          <t>CBL-A-105-M2</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
@@ -5949,22 +5937,22 @@
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>A-106-M2</t>
+          <t>A-105-M2</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>Stabiliser overhead condenser - fan motor 2/2</t>
+          <t>Ago cooler - fan motor 2/2</t>
         </is>
       </c>
       <c r="F75" s="5" t="n">
         <v>0.48</v>
       </c>
       <c r="G75" s="7" t="n">
-        <v>17.1</v>
+        <v>46.7</v>
       </c>
       <c r="H75" s="6" t="n">
-        <v>120</v>
+        <v>190</v>
       </c>
       <c r="I75" s="4" t="inlineStr">
         <is>
@@ -5973,36 +5961,36 @@
       </c>
       <c r="J75" s="4" t="inlineStr">
         <is>
-          <t>3C x 4 + E4 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
+          <t>3C x 16 + E16 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
         </is>
       </c>
       <c r="K75" s="4" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="L75" s="4" t="n">
         <v>1</v>
       </c>
       <c r="M75" s="7" t="n">
-        <v>30.6</v>
+        <v>72.8</v>
       </c>
       <c r="N75" s="5" t="n">
-        <v>3.75</v>
+        <v>4.15</v>
       </c>
       <c r="O75" s="5" t="n">
-        <v>10.33</v>
+        <v>12.37</v>
       </c>
       <c r="P75" s="5" t="n">
-        <v>0.26</v>
+        <v>0.71</v>
       </c>
       <c r="Q75" s="5" t="n">
-        <v>10.59</v>
+        <v>13.08</v>
       </c>
       <c r="R75" s="7" t="n">
-        <v>1.6</v>
+        <v>4.9</v>
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>MCCB 30 A (125 AF) + DOL, NEMA size 1</t>
+          <t>MCCB 90 A (125 AF) + DOL, NEMA size 3</t>
         </is>
       </c>
       <c r="T75" s="4" t="inlineStr"/>
@@ -6015,7 +6003,7 @@
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>CBL-A-107-M1</t>
+          <t>CBL-A-106-M1</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
@@ -6025,22 +6013,22 @@
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>A-107-M1</t>
+          <t>A-106-M1</t>
         </is>
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>Splitter overhead condenser - fan motor 1/2</t>
+          <t>Stabiliser overhead condenser - fan motor 1/2</t>
         </is>
       </c>
       <c r="F76" s="5" t="n">
         <v>0.48</v>
       </c>
       <c r="G76" s="7" t="n">
-        <v>67.3</v>
+        <v>17.1</v>
       </c>
       <c r="H76" s="6" t="n">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="I76" s="4" t="inlineStr">
         <is>
@@ -6049,36 +6037,36 @@
       </c>
       <c r="J76" s="4" t="inlineStr">
         <is>
-          <t>3C x 25 + E16 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
+          <t>3C x 4 + E4 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
         </is>
       </c>
       <c r="K76" s="4" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="L76" s="4" t="n">
         <v>1</v>
       </c>
       <c r="M76" s="7" t="n">
-        <v>92.5</v>
+        <v>30.6</v>
       </c>
       <c r="N76" s="5" t="n">
-        <v>2.36</v>
+        <v>3.75</v>
       </c>
       <c r="O76" s="5" t="n">
-        <v>7.36</v>
+        <v>10.33</v>
       </c>
       <c r="P76" s="5" t="n">
-        <v>1.03</v>
+        <v>0.26</v>
       </c>
       <c r="Q76" s="5" t="n">
-        <v>8.390000000000001</v>
+        <v>10.59</v>
       </c>
       <c r="R76" s="7" t="n">
-        <v>4.9</v>
+        <v>1.6</v>
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>MCCB 125 A (125 AF) + DOL, NEMA size 4</t>
+          <t>MCCB 30 A (125 AF) + DOL, NEMA size 1</t>
         </is>
       </c>
       <c r="T76" s="4" t="inlineStr"/>
@@ -6091,7 +6079,7 @@
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>CBL-A-107-M2</t>
+          <t>CBL-A-106-M2</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
@@ -6101,22 +6089,22 @@
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>A-107-M2</t>
+          <t>A-106-M2</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>Splitter overhead condenser - fan motor 2/2</t>
+          <t>Stabiliser overhead condenser - fan motor 2/2</t>
         </is>
       </c>
       <c r="F77" s="5" t="n">
         <v>0.48</v>
       </c>
       <c r="G77" s="7" t="n">
-        <v>67.3</v>
+        <v>17.1</v>
       </c>
       <c r="H77" s="6" t="n">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="I77" s="4" t="inlineStr">
         <is>
@@ -6125,36 +6113,36 @@
       </c>
       <c r="J77" s="4" t="inlineStr">
         <is>
-          <t>3C x 25 + E16 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
+          <t>3C x 4 + E4 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
         </is>
       </c>
       <c r="K77" s="4" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="L77" s="4" t="n">
         <v>1</v>
       </c>
       <c r="M77" s="7" t="n">
-        <v>92.5</v>
+        <v>30.6</v>
       </c>
       <c r="N77" s="5" t="n">
-        <v>2.36</v>
+        <v>3.75</v>
       </c>
       <c r="O77" s="5" t="n">
-        <v>7.36</v>
+        <v>10.33</v>
       </c>
       <c r="P77" s="5" t="n">
-        <v>1.03</v>
+        <v>0.26</v>
       </c>
       <c r="Q77" s="5" t="n">
-        <v>8.390000000000001</v>
+        <v>10.59</v>
       </c>
       <c r="R77" s="7" t="n">
-        <v>4.9</v>
+        <v>1.6</v>
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>MCCB 125 A (125 AF) + DOL, NEMA size 4</t>
+          <t>MCCB 30 A (125 AF) + DOL, NEMA size 1</t>
         </is>
       </c>
       <c r="T77" s="4" t="inlineStr"/>
@@ -6167,7 +6155,7 @@
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>CBL-A-108-M1</t>
+          <t>CBL-A-107-M1</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
@@ -6177,12 +6165,12 @@
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>A-108-M1</t>
+          <t>A-107-M1</t>
         </is>
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>Heavy naphtha product cooler - fan motor 1/2</t>
+          <t>Splitter overhead condenser - fan motor 1/4</t>
         </is>
       </c>
       <c r="F78" s="5" t="n">
@@ -6192,7 +6180,7 @@
         <v>46.7</v>
       </c>
       <c r="H78" s="6" t="n">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="I78" s="4" t="inlineStr">
         <is>
@@ -6214,16 +6202,16 @@
         <v>72.8</v>
       </c>
       <c r="N78" s="5" t="n">
-        <v>2.84</v>
+        <v>2.51</v>
       </c>
       <c r="O78" s="5" t="n">
-        <v>8.460000000000001</v>
+        <v>7.48</v>
       </c>
       <c r="P78" s="5" t="n">
         <v>0.71</v>
       </c>
       <c r="Q78" s="5" t="n">
-        <v>9.18</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="R78" s="7" t="n">
         <v>4.9</v>
@@ -6243,7 +6231,7 @@
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>CBL-A-108-M2</t>
+          <t>CBL-A-107-M2</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
@@ -6253,12 +6241,12 @@
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>A-108-M2</t>
+          <t>A-107-M2</t>
         </is>
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>Heavy naphtha product cooler - fan motor 2/2</t>
+          <t>Splitter overhead condenser - fan motor 2/4</t>
         </is>
       </c>
       <c r="F79" s="5" t="n">
@@ -6268,7 +6256,7 @@
         <v>46.7</v>
       </c>
       <c r="H79" s="6" t="n">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="I79" s="4" t="inlineStr">
         <is>
@@ -6290,16 +6278,16 @@
         <v>72.8</v>
       </c>
       <c r="N79" s="5" t="n">
-        <v>2.84</v>
+        <v>2.51</v>
       </c>
       <c r="O79" s="5" t="n">
-        <v>8.460000000000001</v>
+        <v>7.48</v>
       </c>
       <c r="P79" s="5" t="n">
         <v>0.71</v>
       </c>
       <c r="Q79" s="5" t="n">
-        <v>9.18</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="R79" s="7" t="n">
         <v>4.9</v>
@@ -6319,7 +6307,7 @@
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>CBL-A-201-M1</t>
+          <t>CBL-A-107-M3</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
@@ -6329,22 +6317,22 @@
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>A-201-M1</t>
+          <t>A-107-M3</t>
         </is>
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>Lvgo cooler - fan motor 1/2</t>
+          <t>Splitter overhead condenser - fan motor 3/4</t>
         </is>
       </c>
       <c r="F80" s="5" t="n">
         <v>0.48</v>
       </c>
       <c r="G80" s="7" t="n">
-        <v>23.3</v>
+        <v>46.7</v>
       </c>
       <c r="H80" s="6" t="n">
-        <v>225</v>
+        <v>120</v>
       </c>
       <c r="I80" s="4" t="inlineStr">
         <is>
@@ -6353,36 +6341,36 @@
       </c>
       <c r="J80" s="4" t="inlineStr">
         <is>
-          <t>3C x 10 + E10 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
+          <t>3C x 16 + E16 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
         </is>
       </c>
       <c r="K80" s="4" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="L80" s="4" t="n">
         <v>1</v>
       </c>
       <c r="M80" s="7" t="n">
-        <v>54.6</v>
+        <v>72.8</v>
       </c>
       <c r="N80" s="5" t="n">
-        <v>3.86</v>
+        <v>2.62</v>
       </c>
       <c r="O80" s="5" t="n">
-        <v>11.07</v>
+        <v>7.81</v>
       </c>
       <c r="P80" s="5" t="n">
-        <v>0.36</v>
+        <v>0.71</v>
       </c>
       <c r="Q80" s="5" t="n">
-        <v>11.43</v>
+        <v>8.52</v>
       </c>
       <c r="R80" s="7" t="n">
-        <v>2.7</v>
+        <v>4.9</v>
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>MCCB 45 A (125 AF) + DOL, NEMA size 2</t>
+          <t>MCCB 90 A (125 AF) + DOL, NEMA size 3</t>
         </is>
       </c>
       <c r="T80" s="4" t="inlineStr"/>
@@ -6395,7 +6383,7 @@
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>CBL-A-201-M2</t>
+          <t>CBL-A-107-M4</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
@@ -6405,22 +6393,22 @@
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>A-201-M2</t>
+          <t>A-107-M4</t>
         </is>
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>Lvgo cooler - fan motor 2/2</t>
+          <t>Splitter overhead condenser - fan motor 4/4</t>
         </is>
       </c>
       <c r="F81" s="5" t="n">
         <v>0.48</v>
       </c>
       <c r="G81" s="7" t="n">
-        <v>23.3</v>
+        <v>46.7</v>
       </c>
       <c r="H81" s="6" t="n">
-        <v>225</v>
+        <v>120</v>
       </c>
       <c r="I81" s="4" t="inlineStr">
         <is>
@@ -6429,36 +6417,36 @@
       </c>
       <c r="J81" s="4" t="inlineStr">
         <is>
-          <t>3C x 10 + E10 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
+          <t>3C x 16 + E16 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
         </is>
       </c>
       <c r="K81" s="4" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="L81" s="4" t="n">
         <v>1</v>
       </c>
       <c r="M81" s="7" t="n">
-        <v>54.6</v>
+        <v>72.8</v>
       </c>
       <c r="N81" s="5" t="n">
-        <v>3.86</v>
+        <v>2.62</v>
       </c>
       <c r="O81" s="5" t="n">
-        <v>11.07</v>
+        <v>7.81</v>
       </c>
       <c r="P81" s="5" t="n">
-        <v>0.36</v>
+        <v>0.71</v>
       </c>
       <c r="Q81" s="5" t="n">
-        <v>11.43</v>
+        <v>8.52</v>
       </c>
       <c r="R81" s="7" t="n">
-        <v>2.7</v>
+        <v>4.9</v>
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>MCCB 45 A (125 AF) + DOL, NEMA size 2</t>
+          <t>MCCB 90 A (125 AF) + DOL, NEMA size 3</t>
         </is>
       </c>
       <c r="T81" s="4" t="inlineStr"/>
@@ -6471,7 +6459,7 @@
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>CBL-A-202-M1</t>
+          <t>CBL-A-108-M1</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
@@ -6481,22 +6469,22 @@
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>A-202-M1</t>
+          <t>A-108-M1</t>
         </is>
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>Hvgo Product cooler - fan motor 1/2</t>
+          <t>Heavy naphtha product cooler - fan motor 1/2</t>
         </is>
       </c>
       <c r="F82" s="5" t="n">
         <v>0.48</v>
       </c>
       <c r="G82" s="7" t="n">
-        <v>55.3</v>
+        <v>46.7</v>
       </c>
       <c r="H82" s="6" t="n">
-        <v>230</v>
+        <v>130</v>
       </c>
       <c r="I82" s="4" t="inlineStr">
         <is>
@@ -6505,36 +6493,36 @@
       </c>
       <c r="J82" s="4" t="inlineStr">
         <is>
-          <t>3C x 25 + E16 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
+          <t>3C x 16 + E16 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
         </is>
       </c>
       <c r="K82" s="4" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="L82" s="4" t="n">
         <v>1</v>
       </c>
       <c r="M82" s="7" t="n">
-        <v>92.5</v>
+        <v>72.8</v>
       </c>
       <c r="N82" s="5" t="n">
-        <v>3.88</v>
+        <v>2.84</v>
       </c>
       <c r="O82" s="5" t="n">
-        <v>12.1</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="P82" s="5" t="n">
-        <v>0.85</v>
+        <v>0.71</v>
       </c>
       <c r="Q82" s="5" t="n">
-        <v>12.95</v>
+        <v>9.18</v>
       </c>
       <c r="R82" s="7" t="n">
         <v>4.9</v>
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>MCCB 100 A (125 AF) + DOL, NEMA size 3</t>
+          <t>MCCB 90 A (125 AF) + DOL, NEMA size 3</t>
         </is>
       </c>
       <c r="T82" s="4" t="inlineStr"/>
@@ -6547,7 +6535,7 @@
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>CBL-A-202-M2</t>
+          <t>CBL-A-108-M2</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
@@ -6557,22 +6545,22 @@
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>A-202-M2</t>
+          <t>A-108-M2</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>Hvgo Product cooler - fan motor 2/2</t>
+          <t>Heavy naphtha product cooler - fan motor 2/2</t>
         </is>
       </c>
       <c r="F83" s="5" t="n">
         <v>0.48</v>
       </c>
       <c r="G83" s="7" t="n">
-        <v>55.3</v>
+        <v>46.7</v>
       </c>
       <c r="H83" s="6" t="n">
-        <v>230</v>
+        <v>130</v>
       </c>
       <c r="I83" s="4" t="inlineStr">
         <is>
@@ -6581,36 +6569,36 @@
       </c>
       <c r="J83" s="4" t="inlineStr">
         <is>
-          <t>3C x 25 + E16 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
+          <t>3C x 16 + E16 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
         </is>
       </c>
       <c r="K83" s="4" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="L83" s="4" t="n">
         <v>1</v>
       </c>
       <c r="M83" s="7" t="n">
-        <v>92.5</v>
+        <v>72.8</v>
       </c>
       <c r="N83" s="5" t="n">
-        <v>3.88</v>
+        <v>2.84</v>
       </c>
       <c r="O83" s="5" t="n">
-        <v>12.1</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="P83" s="5" t="n">
-        <v>0.85</v>
+        <v>0.71</v>
       </c>
       <c r="Q83" s="5" t="n">
-        <v>12.95</v>
+        <v>9.18</v>
       </c>
       <c r="R83" s="7" t="n">
         <v>4.9</v>
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>MCCB 100 A (125 AF) + DOL, NEMA size 3</t>
+          <t>MCCB 90 A (125 AF) + DOL, NEMA size 3</t>
         </is>
       </c>
       <c r="T83" s="4" t="inlineStr"/>
@@ -6623,7 +6611,7 @@
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>CBL-X-101-PA</t>
+          <t>CBL-A-201-M1</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
@@ -6633,22 +6621,22 @@
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>X-101-PA</t>
+          <t>A-201-M1</t>
         </is>
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>Demulsifier injection package - metering pump A</t>
+          <t>Lvgo cooler - fan motor 1/2</t>
         </is>
       </c>
       <c r="F84" s="5" t="n">
         <v>0.48</v>
       </c>
       <c r="G84" s="7" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H84" s="7" t="n">
-        <v>95</v>
+        <v>23.3</v>
+      </c>
+      <c r="H84" s="6" t="n">
+        <v>225</v>
       </c>
       <c r="I84" s="4" t="inlineStr">
         <is>
@@ -6657,36 +6645,36 @@
       </c>
       <c r="J84" s="4" t="inlineStr">
         <is>
-          <t>3C x 4 + E4 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
+          <t>3C x 10 + E10 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
         </is>
       </c>
       <c r="K84" s="4" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="L84" s="4" t="n">
         <v>1</v>
       </c>
       <c r="M84" s="7" t="n">
-        <v>30.6</v>
+        <v>54.6</v>
       </c>
       <c r="N84" s="5" t="n">
-        <v>0.23</v>
+        <v>3.86</v>
       </c>
       <c r="O84" s="5" t="n">
-        <v>0.71</v>
+        <v>11.07</v>
       </c>
       <c r="P84" s="5" t="n">
-        <v>0.02</v>
+        <v>0.36</v>
       </c>
       <c r="Q84" s="5" t="n">
-        <v>0.73</v>
+        <v>11.43</v>
       </c>
       <c r="R84" s="7" t="n">
-        <v>1.6</v>
+        <v>2.7</v>
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>MCCB 15 A (125 AF) + DOL, NEMA size 0</t>
+          <t>MCCB 45 A (125 AF) + DOL, NEMA size 2</t>
         </is>
       </c>
       <c r="T84" s="4" t="inlineStr"/>
@@ -6699,7 +6687,7 @@
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>CBL-X-101-PB</t>
+          <t>CBL-A-201-M2</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
@@ -6709,22 +6697,22 @@
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>X-101-PB</t>
+          <t>A-201-M2</t>
         </is>
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>Demulsifier injection package - metering pump B</t>
+          <t>Lvgo cooler - fan motor 2/2</t>
         </is>
       </c>
       <c r="F85" s="5" t="n">
         <v>0.48</v>
       </c>
       <c r="G85" s="7" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H85" s="7" t="n">
-        <v>95</v>
+        <v>23.3</v>
+      </c>
+      <c r="H85" s="6" t="n">
+        <v>225</v>
       </c>
       <c r="I85" s="4" t="inlineStr">
         <is>
@@ -6733,36 +6721,36 @@
       </c>
       <c r="J85" s="4" t="inlineStr">
         <is>
-          <t>3C x 4 + E4 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
+          <t>3C x 10 + E10 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
         </is>
       </c>
       <c r="K85" s="4" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="L85" s="4" t="n">
         <v>1</v>
       </c>
       <c r="M85" s="7" t="n">
-        <v>30.6</v>
+        <v>54.6</v>
       </c>
       <c r="N85" s="5" t="n">
-        <v>0.23</v>
+        <v>3.86</v>
       </c>
       <c r="O85" s="5" t="n">
-        <v>0.71</v>
+        <v>11.07</v>
       </c>
       <c r="P85" s="5" t="n">
-        <v>0.02</v>
+        <v>0.36</v>
       </c>
       <c r="Q85" s="5" t="n">
-        <v>0.73</v>
+        <v>11.43</v>
       </c>
       <c r="R85" s="7" t="n">
-        <v>1.6</v>
+        <v>2.7</v>
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>MCCB 15 A (125 AF) + DOL, NEMA size 0</t>
+          <t>MCCB 45 A (125 AF) + DOL, NEMA size 2</t>
         </is>
       </c>
       <c r="T85" s="4" t="inlineStr"/>
@@ -6775,7 +6763,7 @@
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>CBL-X-102-PA</t>
+          <t>CBL-A-202-M1</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
@@ -6785,22 +6773,22 @@
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>X-102-PA</t>
+          <t>A-202-M1</t>
         </is>
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>Caustic injection package (desalted crude) - metering pump A</t>
+          <t>Hvgo Product cooler - fan motor 1/2</t>
         </is>
       </c>
       <c r="F86" s="5" t="n">
         <v>0.48</v>
       </c>
       <c r="G86" s="7" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H86" s="7" t="n">
-        <v>95</v>
+        <v>55.3</v>
+      </c>
+      <c r="H86" s="6" t="n">
+        <v>230</v>
       </c>
       <c r="I86" s="4" t="inlineStr">
         <is>
@@ -6809,36 +6797,36 @@
       </c>
       <c r="J86" s="4" t="inlineStr">
         <is>
-          <t>3C x 4 + E4 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
+          <t>3C x 25 + E16 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
         </is>
       </c>
       <c r="K86" s="4" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="L86" s="4" t="n">
         <v>1</v>
       </c>
       <c r="M86" s="7" t="n">
-        <v>30.6</v>
+        <v>92.5</v>
       </c>
       <c r="N86" s="5" t="n">
-        <v>0.23</v>
+        <v>3.88</v>
       </c>
       <c r="O86" s="5" t="n">
-        <v>0.71</v>
+        <v>12.1</v>
       </c>
       <c r="P86" s="5" t="n">
-        <v>0.02</v>
+        <v>0.85</v>
       </c>
       <c r="Q86" s="5" t="n">
-        <v>0.73</v>
+        <v>12.95</v>
       </c>
       <c r="R86" s="7" t="n">
-        <v>1.6</v>
+        <v>4.9</v>
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>MCCB 15 A (125 AF) + DOL, NEMA size 0</t>
+          <t>MCCB 100 A (125 AF) + DOL, NEMA size 3</t>
         </is>
       </c>
       <c r="T86" s="4" t="inlineStr"/>
@@ -6851,7 +6839,7 @@
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>CBL-X-102-PB</t>
+          <t>CBL-A-202-M2</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
@@ -6861,22 +6849,22 @@
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>X-102-PB</t>
+          <t>A-202-M2</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>Caustic injection package (desalted crude) - metering pump B</t>
+          <t>Hvgo Product cooler - fan motor 2/2</t>
         </is>
       </c>
       <c r="F87" s="5" t="n">
         <v>0.48</v>
       </c>
       <c r="G87" s="7" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H87" s="7" t="n">
-        <v>95</v>
+        <v>55.3</v>
+      </c>
+      <c r="H87" s="6" t="n">
+        <v>230</v>
       </c>
       <c r="I87" s="4" t="inlineStr">
         <is>
@@ -6885,36 +6873,36 @@
       </c>
       <c r="J87" s="4" t="inlineStr">
         <is>
-          <t>3C x 4 + E4 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
+          <t>3C x 25 + E16 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
         </is>
       </c>
       <c r="K87" s="4" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="L87" s="4" t="n">
         <v>1</v>
       </c>
       <c r="M87" s="7" t="n">
-        <v>30.6</v>
+        <v>92.5</v>
       </c>
       <c r="N87" s="5" t="n">
-        <v>0.23</v>
+        <v>3.88</v>
       </c>
       <c r="O87" s="5" t="n">
-        <v>0.71</v>
+        <v>12.1</v>
       </c>
       <c r="P87" s="5" t="n">
-        <v>0.02</v>
+        <v>0.85</v>
       </c>
       <c r="Q87" s="5" t="n">
-        <v>0.73</v>
+        <v>12.95</v>
       </c>
       <c r="R87" s="7" t="n">
-        <v>1.6</v>
+        <v>4.9</v>
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>MCCB 15 A (125 AF) + DOL, NEMA size 0</t>
+          <t>MCCB 100 A (125 AF) + DOL, NEMA size 3</t>
         </is>
       </c>
       <c r="T87" s="4" t="inlineStr"/>
@@ -6927,7 +6915,7 @@
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>CBL-X-103-PA</t>
+          <t>CBL-X-101-PA</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
@@ -6937,12 +6925,12 @@
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>X-103-PA</t>
+          <t>X-101-PA</t>
         </is>
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>Neutraliser / filming amine package (atm OH) - metering pump A</t>
+          <t>Demulsifier injection package - metering pump A</t>
         </is>
       </c>
       <c r="F88" s="5" t="n">
@@ -6951,8 +6939,8 @@
       <c r="G88" s="7" t="n">
         <v>1.5</v>
       </c>
-      <c r="H88" s="6" t="n">
-        <v>160</v>
+      <c r="H88" s="7" t="n">
+        <v>95</v>
       </c>
       <c r="I88" s="4" t="inlineStr">
         <is>
@@ -6974,16 +6962,16 @@
         <v>30.6</v>
       </c>
       <c r="N88" s="5" t="n">
-        <v>0.39</v>
+        <v>0.23</v>
       </c>
       <c r="O88" s="5" t="n">
-        <v>1.19</v>
+        <v>0.71</v>
       </c>
       <c r="P88" s="5" t="n">
         <v>0.02</v>
       </c>
       <c r="Q88" s="5" t="n">
-        <v>1.22</v>
+        <v>0.73</v>
       </c>
       <c r="R88" s="7" t="n">
         <v>1.6</v>
@@ -7003,7 +6991,7 @@
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>CBL-X-103-PB</t>
+          <t>CBL-X-101-PB</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
@@ -7013,12 +7001,12 @@
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>X-103-PB</t>
+          <t>X-101-PB</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>Neutraliser / filming amine package (atm OH) - metering pump B</t>
+          <t>Demulsifier injection package - metering pump B</t>
         </is>
       </c>
       <c r="F89" s="5" t="n">
@@ -7027,8 +7015,8 @@
       <c r="G89" s="7" t="n">
         <v>1.5</v>
       </c>
-      <c r="H89" s="6" t="n">
-        <v>160</v>
+      <c r="H89" s="7" t="n">
+        <v>95</v>
       </c>
       <c r="I89" s="4" t="inlineStr">
         <is>
@@ -7050,16 +7038,16 @@
         <v>30.6</v>
       </c>
       <c r="N89" s="5" t="n">
-        <v>0.39</v>
+        <v>0.23</v>
       </c>
       <c r="O89" s="5" t="n">
-        <v>1.19</v>
+        <v>0.71</v>
       </c>
       <c r="P89" s="5" t="n">
         <v>0.02</v>
       </c>
       <c r="Q89" s="5" t="n">
-        <v>1.22</v>
+        <v>0.73</v>
       </c>
       <c r="R89" s="7" t="n">
         <v>1.6</v>
@@ -7079,7 +7067,7 @@
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>CBL-X-104-PA</t>
+          <t>CBL-X-102-PA</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
@@ -7089,12 +7077,12 @@
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>X-104-PA</t>
+          <t>X-102-PA</t>
         </is>
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>Corrosion inhibitor package (VDU OH) - metering pump A</t>
+          <t>Caustic injection package (desalted crude) - metering pump A</t>
         </is>
       </c>
       <c r="F90" s="5" t="n">
@@ -7103,8 +7091,8 @@
       <c r="G90" s="7" t="n">
         <v>1.5</v>
       </c>
-      <c r="H90" s="6" t="n">
-        <v>295</v>
+      <c r="H90" s="7" t="n">
+        <v>95</v>
       </c>
       <c r="I90" s="4" t="inlineStr">
         <is>
@@ -7126,16 +7114,16 @@
         <v>30.6</v>
       </c>
       <c r="N90" s="5" t="n">
-        <v>0.72</v>
+        <v>0.23</v>
       </c>
       <c r="O90" s="5" t="n">
-        <v>2.2</v>
+        <v>0.71</v>
       </c>
       <c r="P90" s="5" t="n">
         <v>0.02</v>
       </c>
       <c r="Q90" s="5" t="n">
-        <v>2.22</v>
+        <v>0.73</v>
       </c>
       <c r="R90" s="7" t="n">
         <v>1.6</v>
@@ -7155,7 +7143,7 @@
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>CBL-X-104-PB</t>
+          <t>CBL-X-102-PB</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
@@ -7165,12 +7153,12 @@
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>X-104-PB</t>
+          <t>X-102-PB</t>
         </is>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>Corrosion inhibitor package (VDU OH) - metering pump B</t>
+          <t>Caustic injection package (desalted crude) - metering pump B</t>
         </is>
       </c>
       <c r="F91" s="5" t="n">
@@ -7179,8 +7167,8 @@
       <c r="G91" s="7" t="n">
         <v>1.5</v>
       </c>
-      <c r="H91" s="6" t="n">
-        <v>295</v>
+      <c r="H91" s="7" t="n">
+        <v>95</v>
       </c>
       <c r="I91" s="4" t="inlineStr">
         <is>
@@ -7202,16 +7190,16 @@
         <v>30.6</v>
       </c>
       <c r="N91" s="5" t="n">
-        <v>0.72</v>
+        <v>0.23</v>
       </c>
       <c r="O91" s="5" t="n">
-        <v>2.2</v>
+        <v>0.71</v>
       </c>
       <c r="P91" s="5" t="n">
         <v>0.02</v>
       </c>
       <c r="Q91" s="5" t="n">
-        <v>2.22</v>
+        <v>0.73</v>
       </c>
       <c r="R91" s="7" t="n">
         <v>1.6</v>
@@ -7231,7 +7219,7 @@
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>CBL-DT-101A1</t>
+          <t>CBL-X-103-PA</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
@@ -7241,22 +7229,22 @@
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>DT-101A1</t>
+          <t>X-103-PA</t>
         </is>
       </c>
       <c r="E92" s="4" t="inlineStr">
         <is>
-          <t>D-101A 1st stage - HV transformer 1/2 (150 kVA, 480 V / 13-23 kV)</t>
+          <t>Neutraliser / filming amine package (atm OH) - metering pump A</t>
         </is>
       </c>
       <c r="F92" s="5" t="n">
         <v>0.48</v>
       </c>
-      <c r="G92" s="6" t="n">
-        <v>180.4</v>
-      </c>
-      <c r="H92" s="7" t="n">
-        <v>70</v>
+      <c r="G92" s="7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H92" s="6" t="n">
+        <v>160</v>
       </c>
       <c r="I92" s="4" t="inlineStr">
         <is>
@@ -7265,30 +7253,36 @@
       </c>
       <c r="J92" s="4" t="inlineStr">
         <is>
-          <t>3C x 120 + E70 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
+          <t>3C x 4 + E4 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
         </is>
       </c>
       <c r="K92" s="4" t="n">
-        <v>120</v>
+        <v>4</v>
       </c>
       <c r="L92" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M92" s="6" t="n">
-        <v>251.9</v>
+      <c r="M92" s="7" t="n">
+        <v>30.6</v>
       </c>
       <c r="N92" s="5" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="O92" s="4" t="n"/>
-      <c r="P92" s="4" t="n"/>
-      <c r="Q92" s="4" t="n"/>
+        <v>0.39</v>
+      </c>
+      <c r="O92" s="5" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="P92" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="Q92" s="5" t="n">
+        <v>1.22</v>
+      </c>
       <c r="R92" s="7" t="n">
-        <v>8.6</v>
+        <v>1.6</v>
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>MCCB 250 A (250 AF) - desalter transformer feeder</t>
+          <t>MCCB 15 A (125 AF) + DOL, NEMA size 0</t>
         </is>
       </c>
       <c r="T92" s="4" t="inlineStr"/>
@@ -7301,7 +7295,7 @@
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>CBL-DT-101A2</t>
+          <t>CBL-X-103-PB</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
@@ -7311,22 +7305,22 @@
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>DT-101A2</t>
+          <t>X-103-PB</t>
         </is>
       </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t>D-101A 1st stage - HV transformer 2/2 (150 kVA, 480 V / 13-23 kV)</t>
+          <t>Neutraliser / filming amine package (atm OH) - metering pump B</t>
         </is>
       </c>
       <c r="F93" s="5" t="n">
         <v>0.48</v>
       </c>
-      <c r="G93" s="6" t="n">
-        <v>180.4</v>
-      </c>
-      <c r="H93" s="7" t="n">
-        <v>70</v>
+      <c r="G93" s="7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H93" s="6" t="n">
+        <v>160</v>
       </c>
       <c r="I93" s="4" t="inlineStr">
         <is>
@@ -7335,30 +7329,36 @@
       </c>
       <c r="J93" s="4" t="inlineStr">
         <is>
-          <t>3C x 120 + E70 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
+          <t>3C x 4 + E4 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
         </is>
       </c>
       <c r="K93" s="4" t="n">
-        <v>120</v>
+        <v>4</v>
       </c>
       <c r="L93" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M93" s="6" t="n">
-        <v>251.9</v>
+      <c r="M93" s="7" t="n">
+        <v>30.6</v>
       </c>
       <c r="N93" s="5" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="O93" s="4" t="n"/>
-      <c r="P93" s="4" t="n"/>
-      <c r="Q93" s="4" t="n"/>
+        <v>0.39</v>
+      </c>
+      <c r="O93" s="5" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="P93" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="Q93" s="5" t="n">
+        <v>1.22</v>
+      </c>
       <c r="R93" s="7" t="n">
-        <v>8.6</v>
+        <v>1.6</v>
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>MCCB 250 A (250 AF) - desalter transformer feeder</t>
+          <t>MCCB 15 A (125 AF) + DOL, NEMA size 0</t>
         </is>
       </c>
       <c r="T93" s="4" t="inlineStr"/>
@@ -7371,7 +7371,7 @@
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>CBL-DT-101B1</t>
+          <t>CBL-X-104-PA</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
@@ -7381,22 +7381,22 @@
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>DT-101B1</t>
+          <t>X-104-PA</t>
         </is>
       </c>
       <c r="E94" s="4" t="inlineStr">
         <is>
-          <t>D-101B 2nd stage - HV transformer 1/2 (150 kVA, 480 V / 13-23 kV)</t>
+          <t>Corrosion inhibitor package (VDU OH) - metering pump A</t>
         </is>
       </c>
       <c r="F94" s="5" t="n">
         <v>0.48</v>
       </c>
-      <c r="G94" s="6" t="n">
-        <v>180.4</v>
-      </c>
-      <c r="H94" s="7" t="n">
-        <v>60</v>
+      <c r="G94" s="7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H94" s="6" t="n">
+        <v>295</v>
       </c>
       <c r="I94" s="4" t="inlineStr">
         <is>
@@ -7405,30 +7405,36 @@
       </c>
       <c r="J94" s="4" t="inlineStr">
         <is>
-          <t>3C x 120 + E70 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
+          <t>3C x 4 + E4 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
         </is>
       </c>
       <c r="K94" s="4" t="n">
-        <v>120</v>
+        <v>4</v>
       </c>
       <c r="L94" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M94" s="6" t="n">
-        <v>251.9</v>
+      <c r="M94" s="7" t="n">
+        <v>30.6</v>
       </c>
       <c r="N94" s="5" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="O94" s="4" t="n"/>
-      <c r="P94" s="4" t="n"/>
-      <c r="Q94" s="4" t="n"/>
+        <v>0.72</v>
+      </c>
+      <c r="O94" s="5" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="P94" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="Q94" s="5" t="n">
+        <v>2.22</v>
+      </c>
       <c r="R94" s="7" t="n">
-        <v>8.6</v>
+        <v>1.6</v>
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>MCCB 250 A (250 AF) - desalter transformer feeder</t>
+          <t>MCCB 15 A (125 AF) + DOL, NEMA size 0</t>
         </is>
       </c>
       <c r="T94" s="4" t="inlineStr"/>
@@ -7441,7 +7447,7 @@
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>CBL-DT-101B2</t>
+          <t>CBL-X-104-PB</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
@@ -7451,22 +7457,22 @@
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>DT-101B2</t>
+          <t>X-104-PB</t>
         </is>
       </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
-          <t>D-101B 2nd stage - HV transformer 2/2 (150 kVA, 480 V / 13-23 kV)</t>
+          <t>Corrosion inhibitor package (VDU OH) - metering pump B</t>
         </is>
       </c>
       <c r="F95" s="5" t="n">
         <v>0.48</v>
       </c>
-      <c r="G95" s="6" t="n">
-        <v>180.4</v>
-      </c>
-      <c r="H95" s="7" t="n">
-        <v>60</v>
+      <c r="G95" s="7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H95" s="6" t="n">
+        <v>295</v>
       </c>
       <c r="I95" s="4" t="inlineStr">
         <is>
@@ -7475,30 +7481,36 @@
       </c>
       <c r="J95" s="4" t="inlineStr">
         <is>
-          <t>3C x 120 + E70 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
+          <t>3C x 4 + E4 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
         </is>
       </c>
       <c r="K95" s="4" t="n">
-        <v>120</v>
+        <v>4</v>
       </c>
       <c r="L95" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M95" s="6" t="n">
-        <v>251.9</v>
+      <c r="M95" s="7" t="n">
+        <v>30.6</v>
       </c>
       <c r="N95" s="5" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="O95" s="4" t="n"/>
-      <c r="P95" s="4" t="n"/>
-      <c r="Q95" s="4" t="n"/>
+        <v>0.72</v>
+      </c>
+      <c r="O95" s="5" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="P95" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="Q95" s="5" t="n">
+        <v>2.22</v>
+      </c>
       <c r="R95" s="7" t="n">
-        <v>8.6</v>
+        <v>1.6</v>
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>MCCB 250 A (250 AF) - desalter transformer feeder</t>
+          <t>MCCB 15 A (125 AF) + DOL, NEMA size 0</t>
         </is>
       </c>
       <c r="T95" s="4" t="inlineStr"/>
@@ -7511,7 +7523,7 @@
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>CBL-MOV-A</t>
+          <t>CBL-DT-101A1</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
@@ -7521,54 +7533,54 @@
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>MOV-A</t>
+          <t>DT-101A1</t>
         </is>
       </c>
       <c r="E96" s="4" t="inlineStr">
         <is>
-          <t>MOV / electric valve actuators - allowance (18 x 1.5 kW), bus A</t>
+          <t>D-101A 1st stage - HV transformer 1/2 (150 kVA, 480 V / 13-23 kV)</t>
         </is>
       </c>
       <c r="F96" s="5" t="n">
         <v>0.48</v>
       </c>
-      <c r="G96" s="7" t="n">
-        <v>43.3</v>
-      </c>
-      <c r="H96" s="6" t="n">
-        <v>170</v>
+      <c r="G96" s="6" t="n">
+        <v>180.4</v>
+      </c>
+      <c r="H96" s="7" t="n">
+        <v>70</v>
       </c>
       <c r="I96" s="4" t="inlineStr">
         <is>
-          <t>area:PLOT</t>
+          <t>layout</t>
         </is>
       </c>
       <c r="J96" s="4" t="inlineStr">
         <is>
-          <t>3C x 10 + E10 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
+          <t>3C x 120 + E70 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
         </is>
       </c>
       <c r="K96" s="4" t="n">
-        <v>10</v>
+        <v>120</v>
       </c>
       <c r="L96" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M96" s="7" t="n">
-        <v>54.6</v>
+      <c r="M96" s="6" t="n">
+        <v>251.9</v>
       </c>
       <c r="N96" s="5" t="n">
-        <v>4.82</v>
+        <v>0.95</v>
       </c>
       <c r="O96" s="4" t="n"/>
       <c r="P96" s="4" t="n"/>
       <c r="Q96" s="4" t="n"/>
       <c r="R96" s="7" t="n">
-        <v>2.7</v>
+        <v>8.6</v>
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>MCCB 60 A (125 AF)</t>
+          <t>MCCB 250 A (250 AF) - desalter transformer feeder</t>
         </is>
       </c>
       <c r="T96" s="4" t="inlineStr"/>
@@ -7581,7 +7593,7 @@
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>CBL-MOV-B</t>
+          <t>CBL-DT-101A2</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
@@ -7591,54 +7603,54 @@
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>MOV-B</t>
+          <t>DT-101A2</t>
         </is>
       </c>
       <c r="E97" s="4" t="inlineStr">
         <is>
-          <t>MOV / electric valve actuators - allowance (18 x 1.5 kW), bus B</t>
+          <t>D-101A 1st stage - HV transformer 2/2 (150 kVA, 480 V / 13-23 kV)</t>
         </is>
       </c>
       <c r="F97" s="5" t="n">
         <v>0.48</v>
       </c>
-      <c r="G97" s="7" t="n">
-        <v>43.3</v>
-      </c>
-      <c r="H97" s="6" t="n">
-        <v>170</v>
+      <c r="G97" s="6" t="n">
+        <v>180.4</v>
+      </c>
+      <c r="H97" s="7" t="n">
+        <v>70</v>
       </c>
       <c r="I97" s="4" t="inlineStr">
         <is>
-          <t>area:PLOT</t>
+          <t>layout</t>
         </is>
       </c>
       <c r="J97" s="4" t="inlineStr">
         <is>
-          <t>3C x 10 + E10 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
+          <t>3C x 120 + E70 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
         </is>
       </c>
       <c r="K97" s="4" t="n">
-        <v>10</v>
+        <v>120</v>
       </c>
       <c r="L97" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M97" s="7" t="n">
-        <v>54.6</v>
+      <c r="M97" s="6" t="n">
+        <v>251.9</v>
       </c>
       <c r="N97" s="5" t="n">
-        <v>4.82</v>
+        <v>0.95</v>
       </c>
       <c r="O97" s="4" t="n"/>
       <c r="P97" s="4" t="n"/>
       <c r="Q97" s="4" t="n"/>
       <c r="R97" s="7" t="n">
-        <v>2.7</v>
+        <v>8.6</v>
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>MCCB 60 A (125 AF)</t>
+          <t>MCCB 250 A (250 AF) - desalter transformer feeder</t>
         </is>
       </c>
       <c r="T97" s="4" t="inlineStr"/>
@@ -7651,7 +7663,7 @@
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>CBL-HTP-101</t>
+          <t>CBL-DT-101B1</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
@@ -7661,54 +7673,54 @@
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>HTP-101</t>
+          <t>DT-101B1</t>
         </is>
       </c>
       <c r="E98" s="4" t="inlineStr">
         <is>
-          <t>Electric heat tracing panel - CDU slop &amp; HN lines (allowance)</t>
+          <t>D-101B 2nd stage - HV transformer 1/2 (150 kVA, 480 V / 13-23 kV)</t>
         </is>
       </c>
       <c r="F98" s="5" t="n">
         <v>0.48</v>
       </c>
-      <c r="G98" s="7" t="n">
-        <v>36.1</v>
-      </c>
-      <c r="H98" s="6" t="n">
-        <v>170</v>
+      <c r="G98" s="6" t="n">
+        <v>180.4</v>
+      </c>
+      <c r="H98" s="7" t="n">
+        <v>60</v>
       </c>
       <c r="I98" s="4" t="inlineStr">
         <is>
-          <t>area:CDU_P</t>
+          <t>layout</t>
         </is>
       </c>
       <c r="J98" s="4" t="inlineStr">
         <is>
-          <t>3C x 16 + E16 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
+          <t>3C x 120 + E70 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
         </is>
       </c>
       <c r="K98" s="4" t="n">
-        <v>16</v>
+        <v>120</v>
       </c>
       <c r="L98" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M98" s="7" t="n">
-        <v>72.8</v>
+      <c r="M98" s="6" t="n">
+        <v>251.9</v>
       </c>
       <c r="N98" s="5" t="n">
-        <v>3.26</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="O98" s="4" t="n"/>
       <c r="P98" s="4" t="n"/>
       <c r="Q98" s="4" t="n"/>
       <c r="R98" s="7" t="n">
-        <v>2.7</v>
+        <v>8.6</v>
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>MCCB 50 A (125 AF)</t>
+          <t>MCCB 250 A (250 AF) - desalter transformer feeder</t>
         </is>
       </c>
       <c r="T98" s="4" t="inlineStr"/>
@@ -7721,7 +7733,7 @@
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>CBL-HTP-102</t>
+          <t>CBL-DT-101B2</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
@@ -7731,54 +7743,54 @@
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>HTP-102</t>
+          <t>DT-101B2</t>
         </is>
       </c>
       <c r="E99" s="4" t="inlineStr">
         <is>
-          <t>Electric heat tracing panel - VDU slop wax / slop oil lines (allowance)</t>
+          <t>D-101B 2nd stage - HV transformer 2/2 (150 kVA, 480 V / 13-23 kV)</t>
         </is>
       </c>
       <c r="F99" s="5" t="n">
         <v>0.48</v>
       </c>
-      <c r="G99" s="7" t="n">
-        <v>48.1</v>
-      </c>
-      <c r="H99" s="6" t="n">
-        <v>250</v>
+      <c r="G99" s="6" t="n">
+        <v>180.4</v>
+      </c>
+      <c r="H99" s="7" t="n">
+        <v>60</v>
       </c>
       <c r="I99" s="4" t="inlineStr">
         <is>
-          <t>area:VDU_P</t>
+          <t>layout</t>
         </is>
       </c>
       <c r="J99" s="4" t="inlineStr">
         <is>
-          <t>3C x 25 + E16 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
+          <t>3C x 120 + E70 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
         </is>
       </c>
       <c r="K99" s="4" t="n">
-        <v>25</v>
+        <v>120</v>
       </c>
       <c r="L99" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M99" s="7" t="n">
-        <v>92.5</v>
+      <c r="M99" s="6" t="n">
+        <v>251.9</v>
       </c>
       <c r="N99" s="5" t="n">
-        <v>4.04</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="O99" s="4" t="n"/>
       <c r="P99" s="4" t="n"/>
       <c r="Q99" s="4" t="n"/>
       <c r="R99" s="7" t="n">
-        <v>4.9</v>
+        <v>8.6</v>
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>MCCB 70 A (125 AF)</t>
+          <t>MCCB 250 A (250 AF) - desalter transformer feeder</t>
         </is>
       </c>
       <c r="T99" s="4" t="inlineStr"/>
@@ -7791,64 +7803,64 @@
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>CBL-AH-101</t>
+          <t>CBL-MOV-A</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>MCC-101B</t>
+          <t>MCC-101A</t>
         </is>
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>AH-101</t>
+          <t>MOV-A</t>
         </is>
       </c>
       <c r="E100" s="4" t="inlineStr">
         <is>
-          <t>Analyser house AH-101 HVAC &amp; utilities (analysers on UPS)</t>
+          <t>MOV / electric valve actuators - allowance (18 x 1.5 kW), bus A</t>
         </is>
       </c>
       <c r="F100" s="5" t="n">
         <v>0.48</v>
       </c>
       <c r="G100" s="7" t="n">
-        <v>21.2</v>
+        <v>43.3</v>
       </c>
       <c r="H100" s="6" t="n">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="I100" s="4" t="inlineStr">
         <is>
-          <t>area:CDU</t>
+          <t>area:PLOT</t>
         </is>
       </c>
       <c r="J100" s="4" t="inlineStr">
         <is>
-          <t>3C x 6 + E6 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
+          <t>3C x 10 + E10 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
         </is>
       </c>
       <c r="K100" s="4" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="L100" s="4" t="n">
         <v>1</v>
       </c>
       <c r="M100" s="7" t="n">
-        <v>39.3</v>
+        <v>54.6</v>
       </c>
       <c r="N100" s="5" t="n">
-        <v>4.94</v>
+        <v>4.82</v>
       </c>
       <c r="O100" s="4" t="n"/>
       <c r="P100" s="4" t="n"/>
       <c r="Q100" s="4" t="n"/>
       <c r="R100" s="7" t="n">
-        <v>1.6</v>
+        <v>2.7</v>
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>MCCB 30 A (125 AF)</t>
+          <t>MCCB 60 A (125 AF)</t>
         </is>
       </c>
       <c r="T100" s="4" t="inlineStr"/>
@@ -7861,64 +7873,64 @@
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>CBL-BEF-101A</t>
+          <t>CBL-MOV-B</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>MCC-101A</t>
+          <t>MCC-101B</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>BEF-101A</t>
+          <t>MOV-B</t>
         </is>
       </c>
       <c r="E101" s="4" t="inlineStr">
         <is>
-          <t>SS-100 battery-room exhaust fan A</t>
+          <t>MOV / electric valve actuators - allowance (18 x 1.5 kW), bus B</t>
         </is>
       </c>
       <c r="F101" s="5" t="n">
         <v>0.48</v>
       </c>
       <c r="G101" s="7" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="H101" s="7" t="n">
-        <v>20</v>
+        <v>43.3</v>
+      </c>
+      <c r="H101" s="6" t="n">
+        <v>170</v>
       </c>
       <c r="I101" s="4" t="inlineStr">
         <is>
-          <t>inside SS-100</t>
+          <t>area:PLOT</t>
         </is>
       </c>
       <c r="J101" s="4" t="inlineStr">
         <is>
-          <t>3C x 4 + E4 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
+          <t>3C x 10 + E10 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
         </is>
       </c>
       <c r="K101" s="4" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="L101" s="4" t="n">
         <v>1</v>
       </c>
       <c r="M101" s="7" t="n">
-        <v>30.6</v>
+        <v>54.6</v>
       </c>
       <c r="N101" s="5" t="n">
-        <v>0.06</v>
+        <v>4.82</v>
       </c>
       <c r="O101" s="4" t="n"/>
       <c r="P101" s="4" t="n"/>
       <c r="Q101" s="4" t="n"/>
       <c r="R101" s="7" t="n">
-        <v>1.6</v>
+        <v>2.7</v>
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>MCCB 15 A (125 AF)</t>
+          <t>MCCB 60 A (125 AF)</t>
         </is>
       </c>
       <c r="T101" s="4" t="inlineStr"/>
@@ -7931,64 +7943,64 @@
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>CBL-BEF-101B</t>
+          <t>CBL-HTP-101</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>MCC-101B</t>
+          <t>MCC-101A</t>
         </is>
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>BEF-101B</t>
+          <t>HTP-101</t>
         </is>
       </c>
       <c r="E102" s="4" t="inlineStr">
         <is>
-          <t>SS-100 battery-room exhaust fan B</t>
+          <t>Electric heat tracing panel - CDU slop &amp; HN lines (allowance)</t>
         </is>
       </c>
       <c r="F102" s="5" t="n">
         <v>0.48</v>
       </c>
       <c r="G102" s="7" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="H102" s="7" t="n">
-        <v>20</v>
+        <v>36.1</v>
+      </c>
+      <c r="H102" s="6" t="n">
+        <v>170</v>
       </c>
       <c r="I102" s="4" t="inlineStr">
         <is>
-          <t>inside SS-100</t>
+          <t>area:CDU_P</t>
         </is>
       </c>
       <c r="J102" s="4" t="inlineStr">
         <is>
-          <t>3C x 4 + E4 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
+          <t>3C x 16 + E16 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
         </is>
       </c>
       <c r="K102" s="4" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="L102" s="4" t="n">
         <v>1</v>
       </c>
       <c r="M102" s="7" t="n">
-        <v>30.6</v>
+        <v>72.8</v>
       </c>
       <c r="N102" s="5" t="n">
-        <v>0.06</v>
+        <v>3.26</v>
       </c>
       <c r="O102" s="4" t="n"/>
       <c r="P102" s="4" t="n"/>
       <c r="Q102" s="4" t="n"/>
       <c r="R102" s="7" t="n">
-        <v>1.6</v>
+        <v>2.7</v>
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>MCCB 15 A (125 AF)</t>
+          <t>MCCB 50 A (125 AF)</t>
         </is>
       </c>
       <c r="T102" s="4" t="inlineStr"/>
@@ -8001,54 +8013,54 @@
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>CBL-HVAC-101A</t>
+          <t>CBL-HTP-102</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>MCC-101A</t>
+          <t>MCC-101B</t>
         </is>
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>HVAC-101A</t>
+          <t>HTP-102</t>
         </is>
       </c>
       <c r="E103" s="4" t="inlineStr">
         <is>
-          <t>SS-100 HVAC package A (2 x 100 %)</t>
+          <t>Electric heat tracing panel - VDU slop wax / slop oil lines (allowance)</t>
         </is>
       </c>
       <c r="F103" s="5" t="n">
         <v>0.48</v>
       </c>
       <c r="G103" s="7" t="n">
-        <v>84.90000000000001</v>
-      </c>
-      <c r="H103" s="7" t="n">
-        <v>20</v>
+        <v>48.1</v>
+      </c>
+      <c r="H103" s="6" t="n">
+        <v>250</v>
       </c>
       <c r="I103" s="4" t="inlineStr">
         <is>
-          <t>inside SS-100</t>
+          <t>area:VDU_P</t>
         </is>
       </c>
       <c r="J103" s="4" t="inlineStr">
         <is>
-          <t>3C x 35 + E16 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
+          <t>3C x 25 + E16 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
         </is>
       </c>
       <c r="K103" s="4" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="L103" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M103" s="6" t="n">
-        <v>115</v>
+      <c r="M103" s="7" t="n">
+        <v>92.5</v>
       </c>
       <c r="N103" s="5" t="n">
-        <v>0.38</v>
+        <v>4.04</v>
       </c>
       <c r="O103" s="4" t="n"/>
       <c r="P103" s="4" t="n"/>
@@ -8058,7 +8070,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>MCCB 110 A (125 AF)</t>
+          <t>MCCB 70 A (125 AF)</t>
         </is>
       </c>
       <c r="T103" s="4" t="inlineStr"/>
@@ -8071,7 +8083,7 @@
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>CBL-HVAC-101B</t>
+          <t>CBL-AH-101</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr">
@@ -8081,54 +8093,54 @@
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>HVAC-101B</t>
+          <t>AH-101</t>
         </is>
       </c>
       <c r="E104" s="4" t="inlineStr">
         <is>
-          <t>SS-100 HVAC package B (2 x 100 %)</t>
+          <t>Analyser house AH-101 HVAC &amp; utilities (analysers on UPS)</t>
         </is>
       </c>
       <c r="F104" s="5" t="n">
         <v>0.48</v>
       </c>
       <c r="G104" s="7" t="n">
-        <v>84.90000000000001</v>
-      </c>
-      <c r="H104" s="7" t="n">
-        <v>20</v>
+        <v>21.2</v>
+      </c>
+      <c r="H104" s="6" t="n">
+        <v>190</v>
       </c>
       <c r="I104" s="4" t="inlineStr">
         <is>
-          <t>inside SS-100</t>
+          <t>area:CDU</t>
         </is>
       </c>
       <c r="J104" s="4" t="inlineStr">
         <is>
-          <t>3C x 35 + E16 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
+          <t>3C x 6 + E6 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
         </is>
       </c>
       <c r="K104" s="4" t="n">
-        <v>35</v>
+        <v>6</v>
       </c>
       <c r="L104" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M104" s="6" t="n">
-        <v>115</v>
+      <c r="M104" s="7" t="n">
+        <v>39.3</v>
       </c>
       <c r="N104" s="5" t="n">
-        <v>0.38</v>
+        <v>4.94</v>
       </c>
       <c r="O104" s="4" t="n"/>
       <c r="P104" s="4" t="n"/>
       <c r="Q104" s="4" t="n"/>
       <c r="R104" s="7" t="n">
-        <v>4.9</v>
+        <v>1.6</v>
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>MCCB 110 A (125 AF)</t>
+          <t>MCCB 30 A (125 AF)</t>
         </is>
       </c>
       <c r="T104" s="4" t="inlineStr"/>
@@ -8141,7 +8153,7 @@
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>CBL-HVAC-102A</t>
+          <t>CBL-BEF-101A</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
@@ -8151,54 +8163,54 @@
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>HVAC-102A</t>
+          <t>BEF-101A</t>
         </is>
       </c>
       <c r="E105" s="4" t="inlineStr">
         <is>
-          <t>FAR-100 HVAC package A (2 x 100 %)</t>
+          <t>SS-100 battery-room exhaust fan A</t>
         </is>
       </c>
       <c r="F105" s="5" t="n">
         <v>0.48</v>
       </c>
       <c r="G105" s="7" t="n">
-        <v>35.4</v>
+        <v>1.7</v>
       </c>
       <c r="H105" s="7" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="I105" s="4" t="inlineStr">
         <is>
-          <t>FAR-100</t>
+          <t>inside SS-100</t>
         </is>
       </c>
       <c r="J105" s="4" t="inlineStr">
         <is>
-          <t>3C x 10 + E10 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
+          <t>3C x 4 + E4 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
         </is>
       </c>
       <c r="K105" s="4" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="L105" s="4" t="n">
         <v>1</v>
       </c>
       <c r="M105" s="7" t="n">
-        <v>54.6</v>
+        <v>30.6</v>
       </c>
       <c r="N105" s="5" t="n">
-        <v>1.3</v>
+        <v>0.06</v>
       </c>
       <c r="O105" s="4" t="n"/>
       <c r="P105" s="4" t="n"/>
       <c r="Q105" s="4" t="n"/>
       <c r="R105" s="7" t="n">
-        <v>2.7</v>
+        <v>1.6</v>
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>MCCB 45 A (125 AF)</t>
+          <t>MCCB 15 A (125 AF)</t>
         </is>
       </c>
       <c r="T105" s="4" t="inlineStr"/>
@@ -8211,7 +8223,7 @@
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>CBL-HVAC-102B</t>
+          <t>CBL-BEF-101B</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr">
@@ -8221,54 +8233,54 @@
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>HVAC-102B</t>
+          <t>BEF-101B</t>
         </is>
       </c>
       <c r="E106" s="4" t="inlineStr">
         <is>
-          <t>FAR-100 HVAC package B (2 x 100 %)</t>
+          <t>SS-100 battery-room exhaust fan B</t>
         </is>
       </c>
       <c r="F106" s="5" t="n">
         <v>0.48</v>
       </c>
       <c r="G106" s="7" t="n">
-        <v>35.4</v>
+        <v>1.7</v>
       </c>
       <c r="H106" s="7" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="I106" s="4" t="inlineStr">
         <is>
-          <t>FAR-100</t>
+          <t>inside SS-100</t>
         </is>
       </c>
       <c r="J106" s="4" t="inlineStr">
         <is>
-          <t>3C x 10 + E10 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
+          <t>3C x 4 + E4 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
         </is>
       </c>
       <c r="K106" s="4" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="L106" s="4" t="n">
         <v>1</v>
       </c>
       <c r="M106" s="7" t="n">
-        <v>54.6</v>
+        <v>30.6</v>
       </c>
       <c r="N106" s="5" t="n">
-        <v>1.3</v>
+        <v>0.06</v>
       </c>
       <c r="O106" s="4" t="n"/>
       <c r="P106" s="4" t="n"/>
       <c r="Q106" s="4" t="n"/>
       <c r="R106" s="7" t="n">
-        <v>2.7</v>
+        <v>1.6</v>
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>MCCB 45 A (125 AF)</t>
+          <t>MCCB 15 A (125 AF)</t>
         </is>
       </c>
       <c r="T106" s="4" t="inlineStr"/>
@@ -8281,7 +8293,7 @@
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>CBL-WR-A</t>
+          <t>CBL-HVAC-101A</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
@@ -8291,54 +8303,54 @@
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>WR-A</t>
+          <t>HVAC-101A</t>
         </is>
       </c>
       <c r="E107" s="4" t="inlineStr">
         <is>
-          <t>Welding receptacles 3 x 63 A, 480 V, bus A</t>
+          <t>SS-100 HVAC package A (2 x 100 %)</t>
         </is>
       </c>
       <c r="F107" s="5" t="n">
         <v>0.48</v>
       </c>
-      <c r="G107" s="6" t="n">
-        <v>128.9</v>
-      </c>
-      <c r="H107" s="6" t="n">
-        <v>170</v>
+      <c r="G107" s="7" t="n">
+        <v>84.90000000000001</v>
+      </c>
+      <c r="H107" s="7" t="n">
+        <v>20</v>
       </c>
       <c r="I107" s="4" t="inlineStr">
         <is>
-          <t>area:PLOT</t>
+          <t>inside SS-100</t>
         </is>
       </c>
       <c r="J107" s="4" t="inlineStr">
         <is>
-          <t>3C x 70 + E35 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
+          <t>3C x 35 + E16 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
         </is>
       </c>
       <c r="K107" s="4" t="n">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="L107" s="4" t="n">
         <v>1</v>
       </c>
       <c r="M107" s="6" t="n">
-        <v>179.1</v>
+        <v>115</v>
       </c>
       <c r="N107" s="5" t="n">
-        <v>2.34</v>
+        <v>0.38</v>
       </c>
       <c r="O107" s="4" t="n"/>
       <c r="P107" s="4" t="n"/>
       <c r="Q107" s="4" t="n"/>
       <c r="R107" s="7" t="n">
-        <v>8.6</v>
+        <v>4.9</v>
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>MCCB 175 A (250 AF)</t>
+          <t>MCCB 110 A (125 AF)</t>
         </is>
       </c>
       <c r="T107" s="4" t="inlineStr"/>
@@ -8351,7 +8363,7 @@
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>CBL-WR-B</t>
+          <t>CBL-HVAC-101B</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr">
@@ -8361,54 +8373,54 @@
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>WR-B</t>
+          <t>HVAC-101B</t>
         </is>
       </c>
       <c r="E108" s="4" t="inlineStr">
         <is>
-          <t>Welding receptacles 3 x 63 A, 480 V, bus B</t>
+          <t>SS-100 HVAC package B (2 x 100 %)</t>
         </is>
       </c>
       <c r="F108" s="5" t="n">
         <v>0.48</v>
       </c>
-      <c r="G108" s="6" t="n">
-        <v>128.9</v>
-      </c>
-      <c r="H108" s="6" t="n">
-        <v>170</v>
+      <c r="G108" s="7" t="n">
+        <v>84.90000000000001</v>
+      </c>
+      <c r="H108" s="7" t="n">
+        <v>20</v>
       </c>
       <c r="I108" s="4" t="inlineStr">
         <is>
-          <t>area:PLOT</t>
+          <t>inside SS-100</t>
         </is>
       </c>
       <c r="J108" s="4" t="inlineStr">
         <is>
-          <t>3C x 70 + E35 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
+          <t>3C x 35 + E16 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
         </is>
       </c>
       <c r="K108" s="4" t="n">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="L108" s="4" t="n">
         <v>1</v>
       </c>
       <c r="M108" s="6" t="n">
-        <v>179.1</v>
+        <v>115</v>
       </c>
       <c r="N108" s="5" t="n">
-        <v>2.34</v>
+        <v>0.38</v>
       </c>
       <c r="O108" s="4" t="n"/>
       <c r="P108" s="4" t="n"/>
       <c r="Q108" s="4" t="n"/>
       <c r="R108" s="7" t="n">
-        <v>8.6</v>
+        <v>4.9</v>
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>MCCB 175 A (250 AF)</t>
+          <t>MCCB 110 A (125 AF)</t>
         </is>
       </c>
       <c r="T108" s="4" t="inlineStr"/>
@@ -8421,7 +8433,7 @@
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>CBL-CP-101</t>
+          <t>CBL-HVAC-102A</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
@@ -8431,54 +8443,54 @@
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>CP-101</t>
+          <t>HVAC-102A</t>
         </is>
       </c>
       <c r="E109" s="4" t="inlineStr">
         <is>
-          <t>Cathodic protection transformer-rectifier (buried piping / tank bottoms in plot)</t>
+          <t>FAR-100 HVAC package A (2 x 100 %)</t>
         </is>
       </c>
       <c r="F109" s="5" t="n">
         <v>0.48</v>
       </c>
       <c r="G109" s="7" t="n">
-        <v>12</v>
+        <v>35.4</v>
       </c>
       <c r="H109" s="7" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="I109" s="4" t="inlineStr">
         <is>
-          <t>area:DESALT</t>
+          <t>FAR-100</t>
         </is>
       </c>
       <c r="J109" s="4" t="inlineStr">
         <is>
-          <t>3C x 4 + E4 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
+          <t>3C x 10 + E10 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
         </is>
       </c>
       <c r="K109" s="4" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="L109" s="4" t="n">
         <v>1</v>
       </c>
       <c r="M109" s="7" t="n">
-        <v>30.6</v>
+        <v>54.6</v>
       </c>
       <c r="N109" s="5" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="O109" s="4" t="n"/>
       <c r="P109" s="4" t="n"/>
       <c r="Q109" s="4" t="n"/>
       <c r="R109" s="7" t="n">
-        <v>1.6</v>
+        <v>2.7</v>
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>MCCB 20 A (125 AF)</t>
+          <t>MCCB 45 A (125 AF)</t>
         </is>
       </c>
       <c r="T109" s="4" t="inlineStr"/>
@@ -8491,64 +8503,64 @@
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>CBL-BC-101A</t>
+          <t>CBL-HVAC-102B</t>
         </is>
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>MCC-101A</t>
+          <t>MCC-101B</t>
         </is>
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>BC-101A</t>
+          <t>HVAC-102B</t>
         </is>
       </c>
       <c r="E110" s="4" t="inlineStr">
         <is>
-          <t>125 V DC battery charger A (switchgear control), 2 x 100 %</t>
+          <t>FAR-100 HVAC package B (2 x 100 %)</t>
         </is>
       </c>
       <c r="F110" s="5" t="n">
         <v>0.48</v>
       </c>
       <c r="G110" s="7" t="n">
-        <v>9.4</v>
+        <v>35.4</v>
       </c>
       <c r="H110" s="7" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="I110" s="4" t="inlineStr">
         <is>
-          <t>inside SS-100</t>
+          <t>FAR-100</t>
         </is>
       </c>
       <c r="J110" s="4" t="inlineStr">
         <is>
-          <t>3C x 4 + E4 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
+          <t>3C x 10 + E10 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
         </is>
       </c>
       <c r="K110" s="4" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="L110" s="4" t="n">
         <v>1</v>
       </c>
       <c r="M110" s="7" t="n">
-        <v>30.6</v>
+        <v>54.6</v>
       </c>
       <c r="N110" s="5" t="n">
-        <v>0.34</v>
+        <v>1.3</v>
       </c>
       <c r="O110" s="4" t="n"/>
       <c r="P110" s="4" t="n"/>
       <c r="Q110" s="4" t="n"/>
       <c r="R110" s="7" t="n">
-        <v>1.6</v>
+        <v>2.7</v>
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>MCCB 15 A (125 AF)</t>
+          <t>MCCB 45 A (125 AF)</t>
         </is>
       </c>
       <c r="T110" s="4" t="inlineStr"/>
@@ -8561,64 +8573,64 @@
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>CBL-BC-101B</t>
+          <t>CBL-WR-A</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>MCC-101B</t>
+          <t>MCC-101A</t>
         </is>
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>BC-101B</t>
+          <t>WR-A</t>
         </is>
       </c>
       <c r="E111" s="4" t="inlineStr">
         <is>
-          <t>125 V DC battery charger B (switchgear control), 2 x 100 %</t>
+          <t>Welding receptacles 3 x 63 A, 480 V, bus A</t>
         </is>
       </c>
       <c r="F111" s="5" t="n">
         <v>0.48</v>
       </c>
-      <c r="G111" s="7" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="H111" s="7" t="n">
-        <v>20</v>
+      <c r="G111" s="6" t="n">
+        <v>128.9</v>
+      </c>
+      <c r="H111" s="6" t="n">
+        <v>170</v>
       </c>
       <c r="I111" s="4" t="inlineStr">
         <is>
-          <t>inside SS-100</t>
+          <t>area:PLOT</t>
         </is>
       </c>
       <c r="J111" s="4" t="inlineStr">
         <is>
-          <t>3C x 4 + E4 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
+          <t>3C x 70 + E35 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
         </is>
       </c>
       <c r="K111" s="4" t="n">
-        <v>4</v>
+        <v>70</v>
       </c>
       <c r="L111" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M111" s="7" t="n">
-        <v>30.6</v>
+      <c r="M111" s="6" t="n">
+        <v>179.1</v>
       </c>
       <c r="N111" s="5" t="n">
-        <v>0.34</v>
+        <v>2.34</v>
       </c>
       <c r="O111" s="4" t="n"/>
       <c r="P111" s="4" t="n"/>
       <c r="Q111" s="4" t="n"/>
       <c r="R111" s="7" t="n">
-        <v>1.6</v>
+        <v>8.6</v>
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>MCCB 15 A (125 AF)</t>
+          <t>MCCB 175 A (250 AF)</t>
         </is>
       </c>
       <c r="T111" s="4" t="inlineStr"/>
@@ -8631,64 +8643,64 @@
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>CBL-UPS-101A</t>
+          <t>CBL-WR-B</t>
         </is>
       </c>
       <c r="C112" s="4" t="inlineStr">
         <is>
-          <t>MCC-101A</t>
+          <t>MCC-101B</t>
         </is>
       </c>
       <c r="D112" s="4" t="inlineStr">
         <is>
-          <t>UPS-101A</t>
+          <t>WR-B</t>
         </is>
       </c>
       <c r="E112" s="4" t="inlineStr">
         <is>
-          <t>UPS-101A rectifier input (2 x 100 % 100 kVA, 50 % share + battery recharge)</t>
+          <t>Welding receptacles 3 x 63 A, 480 V, bus B</t>
         </is>
       </c>
       <c r="F112" s="5" t="n">
         <v>0.48</v>
       </c>
-      <c r="G112" s="7" t="n">
-        <v>43.1</v>
-      </c>
-      <c r="H112" s="7" t="n">
-        <v>20</v>
+      <c r="G112" s="6" t="n">
+        <v>128.9</v>
+      </c>
+      <c r="H112" s="6" t="n">
+        <v>170</v>
       </c>
       <c r="I112" s="4" t="inlineStr">
         <is>
-          <t>inside SS-100</t>
+          <t>area:PLOT</t>
         </is>
       </c>
       <c r="J112" s="4" t="inlineStr">
         <is>
-          <t>3C x 10 + E10 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
+          <t>3C x 70 + E35 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
         </is>
       </c>
       <c r="K112" s="4" t="n">
-        <v>10</v>
+        <v>70</v>
       </c>
       <c r="L112" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M112" s="7" t="n">
-        <v>54.6</v>
+      <c r="M112" s="6" t="n">
+        <v>179.1</v>
       </c>
       <c r="N112" s="5" t="n">
-        <v>0.7</v>
+        <v>2.34</v>
       </c>
       <c r="O112" s="4" t="n"/>
       <c r="P112" s="4" t="n"/>
       <c r="Q112" s="4" t="n"/>
       <c r="R112" s="7" t="n">
-        <v>2.7</v>
+        <v>8.6</v>
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>MCCB 60 A (125 AF)</t>
+          <t>MCCB 175 A (250 AF)</t>
         </is>
       </c>
       <c r="T112" s="4" t="inlineStr"/>
@@ -8701,64 +8713,64 @@
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>CBL-UPS-101B</t>
+          <t>CBL-CP-101</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>MCC-101B</t>
+          <t>MCC-101A</t>
         </is>
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>UPS-101B</t>
+          <t>CP-101</t>
         </is>
       </c>
       <c r="E113" s="4" t="inlineStr">
         <is>
-          <t>UPS-101B rectifier input (2 x 100 % 100 kVA, 50 % share + battery recharge)</t>
+          <t>Cathodic protection transformer-rectifier (buried piping / tank bottoms in plot)</t>
         </is>
       </c>
       <c r="F113" s="5" t="n">
         <v>0.48</v>
       </c>
       <c r="G113" s="7" t="n">
-        <v>43.1</v>
+        <v>12</v>
       </c>
       <c r="H113" s="7" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="I113" s="4" t="inlineStr">
         <is>
-          <t>inside SS-100</t>
+          <t>area:DESALT</t>
         </is>
       </c>
       <c r="J113" s="4" t="inlineStr">
         <is>
-          <t>3C x 10 + E10 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
+          <t>3C x 4 + E4 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
         </is>
       </c>
       <c r="K113" s="4" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="L113" s="4" t="n">
         <v>1</v>
       </c>
       <c r="M113" s="7" t="n">
-        <v>54.6</v>
+        <v>30.6</v>
       </c>
       <c r="N113" s="5" t="n">
-        <v>0.7</v>
+        <v>1.24</v>
       </c>
       <c r="O113" s="4" t="n"/>
       <c r="P113" s="4" t="n"/>
       <c r="Q113" s="4" t="n"/>
       <c r="R113" s="7" t="n">
-        <v>2.7</v>
+        <v>1.6</v>
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>MCCB 60 A (125 AF)</t>
+          <t>MCCB 20 A (125 AF)</t>
         </is>
       </c>
       <c r="T113" s="4" t="inlineStr"/>
@@ -8771,7 +8783,7 @@
       </c>
       <c r="B114" s="4" t="inlineStr">
         <is>
-          <t>CBL-HST-101</t>
+          <t>CBL-BC-101A</t>
         </is>
       </c>
       <c r="C114" s="4" t="inlineStr">
@@ -8781,26 +8793,26 @@
       </c>
       <c r="D114" s="4" t="inlineStr">
         <is>
-          <t>HST-101</t>
+          <t>BC-101A</t>
         </is>
       </c>
       <c r="E114" s="4" t="inlineStr">
         <is>
-          <t>Monorail hoists P-101/P-102 maintenance (2 x 7.5 kW)</t>
+          <t>125 V DC battery charger A (switchgear control), 2 x 100 %</t>
         </is>
       </c>
       <c r="F114" s="5" t="n">
         <v>0.48</v>
       </c>
       <c r="G114" s="7" t="n">
-        <v>22.6</v>
+        <v>9.4</v>
       </c>
       <c r="H114" s="7" t="n">
-        <v>85</v>
+        <v>20</v>
       </c>
       <c r="I114" s="4" t="inlineStr">
         <is>
-          <t>area:DESALT_P</t>
+          <t>inside SS-100</t>
         </is>
       </c>
       <c r="J114" s="4" t="inlineStr">
@@ -8818,7 +8830,7 @@
         <v>30.6</v>
       </c>
       <c r="N114" s="5" t="n">
-        <v>3.3</v>
+        <v>0.34</v>
       </c>
       <c r="O114" s="4" t="n"/>
       <c r="P114" s="4" t="n"/>
@@ -8828,7 +8840,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>MCCB 30 A (125 AF)</t>
+          <t>MCCB 15 A (125 AF)</t>
         </is>
       </c>
       <c r="T114" s="4" t="inlineStr"/>
@@ -8841,7 +8853,7 @@
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>CBL-SB-101</t>
+          <t>CBL-BC-101B</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr">
@@ -8851,26 +8863,26 @@
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>SB-101</t>
+          <t>BC-101B</t>
         </is>
       </c>
       <c r="E115" s="4" t="inlineStr">
         <is>
-          <t>H-101 convection sootblowers (8 x 0.75 kW, electric retract)</t>
+          <t>125 V DC battery charger B (switchgear control), 2 x 100 %</t>
         </is>
       </c>
       <c r="F115" s="5" t="n">
         <v>0.48</v>
       </c>
       <c r="G115" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="H115" s="6" t="n">
-        <v>120</v>
+        <v>9.4</v>
+      </c>
+      <c r="H115" s="7" t="n">
+        <v>20</v>
       </c>
       <c r="I115" s="4" t="inlineStr">
         <is>
-          <t>area:H101</t>
+          <t>inside SS-100</t>
         </is>
       </c>
       <c r="J115" s="4" t="inlineStr">
@@ -8888,7 +8900,7 @@
         <v>30.6</v>
       </c>
       <c r="N115" s="5" t="n">
-        <v>1.86</v>
+        <v>0.34</v>
       </c>
       <c r="O115" s="4" t="n"/>
       <c r="P115" s="4" t="n"/>
@@ -8911,7 +8923,7 @@
       </c>
       <c r="B116" s="4" t="inlineStr">
         <is>
-          <t>CBL-LTR-101A</t>
+          <t>CBL-UPS-101A</t>
         </is>
       </c>
       <c r="C116" s="4" t="inlineStr">
@@ -8921,19 +8933,19 @@
       </c>
       <c r="D116" s="4" t="inlineStr">
         <is>
-          <t>LTR-101A (75 kVA 480-208Y/120 V)</t>
+          <t>UPS-101A</t>
         </is>
       </c>
       <c r="E116" s="4" t="inlineStr">
         <is>
-          <t>Lighting &amp; small-power transformer -&gt; LDB-101A</t>
+          <t>UPS-101A rectifier input (2 x 100 % 100 kVA, 50 % share + battery recharge)</t>
         </is>
       </c>
       <c r="F116" s="5" t="n">
         <v>0.48</v>
       </c>
       <c r="G116" s="7" t="n">
-        <v>90.2</v>
+        <v>43.1</v>
       </c>
       <c r="H116" s="7" t="n">
         <v>20</v>
@@ -8945,30 +8957,30 @@
       </c>
       <c r="J116" s="4" t="inlineStr">
         <is>
-          <t>3C x 35 + E16 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
+          <t>3C x 10 + E10 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
         </is>
       </c>
       <c r="K116" s="4" t="n">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="L116" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M116" s="6" t="n">
-        <v>115</v>
+      <c r="M116" s="7" t="n">
+        <v>54.6</v>
       </c>
       <c r="N116" s="5" t="n">
-        <v>0.43</v>
+        <v>0.7</v>
       </c>
       <c r="O116" s="4" t="n"/>
       <c r="P116" s="4" t="n"/>
       <c r="Q116" s="4" t="n"/>
       <c r="R116" s="7" t="n">
-        <v>4.9</v>
+        <v>2.7</v>
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>MCCB 125 A (125 AF)</t>
+          <t>MCCB 60 A (125 AF)</t>
         </is>
       </c>
       <c r="T116" s="4" t="inlineStr"/>
@@ -8981,7 +8993,7 @@
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>CBL-LTR-101B</t>
+          <t>CBL-UPS-101B</t>
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr">
@@ -8991,19 +9003,19 @@
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>LTR-101B (75 kVA 480-208Y/120 V)</t>
+          <t>UPS-101B</t>
         </is>
       </c>
       <c r="E117" s="4" t="inlineStr">
         <is>
-          <t>Lighting &amp; small-power transformer -&gt; LDB-101B</t>
+          <t>UPS-101B rectifier input (2 x 100 % 100 kVA, 50 % share + battery recharge)</t>
         </is>
       </c>
       <c r="F117" s="5" t="n">
         <v>0.48</v>
       </c>
       <c r="G117" s="7" t="n">
-        <v>90.2</v>
+        <v>43.1</v>
       </c>
       <c r="H117" s="7" t="n">
         <v>20</v>
@@ -9015,44 +9027,324 @@
       </c>
       <c r="J117" s="4" t="inlineStr">
         <is>
-          <t>3C x 35 + E16 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
+          <t>3C x 10 + E10 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
         </is>
       </c>
       <c r="K117" s="4" t="n">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="L117" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M117" s="6" t="n">
-        <v>115</v>
+      <c r="M117" s="7" t="n">
+        <v>54.6</v>
       </c>
       <c r="N117" s="5" t="n">
-        <v>0.43</v>
+        <v>0.7</v>
       </c>
       <c r="O117" s="4" t="n"/>
       <c r="P117" s="4" t="n"/>
       <c r="Q117" s="4" t="n"/>
       <c r="R117" s="7" t="n">
-        <v>4.9</v>
+        <v>2.7</v>
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>MCCB 125 A (125 AF)</t>
+          <t>MCCB 60 A (125 AF)</t>
         </is>
       </c>
       <c r="T117" s="4" t="inlineStr"/>
       <c r="U117" s="4" t="inlineStr"/>
       <c r="V117" s="4" t="inlineStr"/>
     </row>
+    <row r="118">
+      <c r="A118" s="4" t="n">
+        <v>114</v>
+      </c>
+      <c r="B118" s="4" t="inlineStr">
+        <is>
+          <t>CBL-HST-101</t>
+        </is>
+      </c>
+      <c r="C118" s="4" t="inlineStr">
+        <is>
+          <t>MCC-101A</t>
+        </is>
+      </c>
+      <c r="D118" s="4" t="inlineStr">
+        <is>
+          <t>HST-101</t>
+        </is>
+      </c>
+      <c r="E118" s="4" t="inlineStr">
+        <is>
+          <t>Monorail hoists P-101/P-102 maintenance (2 x 7.5 kW)</t>
+        </is>
+      </c>
+      <c r="F118" s="5" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="G118" s="7" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="H118" s="7" t="n">
+        <v>85</v>
+      </c>
+      <c r="I118" s="4" t="inlineStr">
+        <is>
+          <t>area:DESALT_P</t>
+        </is>
+      </c>
+      <c r="J118" s="4" t="inlineStr">
+        <is>
+          <t>3C x 4 + E4 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
+        </is>
+      </c>
+      <c r="K118" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="L118" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M118" s="7" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="N118" s="5" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O118" s="4" t="n"/>
+      <c r="P118" s="4" t="n"/>
+      <c r="Q118" s="4" t="n"/>
+      <c r="R118" s="7" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="S118" s="4" t="inlineStr">
+        <is>
+          <t>MCCB 30 A (125 AF)</t>
+        </is>
+      </c>
+      <c r="T118" s="4" t="inlineStr"/>
+      <c r="U118" s="4" t="inlineStr"/>
+      <c r="V118" s="4" t="inlineStr"/>
+    </row>
     <row r="119">
-      <c r="B119" s="8" t="inlineStr">
+      <c r="A119" s="4" t="n">
+        <v>115</v>
+      </c>
+      <c r="B119" s="4" t="inlineStr">
+        <is>
+          <t>CBL-SB-101</t>
+        </is>
+      </c>
+      <c r="C119" s="4" t="inlineStr">
+        <is>
+          <t>MCC-101B</t>
+        </is>
+      </c>
+      <c r="D119" s="4" t="inlineStr">
+        <is>
+          <t>SB-101</t>
+        </is>
+      </c>
+      <c r="E119" s="4" t="inlineStr">
+        <is>
+          <t>H-101 convection sootblowers (8 x 0.75 kW, electric retract)</t>
+        </is>
+      </c>
+      <c r="F119" s="5" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="G119" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="H119" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="I119" s="4" t="inlineStr">
+        <is>
+          <t>area:H101</t>
+        </is>
+      </c>
+      <c r="J119" s="4" t="inlineStr">
+        <is>
+          <t>3C x 4 + E4 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
+        </is>
+      </c>
+      <c r="K119" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="L119" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M119" s="7" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="N119" s="5" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="O119" s="4" t="n"/>
+      <c r="P119" s="4" t="n"/>
+      <c r="Q119" s="4" t="n"/>
+      <c r="R119" s="7" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="S119" s="4" t="inlineStr">
+        <is>
+          <t>MCCB 15 A (125 AF)</t>
+        </is>
+      </c>
+      <c r="T119" s="4" t="inlineStr"/>
+      <c r="U119" s="4" t="inlineStr"/>
+      <c r="V119" s="4" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="4" t="n">
+        <v>116</v>
+      </c>
+      <c r="B120" s="4" t="inlineStr">
+        <is>
+          <t>CBL-LTR-101A</t>
+        </is>
+      </c>
+      <c r="C120" s="4" t="inlineStr">
+        <is>
+          <t>MCC-101A</t>
+        </is>
+      </c>
+      <c r="D120" s="4" t="inlineStr">
+        <is>
+          <t>LTR-101A (75 kVA 480-208Y/120 V)</t>
+        </is>
+      </c>
+      <c r="E120" s="4" t="inlineStr">
+        <is>
+          <t>Lighting &amp; small-power transformer -&gt; LDB-101A</t>
+        </is>
+      </c>
+      <c r="F120" s="5" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="G120" s="7" t="n">
+        <v>90.2</v>
+      </c>
+      <c r="H120" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="I120" s="4" t="inlineStr">
+        <is>
+          <t>inside SS-100</t>
+        </is>
+      </c>
+      <c r="J120" s="4" t="inlineStr">
+        <is>
+          <t>3C x 35 + E16 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
+        </is>
+      </c>
+      <c r="K120" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="L120" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M120" s="6" t="n">
+        <v>115</v>
+      </c>
+      <c r="N120" s="5" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="O120" s="4" t="n"/>
+      <c r="P120" s="4" t="n"/>
+      <c r="Q120" s="4" t="n"/>
+      <c r="R120" s="7" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="S120" s="4" t="inlineStr">
+        <is>
+          <t>MCCB 125 A (125 AF)</t>
+        </is>
+      </c>
+      <c r="T120" s="4" t="inlineStr"/>
+      <c r="U120" s="4" t="inlineStr"/>
+      <c r="V120" s="4" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="4" t="n">
+        <v>117</v>
+      </c>
+      <c r="B121" s="4" t="inlineStr">
+        <is>
+          <t>CBL-LTR-101B</t>
+        </is>
+      </c>
+      <c r="C121" s="4" t="inlineStr">
+        <is>
+          <t>MCC-101B</t>
+        </is>
+      </c>
+      <c r="D121" s="4" t="inlineStr">
+        <is>
+          <t>LTR-101B (75 kVA 480-208Y/120 V)</t>
+        </is>
+      </c>
+      <c r="E121" s="4" t="inlineStr">
+        <is>
+          <t>Lighting &amp; small-power transformer -&gt; LDB-101B</t>
+        </is>
+      </c>
+      <c r="F121" s="5" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="G121" s="7" t="n">
+        <v>90.2</v>
+      </c>
+      <c r="H121" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="I121" s="4" t="inlineStr">
+        <is>
+          <t>inside SS-100</t>
+        </is>
+      </c>
+      <c r="J121" s="4" t="inlineStr">
+        <is>
+          <t>3C x 35 + E16 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
+        </is>
+      </c>
+      <c r="K121" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="L121" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M121" s="6" t="n">
+        <v>115</v>
+      </c>
+      <c r="N121" s="5" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="O121" s="4" t="n"/>
+      <c r="P121" s="4" t="n"/>
+      <c r="Q121" s="4" t="n"/>
+      <c r="R121" s="7" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="S121" s="4" t="inlineStr">
+        <is>
+          <t>MCCB 125 A (125 AF)</t>
+        </is>
+      </c>
+      <c r="T121" s="4" t="inlineStr"/>
+      <c r="U121" s="4" t="inlineStr"/>
+      <c r="V121" s="4" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="B123" s="8" t="inlineStr">
         <is>
           <t>TOTAL LENGTH (m)</t>
         </is>
       </c>
-      <c r="H119" s="8">
-        <f>SUM(H5:H117)</f>
+      <c r="H123" s="8">
+        <f>SUM(H5:H121)</f>
         <v/>
       </c>
     </row>
@@ -9191,10 +9483,10 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>810</v>
+        <v>1280</v>
       </c>
       <c r="C11" s="6" t="n">
-        <v>891.0000000000001</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="12">
@@ -9230,62 +9522,62 @@
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>1550</v>
+        <v>1320</v>
       </c>
       <c r="C14" s="6" t="n">
-        <v>1705</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>3C x 35 + E16 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
+          <t>3C x 35 + 3E x 11.6667 mm2 Cu/XLPE/CWS/SWA/PVC 0.6/1 kV, symmetrical VFD cable</t>
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>925</v>
+        <v>870</v>
       </c>
       <c r="C15" s="6" t="n">
-        <v>1017.5</v>
+        <v>957.0000000000001</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>3C x 4 + E4 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
+          <t>3C x 35 + E16 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>3890</v>
+        <v>925</v>
       </c>
       <c r="C16" s="6" t="n">
-        <v>4279</v>
+        <v>1017.5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>3C x 6 + E6 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
+          <t>3C x 4 + E4 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
         </is>
       </c>
       <c r="B17" s="6" t="n">
-        <v>940</v>
+        <v>3890</v>
       </c>
       <c r="C17" s="6" t="n">
-        <v>1034</v>
+        <v>4279</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>3C x 70 + 3E x 16 mm2 Cu/XLPE/CWS/SWA/PVC 0.6/1 kV, symmetrical VFD cable</t>
+          <t>3C x 6 + E6 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
         </is>
       </c>
       <c r="B18" s="6" t="n">
-        <v>570</v>
+        <v>940</v>
       </c>
       <c r="C18" s="6" t="n">
-        <v>627</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="19">
@@ -9409,7 +9701,7 @@
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t>6. Route length = Manhattan distance from SS-100 reference point (25, 12.5) m to the consumer + 15 m riser/termination allowance (+10 m for air-cooler fan motors on top of the pipe rack), rounded up to 5 m. Coordinates source: data/layout.json (137 tagged items).</t>
+          <t>6. Route length = Manhattan distance from SS-100 reference point (25, 12.5) m to the consumer + 15 m riser/termination allowance (+10 m for air-cooler fan motors on top of the pipe rack), rounded up to 5 m. Coordinates source: data/layout.json (139 tagged items).</t>
         </is>
       </c>
     </row>

--- a/deliverables/05-electrical/CFU-000-EL-CBL-001_Cable-Schedule.xlsx
+++ b/deliverables/05-electrical/CFU-000-EL-CBL-001_Cable-Schedule.xlsx
@@ -468,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V123"/>
+  <dimension ref="A1:V125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -824,7 +824,7 @@
       <c r="P7" s="4" t="n"/>
       <c r="Q7" s="4" t="n"/>
       <c r="R7" s="7" t="n">
-        <v>78.5</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
       <c r="P8" s="4" t="n"/>
       <c r="Q8" s="4" t="n"/>
       <c r="R8" s="7" t="n">
-        <v>78.5</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
       <c r="P12" s="4" t="n"/>
       <c r="Q12" s="4" t="n"/>
       <c r="R12" s="7" t="n">
-        <v>78.5</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
       <c r="P13" s="4" t="n"/>
       <c r="Q13" s="4" t="n"/>
       <c r="R13" s="7" t="n">
-        <v>78.5</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
         <v>5.88</v>
       </c>
       <c r="R15" s="7" t="n">
-        <v>55.5</v>
+        <v>55.6</v>
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>5.84</v>
       </c>
       <c r="R16" s="7" t="n">
-        <v>55.5</v>
+        <v>55.6</v>
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
         <v>5.81</v>
       </c>
       <c r="R17" s="7" t="n">
-        <v>55.5</v>
+        <v>55.6</v>
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>5.85</v>
       </c>
       <c r="R18" s="7" t="n">
-        <v>55.5</v>
+        <v>55.6</v>
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
@@ -1730,7 +1730,7 @@
         <v>2.9</v>
       </c>
       <c r="R19" s="7" t="n">
-        <v>55.5</v>
+        <v>55.6</v>
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         <v>2.92</v>
       </c>
       <c r="R20" s="7" t="n">
-        <v>55.5</v>
+        <v>55.6</v>
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
@@ -1898,7 +1898,7 @@
         <v>2.01</v>
       </c>
       <c r="R21" s="7" t="n">
-        <v>55.5</v>
+        <v>55.6</v>
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         <v>2.01</v>
       </c>
       <c r="R22" s="7" t="n">
-        <v>55.5</v>
+        <v>55.6</v>
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
       <c r="P23" s="4" t="n"/>
       <c r="Q23" s="4" t="n"/>
       <c r="R23" s="7" t="n">
-        <v>55.5</v>
+        <v>55.6</v>
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
       <c r="P24" s="4" t="n"/>
       <c r="Q24" s="4" t="n"/>
       <c r="R24" s="7" t="n">
-        <v>55.5</v>
+        <v>55.6</v>
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
@@ -3283,7 +3283,7 @@
         <v>1.7</v>
       </c>
       <c r="Q39" s="5" t="n">
-        <v>10.6</v>
+        <v>10.59</v>
       </c>
       <c r="R39" s="7" t="n">
         <v>8.6</v>
@@ -3553,7 +3553,7 @@
         <v>0.48</v>
       </c>
       <c r="G43" s="7" t="n">
-        <v>28.8</v>
+        <v>46.7</v>
       </c>
       <c r="H43" s="7" t="n">
         <v>70</v>
@@ -3565,36 +3565,36 @@
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
-          <t>3C x 6 + E6 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
+          <t>3C x 16 + E16 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
         </is>
       </c>
       <c r="K43" s="4" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="L43" s="4" t="n">
         <v>1</v>
       </c>
       <c r="M43" s="7" t="n">
-        <v>39.3</v>
+        <v>72.8</v>
       </c>
       <c r="N43" s="5" t="n">
-        <v>2.47</v>
+        <v>1.53</v>
       </c>
       <c r="O43" s="5" t="n">
-        <v>6.89</v>
+        <v>4.56</v>
       </c>
       <c r="P43" s="5" t="n">
-        <v>0.44</v>
+        <v>0.71</v>
       </c>
       <c r="Q43" s="5" t="n">
-        <v>7.34</v>
+        <v>5.27</v>
       </c>
       <c r="R43" s="7" t="n">
-        <v>2.7</v>
+        <v>4.9</v>
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>MCCB 60 A (125 AF) + DOL, NEMA size 2</t>
+          <t>MCCB 90 A (125 AF) + DOL, NEMA size 3</t>
         </is>
       </c>
       <c r="T43" s="4" t="inlineStr"/>
@@ -3629,7 +3629,7 @@
         <v>0.48</v>
       </c>
       <c r="G44" s="7" t="n">
-        <v>28.8</v>
+        <v>46.7</v>
       </c>
       <c r="H44" s="7" t="n">
         <v>75</v>
@@ -3641,36 +3641,36 @@
       </c>
       <c r="J44" s="4" t="inlineStr">
         <is>
-          <t>3C x 6 + E6 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
+          <t>3C x 16 + E16 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
         </is>
       </c>
       <c r="K44" s="4" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="L44" s="4" t="n">
         <v>1</v>
       </c>
       <c r="M44" s="7" t="n">
-        <v>39.3</v>
+        <v>72.8</v>
       </c>
       <c r="N44" s="5" t="n">
-        <v>2.64</v>
+        <v>1.64</v>
       </c>
       <c r="O44" s="5" t="n">
-        <v>7.39</v>
+        <v>4.88</v>
       </c>
       <c r="P44" s="5" t="n">
-        <v>0.44</v>
+        <v>0.71</v>
       </c>
       <c r="Q44" s="5" t="n">
-        <v>7.83</v>
+        <v>5.6</v>
       </c>
       <c r="R44" s="7" t="n">
-        <v>2.7</v>
+        <v>4.9</v>
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>MCCB 60 A (125 AF) + DOL, NEMA size 2</t>
+          <t>MCCB 90 A (125 AF) + DOL, NEMA size 3</t>
         </is>
       </c>
       <c r="T44" s="4" t="inlineStr"/>
@@ -4215,7 +4215,7 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>CBL-P-201A</t>
+          <t>CBL-P-119A</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
@@ -4225,22 +4225,22 @@
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>P-201A</t>
+          <t>P-119A</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>LVGO pumparound / product pump A</t>
+          <t>Flare KO drum pump-out pump A</t>
         </is>
       </c>
       <c r="F52" s="5" t="n">
         <v>0.48</v>
       </c>
-      <c r="G52" s="6" t="n">
-        <v>160.1</v>
+      <c r="G52" s="7" t="n">
+        <v>12.6</v>
       </c>
       <c r="H52" s="6" t="n">
-        <v>255</v>
+        <v>235</v>
       </c>
       <c r="I52" s="4" t="inlineStr">
         <is>
@@ -4249,36 +4249,36 @@
       </c>
       <c r="J52" s="4" t="inlineStr">
         <is>
-          <t>3C x 150 + E95 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
+          <t>3C x 6 + E6 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
         </is>
       </c>
       <c r="K52" s="4" t="n">
-        <v>150</v>
+        <v>6</v>
       </c>
       <c r="L52" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M52" s="6" t="n">
-        <v>290.5</v>
+      <c r="M52" s="7" t="n">
+        <v>39.3</v>
       </c>
       <c r="N52" s="5" t="n">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="O52" s="5" t="n">
-        <v>12.31</v>
+        <v>10.11</v>
       </c>
       <c r="P52" s="5" t="n">
-        <v>2.41</v>
+        <v>0.19</v>
       </c>
       <c r="Q52" s="5" t="n">
-        <v>14.73</v>
+        <v>10.31</v>
       </c>
       <c r="R52" s="7" t="n">
-        <v>12.1</v>
+        <v>1.6</v>
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>MCCB 300 A (400 AF) + DOL, NEMA size 5</t>
+          <t>MCCB 25 A (125 AF) + DOL, NEMA size 1</t>
         </is>
       </c>
       <c r="T52" s="4" t="inlineStr"/>
@@ -4291,7 +4291,7 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>CBL-P-201B</t>
+          <t>CBL-P-119B</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
@@ -4301,22 +4301,22 @@
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>P-201B</t>
+          <t>P-119B</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>LVGO pumparound / product pump B</t>
+          <t>Flare KO drum pump-out pump B</t>
         </is>
       </c>
       <c r="F53" s="5" t="n">
         <v>0.48</v>
       </c>
-      <c r="G53" s="6" t="n">
-        <v>160.1</v>
+      <c r="G53" s="7" t="n">
+        <v>12.6</v>
       </c>
       <c r="H53" s="6" t="n">
-        <v>260</v>
+        <v>235</v>
       </c>
       <c r="I53" s="4" t="inlineStr">
         <is>
@@ -4325,36 +4325,36 @@
       </c>
       <c r="J53" s="4" t="inlineStr">
         <is>
-          <t>3C x 150 + E95 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
+          <t>3C x 6 + E6 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
         </is>
       </c>
       <c r="K53" s="4" t="n">
-        <v>150</v>
+        <v>6</v>
       </c>
       <c r="L53" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M53" s="6" t="n">
-        <v>290.5</v>
+      <c r="M53" s="7" t="n">
+        <v>39.3</v>
       </c>
       <c r="N53" s="5" t="n">
-        <v>2.65</v>
+        <v>3.5</v>
       </c>
       <c r="O53" s="5" t="n">
-        <v>12.56</v>
+        <v>10.11</v>
       </c>
       <c r="P53" s="5" t="n">
-        <v>2.41</v>
+        <v>0.19</v>
       </c>
       <c r="Q53" s="5" t="n">
-        <v>14.97</v>
+        <v>10.31</v>
       </c>
       <c r="R53" s="7" t="n">
-        <v>12.1</v>
+        <v>1.6</v>
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>MCCB 300 A (400 AF) + DOL, NEMA size 5</t>
+          <t>MCCB 25 A (125 AF) + DOL, NEMA size 1</t>
         </is>
       </c>
       <c r="T53" s="4" t="inlineStr"/>
@@ -4367,7 +4367,7 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>CBL-P-203A</t>
+          <t>CBL-P-201A</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
@@ -4377,22 +4377,22 @@
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>P-203A</t>
+          <t>P-201A</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>Slop wax pump A</t>
+          <t>LVGO pumparound / product pump A</t>
         </is>
       </c>
       <c r="F54" s="5" t="n">
         <v>0.48</v>
       </c>
-      <c r="G54" s="7" t="n">
-        <v>9.199999999999999</v>
+      <c r="G54" s="6" t="n">
+        <v>160.1</v>
       </c>
       <c r="H54" s="6" t="n">
-        <v>240</v>
+        <v>255</v>
       </c>
       <c r="I54" s="4" t="inlineStr">
         <is>
@@ -4401,36 +4401,36 @@
       </c>
       <c r="J54" s="4" t="inlineStr">
         <is>
-          <t>3C x 4 + E4 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
+          <t>3C x 150 + E95 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
         </is>
       </c>
       <c r="K54" s="4" t="n">
-        <v>4</v>
+        <v>150</v>
       </c>
       <c r="L54" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M54" s="7" t="n">
-        <v>30.6</v>
+      <c r="M54" s="6" t="n">
+        <v>290.5</v>
       </c>
       <c r="N54" s="5" t="n">
-        <v>3.9</v>
+        <v>2.6</v>
       </c>
       <c r="O54" s="5" t="n">
-        <v>11.13</v>
+        <v>12.31</v>
       </c>
       <c r="P54" s="5" t="n">
-        <v>0.14</v>
+        <v>2.41</v>
       </c>
       <c r="Q54" s="5" t="n">
-        <v>11.27</v>
+        <v>14.73</v>
       </c>
       <c r="R54" s="7" t="n">
-        <v>1.6</v>
+        <v>12.1</v>
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>MCCB 20 A (125 AF) + DOL, NEMA size 0</t>
+          <t>MCCB 300 A (400 AF) + DOL, NEMA size 5</t>
         </is>
       </c>
       <c r="T54" s="4" t="inlineStr"/>
@@ -4443,7 +4443,7 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>CBL-P-203B</t>
+          <t>CBL-P-201B</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
@@ -4453,22 +4453,22 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>P-203B</t>
+          <t>P-201B</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>Slop wax pump B</t>
+          <t>LVGO pumparound / product pump B</t>
         </is>
       </c>
       <c r="F55" s="5" t="n">
         <v>0.48</v>
       </c>
-      <c r="G55" s="7" t="n">
-        <v>9.199999999999999</v>
+      <c r="G55" s="6" t="n">
+        <v>160.1</v>
       </c>
       <c r="H55" s="6" t="n">
-        <v>245</v>
+        <v>260</v>
       </c>
       <c r="I55" s="4" t="inlineStr">
         <is>
@@ -4477,36 +4477,36 @@
       </c>
       <c r="J55" s="4" t="inlineStr">
         <is>
-          <t>3C x 4 + E4 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
+          <t>3C x 150 + E95 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
         </is>
       </c>
       <c r="K55" s="4" t="n">
-        <v>4</v>
+        <v>150</v>
       </c>
       <c r="L55" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M55" s="7" t="n">
-        <v>30.6</v>
+      <c r="M55" s="6" t="n">
+        <v>290.5</v>
       </c>
       <c r="N55" s="5" t="n">
-        <v>3.98</v>
+        <v>2.65</v>
       </c>
       <c r="O55" s="5" t="n">
-        <v>11.36</v>
+        <v>12.56</v>
       </c>
       <c r="P55" s="5" t="n">
-        <v>0.14</v>
+        <v>2.41</v>
       </c>
       <c r="Q55" s="5" t="n">
-        <v>11.51</v>
+        <v>14.97</v>
       </c>
       <c r="R55" s="7" t="n">
-        <v>1.6</v>
+        <v>12.1</v>
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>MCCB 20 A (125 AF) + DOL, NEMA size 0</t>
+          <t>MCCB 300 A (400 AF) + DOL, NEMA size 5</t>
         </is>
       </c>
       <c r="T55" s="4" t="inlineStr"/>
@@ -4519,7 +4519,7 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>CBL-P-204A</t>
+          <t>CBL-P-203A</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
@@ -4529,22 +4529,22 @@
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>P-204A</t>
+          <t>P-203A</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>Vacuum residue (incl. quench) pump A</t>
+          <t>Slop wax pump A</t>
         </is>
       </c>
       <c r="F56" s="5" t="n">
         <v>0.48</v>
       </c>
-      <c r="G56" s="6" t="n">
-        <v>192.1</v>
+      <c r="G56" s="7" t="n">
+        <v>9.199999999999999</v>
       </c>
       <c r="H56" s="6" t="n">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="I56" s="4" t="inlineStr">
         <is>
@@ -4553,36 +4553,36 @@
       </c>
       <c r="J56" s="4" t="inlineStr">
         <is>
-          <t>3C x 240 + E120 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
+          <t>3C x 4 + E4 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
         </is>
       </c>
       <c r="K56" s="4" t="n">
-        <v>240</v>
+        <v>4</v>
       </c>
       <c r="L56" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M56" s="6" t="n">
-        <v>391.7</v>
+      <c r="M56" s="7" t="n">
+        <v>30.6</v>
       </c>
       <c r="N56" s="5" t="n">
-        <v>1.99</v>
+        <v>3.9</v>
       </c>
       <c r="O56" s="5" t="n">
-        <v>11.31</v>
+        <v>11.13</v>
       </c>
       <c r="P56" s="5" t="n">
-        <v>2.88</v>
+        <v>0.14</v>
       </c>
       <c r="Q56" s="5" t="n">
-        <v>14.19</v>
+        <v>11.27</v>
       </c>
       <c r="R56" s="7" t="n">
-        <v>12.1</v>
+        <v>1.6</v>
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>MCCB 350 A (400 AF) + DOL, NEMA size 5</t>
+          <t>MCCB 20 A (125 AF) + DOL, NEMA size 0</t>
         </is>
       </c>
       <c r="T56" s="4" t="inlineStr"/>
@@ -4595,7 +4595,7 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>CBL-P-204B</t>
+          <t>CBL-P-203B</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
@@ -4605,22 +4605,22 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>P-204B</t>
+          <t>P-203B</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>Vacuum residue (incl. quench) pump B</t>
+          <t>Slop wax pump B</t>
         </is>
       </c>
       <c r="F57" s="5" t="n">
         <v>0.48</v>
       </c>
-      <c r="G57" s="6" t="n">
-        <v>192.1</v>
+      <c r="G57" s="7" t="n">
+        <v>9.199999999999999</v>
       </c>
       <c r="H57" s="6" t="n">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="I57" s="4" t="inlineStr">
         <is>
@@ -4629,36 +4629,36 @@
       </c>
       <c r="J57" s="4" t="inlineStr">
         <is>
-          <t>3C x 240 + E120 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
+          <t>3C x 4 + E4 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
         </is>
       </c>
       <c r="K57" s="4" t="n">
-        <v>240</v>
+        <v>4</v>
       </c>
       <c r="L57" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M57" s="6" t="n">
-        <v>391.7</v>
+      <c r="M57" s="7" t="n">
+        <v>30.6</v>
       </c>
       <c r="N57" s="5" t="n">
-        <v>2.04</v>
+        <v>3.98</v>
       </c>
       <c r="O57" s="5" t="n">
-        <v>11.55</v>
+        <v>11.36</v>
       </c>
       <c r="P57" s="5" t="n">
-        <v>2.88</v>
+        <v>0.14</v>
       </c>
       <c r="Q57" s="5" t="n">
-        <v>14.43</v>
+        <v>11.51</v>
       </c>
       <c r="R57" s="7" t="n">
-        <v>12.1</v>
+        <v>1.6</v>
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>MCCB 350 A (400 AF) + DOL, NEMA size 5</t>
+          <t>MCCB 20 A (125 AF) + DOL, NEMA size 0</t>
         </is>
       </c>
       <c r="T57" s="4" t="inlineStr"/>
@@ -4671,7 +4671,7 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>CBL-P-205A</t>
+          <t>CBL-P-204A</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
@@ -4681,22 +4681,22 @@
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>P-205A</t>
+          <t>P-204A</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>Hotwell sour water pump A</t>
+          <t>Vacuum residue (incl. quench) pump A</t>
         </is>
       </c>
       <c r="F58" s="5" t="n">
         <v>0.48</v>
       </c>
-      <c r="G58" s="7" t="n">
-        <v>6.2</v>
+      <c r="G58" s="6" t="n">
+        <v>192.1</v>
       </c>
       <c r="H58" s="6" t="n">
-        <v>285</v>
+        <v>235</v>
       </c>
       <c r="I58" s="4" t="inlineStr">
         <is>
@@ -4705,36 +4705,36 @@
       </c>
       <c r="J58" s="4" t="inlineStr">
         <is>
-          <t>3C x 4 + E4 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
+          <t>3C x 240 + E120 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
         </is>
       </c>
       <c r="K58" s="4" t="n">
-        <v>4</v>
+        <v>240</v>
       </c>
       <c r="L58" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M58" s="7" t="n">
-        <v>30.6</v>
+      <c r="M58" s="6" t="n">
+        <v>391.7</v>
       </c>
       <c r="N58" s="5" t="n">
-        <v>3.12</v>
+        <v>1.99</v>
       </c>
       <c r="O58" s="5" t="n">
-        <v>8.890000000000001</v>
+        <v>11.31</v>
       </c>
       <c r="P58" s="5" t="n">
-        <v>0.1</v>
+        <v>2.88</v>
       </c>
       <c r="Q58" s="5" t="n">
-        <v>8.99</v>
+        <v>14.19</v>
       </c>
       <c r="R58" s="7" t="n">
-        <v>1.6</v>
+        <v>12.1</v>
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>MCCB 15 A (125 AF) + DOL, NEMA size 0</t>
+          <t>MCCB 350 A (400 AF) + DOL, NEMA size 5</t>
         </is>
       </c>
       <c r="T58" s="4" t="inlineStr"/>
@@ -4747,7 +4747,7 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>CBL-P-205B</t>
+          <t>CBL-P-204B</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
@@ -4757,22 +4757,22 @@
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>P-205B</t>
+          <t>P-204B</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>Hotwell sour water pump B</t>
+          <t>Vacuum residue (incl. quench) pump B</t>
         </is>
       </c>
       <c r="F59" s="5" t="n">
         <v>0.48</v>
       </c>
-      <c r="G59" s="7" t="n">
-        <v>6.2</v>
+      <c r="G59" s="6" t="n">
+        <v>192.1</v>
       </c>
       <c r="H59" s="6" t="n">
-        <v>285</v>
+        <v>240</v>
       </c>
       <c r="I59" s="4" t="inlineStr">
         <is>
@@ -4781,36 +4781,36 @@
       </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
-          <t>3C x 4 + E4 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
+          <t>3C x 240 + E120 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
         </is>
       </c>
       <c r="K59" s="4" t="n">
-        <v>4</v>
+        <v>240</v>
       </c>
       <c r="L59" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M59" s="7" t="n">
-        <v>30.6</v>
+      <c r="M59" s="6" t="n">
+        <v>391.7</v>
       </c>
       <c r="N59" s="5" t="n">
-        <v>3.12</v>
+        <v>2.04</v>
       </c>
       <c r="O59" s="5" t="n">
-        <v>8.890000000000001</v>
+        <v>11.55</v>
       </c>
       <c r="P59" s="5" t="n">
-        <v>0.1</v>
+        <v>2.88</v>
       </c>
       <c r="Q59" s="5" t="n">
-        <v>8.99</v>
+        <v>14.43</v>
       </c>
       <c r="R59" s="7" t="n">
-        <v>1.6</v>
+        <v>12.1</v>
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>MCCB 15 A (125 AF) + DOL, NEMA size 0</t>
+          <t>MCCB 350 A (400 AF) + DOL, NEMA size 5</t>
         </is>
       </c>
       <c r="T59" s="4" t="inlineStr"/>
@@ -4823,7 +4823,7 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>CBL-P-206A</t>
+          <t>CBL-P-205A</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
@@ -4833,22 +4833,22 @@
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>P-206A</t>
+          <t>P-205A</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>Hotwell slop oil pump A</t>
+          <t>Hotwell sour water pump A</t>
         </is>
       </c>
       <c r="F60" s="5" t="n">
         <v>0.48</v>
       </c>
       <c r="G60" s="7" t="n">
-        <v>1.5</v>
+        <v>6.2</v>
       </c>
       <c r="H60" s="6" t="n">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="I60" s="4" t="inlineStr">
         <is>
@@ -4870,16 +4870,16 @@
         <v>30.6</v>
       </c>
       <c r="N60" s="5" t="n">
-        <v>0.7</v>
+        <v>3.12</v>
       </c>
       <c r="O60" s="5" t="n">
-        <v>2.16</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="P60" s="5" t="n">
-        <v>0.02</v>
+        <v>0.1</v>
       </c>
       <c r="Q60" s="5" t="n">
-        <v>2.19</v>
+        <v>8.99</v>
       </c>
       <c r="R60" s="7" t="n">
         <v>1.6</v>
@@ -4899,7 +4899,7 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>CBL-P-206B</t>
+          <t>CBL-P-205B</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
@@ -4909,22 +4909,22 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>P-206B</t>
+          <t>P-205B</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>Hotwell slop oil pump B</t>
+          <t>Hotwell sour water pump B</t>
         </is>
       </c>
       <c r="F61" s="5" t="n">
         <v>0.48</v>
       </c>
       <c r="G61" s="7" t="n">
-        <v>1.5</v>
+        <v>6.2</v>
       </c>
       <c r="H61" s="6" t="n">
-        <v>295</v>
+        <v>285</v>
       </c>
       <c r="I61" s="4" t="inlineStr">
         <is>
@@ -4946,16 +4946,16 @@
         <v>30.6</v>
       </c>
       <c r="N61" s="5" t="n">
-        <v>0.72</v>
+        <v>3.12</v>
       </c>
       <c r="O61" s="5" t="n">
-        <v>2.2</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="P61" s="5" t="n">
-        <v>0.02</v>
+        <v>0.1</v>
       </c>
       <c r="Q61" s="5" t="n">
-        <v>2.22</v>
+        <v>8.99</v>
       </c>
       <c r="R61" s="7" t="n">
         <v>1.6</v>
@@ -4975,7 +4975,7 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>CBL-K-101A</t>
+          <t>CBL-P-206A</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
@@ -4985,22 +4985,22 @@
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>K-101A</t>
+          <t>P-206A</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>H-101 forced-draft fan A</t>
+          <t>Hotwell slop oil pump A</t>
         </is>
       </c>
       <c r="F62" s="5" t="n">
         <v>0.48</v>
       </c>
-      <c r="G62" s="6" t="n">
-        <v>134.6</v>
+      <c r="G62" s="7" t="n">
+        <v>1.5</v>
       </c>
       <c r="H62" s="6" t="n">
-        <v>100</v>
+        <v>290</v>
       </c>
       <c r="I62" s="4" t="inlineStr">
         <is>
@@ -5009,36 +5009,36 @@
       </c>
       <c r="J62" s="4" t="inlineStr">
         <is>
-          <t>3C x 70 + E35 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
+          <t>3C x 4 + E4 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
         </is>
       </c>
       <c r="K62" s="4" t="n">
-        <v>70</v>
+        <v>4</v>
       </c>
       <c r="L62" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M62" s="6" t="n">
-        <v>179.1</v>
+      <c r="M62" s="7" t="n">
+        <v>30.6</v>
       </c>
       <c r="N62" s="5" t="n">
-        <v>1.63</v>
+        <v>0.7</v>
       </c>
       <c r="O62" s="5" t="n">
-        <v>6.1</v>
+        <v>2.16</v>
       </c>
       <c r="P62" s="5" t="n">
-        <v>2.04</v>
+        <v>0.02</v>
       </c>
       <c r="Q62" s="5" t="n">
-        <v>8.130000000000001</v>
+        <v>2.19</v>
       </c>
       <c r="R62" s="7" t="n">
-        <v>8.6</v>
+        <v>1.6</v>
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>MCCB 250 A (250 AF) + DOL, NEMA size 5</t>
+          <t>MCCB 15 A (125 AF) + DOL, NEMA size 0</t>
         </is>
       </c>
       <c r="T62" s="4" t="inlineStr"/>
@@ -5051,7 +5051,7 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>CBL-K-101B</t>
+          <t>CBL-P-206B</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
@@ -5061,22 +5061,22 @@
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>K-101B</t>
+          <t>P-206B</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>H-101 forced-draft fan B</t>
+          <t>Hotwell slop oil pump B</t>
         </is>
       </c>
       <c r="F63" s="5" t="n">
         <v>0.48</v>
       </c>
-      <c r="G63" s="6" t="n">
-        <v>134.6</v>
+      <c r="G63" s="7" t="n">
+        <v>1.5</v>
       </c>
       <c r="H63" s="6" t="n">
-        <v>105</v>
+        <v>295</v>
       </c>
       <c r="I63" s="4" t="inlineStr">
         <is>
@@ -5085,36 +5085,36 @@
       </c>
       <c r="J63" s="4" t="inlineStr">
         <is>
-          <t>3C x 70 + E35 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
+          <t>3C x 4 + E4 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
         </is>
       </c>
       <c r="K63" s="4" t="n">
-        <v>70</v>
+        <v>4</v>
       </c>
       <c r="L63" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M63" s="6" t="n">
-        <v>179.1</v>
+      <c r="M63" s="7" t="n">
+        <v>30.6</v>
       </c>
       <c r="N63" s="5" t="n">
-        <v>1.71</v>
+        <v>0.72</v>
       </c>
       <c r="O63" s="5" t="n">
-        <v>6.4</v>
+        <v>2.2</v>
       </c>
       <c r="P63" s="5" t="n">
-        <v>2.04</v>
+        <v>0.02</v>
       </c>
       <c r="Q63" s="5" t="n">
-        <v>8.44</v>
+        <v>2.22</v>
       </c>
       <c r="R63" s="7" t="n">
-        <v>8.6</v>
+        <v>1.6</v>
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>MCCB 250 A (250 AF) + DOL, NEMA size 5</t>
+          <t>MCCB 15 A (125 AF) + DOL, NEMA size 0</t>
         </is>
       </c>
       <c r="T63" s="4" t="inlineStr"/>
@@ -5127,32 +5127,32 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>CBL-A-101-M1</t>
+          <t>CBL-K-101A</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>VFD-A-101-M1</t>
+          <t>MCC-101A</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>A-101-M1</t>
+          <t>K-101A</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>Atm. overhead condenser - fan motor 1/6 (VFD)</t>
+          <t>H-101 forced-draft fan A</t>
         </is>
       </c>
       <c r="F64" s="5" t="n">
         <v>0.48</v>
       </c>
-      <c r="G64" s="7" t="n">
-        <v>82.3</v>
+      <c r="G64" s="6" t="n">
+        <v>134.6</v>
       </c>
       <c r="H64" s="6" t="n">
-        <v>140</v>
+        <v>100</v>
       </c>
       <c r="I64" s="4" t="inlineStr">
         <is>
@@ -5161,30 +5161,36 @@
       </c>
       <c r="J64" s="4" t="inlineStr">
         <is>
-          <t>3C x 35 + 3E x 11.6667 mm2 Cu/XLPE/CWS/SWA/PVC 0.6/1 kV, symmetrical VFD cable</t>
+          <t>3C x 70 + E35 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
         </is>
       </c>
       <c r="K64" s="4" t="n">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="L64" s="4" t="n">
         <v>1</v>
       </c>
       <c r="M64" s="6" t="n">
-        <v>115</v>
+        <v>179.1</v>
       </c>
       <c r="N64" s="5" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="O64" s="4" t="n"/>
-      <c r="P64" s="4" t="n"/>
-      <c r="Q64" s="4" t="n"/>
+        <v>1.63</v>
+      </c>
+      <c r="O64" s="5" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="P64" s="5" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q64" s="5" t="n">
+        <v>8.130000000000001</v>
+      </c>
       <c r="R64" s="7" t="n">
-        <v>4.9</v>
+        <v>8.6</v>
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>MCCB 100 A (125 AF) + VFD (6-pulse + harmonic filter)</t>
+          <t>MCCB 250 A (250 AF) + DOL, NEMA size 5</t>
         </is>
       </c>
       <c r="T64" s="4" t="inlineStr"/>
@@ -5197,32 +5203,32 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>CBL-A-101-M2</t>
+          <t>CBL-K-101B</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>VFD-A-101-M2</t>
+          <t>MCC-101B</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>A-101-M2</t>
+          <t>K-101B</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>Atm. overhead condenser - fan motor 2/6 (VFD)</t>
+          <t>H-101 forced-draft fan B</t>
         </is>
       </c>
       <c r="F65" s="5" t="n">
         <v>0.48</v>
       </c>
-      <c r="G65" s="7" t="n">
-        <v>82.3</v>
+      <c r="G65" s="6" t="n">
+        <v>134.6</v>
       </c>
       <c r="H65" s="6" t="n">
-        <v>140</v>
+        <v>105</v>
       </c>
       <c r="I65" s="4" t="inlineStr">
         <is>
@@ -5231,30 +5237,36 @@
       </c>
       <c r="J65" s="4" t="inlineStr">
         <is>
-          <t>3C x 35 + 3E x 11.6667 mm2 Cu/XLPE/CWS/SWA/PVC 0.6/1 kV, symmetrical VFD cable</t>
+          <t>3C x 70 + E35 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
         </is>
       </c>
       <c r="K65" s="4" t="n">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="L65" s="4" t="n">
         <v>1</v>
       </c>
       <c r="M65" s="6" t="n">
-        <v>115</v>
+        <v>179.1</v>
       </c>
       <c r="N65" s="5" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="O65" s="4" t="n"/>
-      <c r="P65" s="4" t="n"/>
-      <c r="Q65" s="4" t="n"/>
+        <v>1.71</v>
+      </c>
+      <c r="O65" s="5" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="P65" s="5" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q65" s="5" t="n">
+        <v>8.44</v>
+      </c>
       <c r="R65" s="7" t="n">
-        <v>4.9</v>
+        <v>8.6</v>
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>MCCB 100 A (125 AF) + VFD (6-pulse + harmonic filter)</t>
+          <t>MCCB 250 A (250 AF) + DOL, NEMA size 5</t>
         </is>
       </c>
       <c r="T65" s="4" t="inlineStr"/>
@@ -5267,22 +5279,22 @@
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>CBL-A-101-M3</t>
+          <t>CBL-A-101-M1</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>VFD-A-101-M3</t>
+          <t>VFD-A-101-M1</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>A-101-M3</t>
+          <t>A-101-M1</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>Atm. overhead condenser - fan motor 3/6 (VFD)</t>
+          <t>Atm. overhead condenser - fan motor 1/6 (VFD)</t>
         </is>
       </c>
       <c r="F66" s="5" t="n">
@@ -5292,7 +5304,7 @@
         <v>82.3</v>
       </c>
       <c r="H66" s="6" t="n">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="I66" s="4" t="inlineStr">
         <is>
@@ -5314,7 +5326,7 @@
         <v>115</v>
       </c>
       <c r="N66" s="5" t="n">
-        <v>2.67</v>
+        <v>2.58</v>
       </c>
       <c r="O66" s="4" t="n"/>
       <c r="P66" s="4" t="n"/>
@@ -5337,22 +5349,22 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>CBL-A-101-M4</t>
+          <t>CBL-A-101-M2</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>VFD-A-101-M4</t>
+          <t>VFD-A-101-M2</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>A-101-M4</t>
+          <t>A-101-M2</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>Atm. overhead condenser - fan motor 4/6 (VFD)</t>
+          <t>Atm. overhead condenser - fan motor 2/6 (VFD)</t>
         </is>
       </c>
       <c r="F67" s="5" t="n">
@@ -5362,7 +5374,7 @@
         <v>82.3</v>
       </c>
       <c r="H67" s="6" t="n">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="I67" s="4" t="inlineStr">
         <is>
@@ -5384,7 +5396,7 @@
         <v>115</v>
       </c>
       <c r="N67" s="5" t="n">
-        <v>2.67</v>
+        <v>2.58</v>
       </c>
       <c r="O67" s="4" t="n"/>
       <c r="P67" s="4" t="n"/>
@@ -5407,22 +5419,22 @@
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>CBL-A-101-M5</t>
+          <t>CBL-A-101-M3</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>VFD-A-101-M5</t>
+          <t>VFD-A-101-M3</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>A-101-M5</t>
+          <t>A-101-M3</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>Atm. overhead condenser - fan motor 5/6 (VFD)</t>
+          <t>Atm. overhead condenser - fan motor 3/6 (VFD)</t>
         </is>
       </c>
       <c r="F68" s="5" t="n">
@@ -5432,7 +5444,7 @@
         <v>82.3</v>
       </c>
       <c r="H68" s="6" t="n">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="I68" s="4" t="inlineStr">
         <is>
@@ -5454,7 +5466,7 @@
         <v>115</v>
       </c>
       <c r="N68" s="5" t="n">
-        <v>2.76</v>
+        <v>2.67</v>
       </c>
       <c r="O68" s="4" t="n"/>
       <c r="P68" s="4" t="n"/>
@@ -5477,22 +5489,22 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>CBL-A-101-M6</t>
+          <t>CBL-A-101-M4</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>VFD-A-101-M6</t>
+          <t>VFD-A-101-M4</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>A-101-M6</t>
+          <t>A-101-M4</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>Atm. overhead condenser - fan motor 6/6 (VFD)</t>
+          <t>Atm. overhead condenser - fan motor 4/6 (VFD)</t>
         </is>
       </c>
       <c r="F69" s="5" t="n">
@@ -5502,7 +5514,7 @@
         <v>82.3</v>
       </c>
       <c r="H69" s="6" t="n">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="I69" s="4" t="inlineStr">
         <is>
@@ -5524,7 +5536,7 @@
         <v>115</v>
       </c>
       <c r="N69" s="5" t="n">
-        <v>2.76</v>
+        <v>2.67</v>
       </c>
       <c r="O69" s="4" t="n"/>
       <c r="P69" s="4" t="n"/>
@@ -5547,32 +5559,32 @@
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>CBL-A-103-M1</t>
+          <t>CBL-A-101-M5</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>MCC-101A</t>
+          <t>VFD-A-101-M5</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>A-103-M1</t>
+          <t>A-101-M5</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>Kero cooler - fan motor 1/2</t>
+          <t>Atm. overhead condenser - fan motor 5/6 (VFD)</t>
         </is>
       </c>
       <c r="F70" s="5" t="n">
         <v>0.48</v>
       </c>
       <c r="G70" s="7" t="n">
-        <v>17.1</v>
+        <v>82.3</v>
       </c>
       <c r="H70" s="6" t="n">
-        <v>175</v>
+        <v>150</v>
       </c>
       <c r="I70" s="4" t="inlineStr">
         <is>
@@ -5581,36 +5593,30 @@
       </c>
       <c r="J70" s="4" t="inlineStr">
         <is>
-          <t>3C x 6 + E6 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
+          <t>3C x 35 + 3E x 11.6667 mm2 Cu/XLPE/CWS/SWA/PVC 0.6/1 kV, symmetrical VFD cable</t>
         </is>
       </c>
       <c r="K70" s="4" t="n">
-        <v>6</v>
+        <v>35</v>
       </c>
       <c r="L70" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M70" s="7" t="n">
-        <v>39.3</v>
+      <c r="M70" s="6" t="n">
+        <v>115</v>
       </c>
       <c r="N70" s="5" t="n">
-        <v>3.67</v>
-      </c>
-      <c r="O70" s="5" t="n">
-        <v>10.25</v>
-      </c>
-      <c r="P70" s="5" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="Q70" s="5" t="n">
-        <v>10.51</v>
-      </c>
+        <v>2.76</v>
+      </c>
+      <c r="O70" s="4" t="n"/>
+      <c r="P70" s="4" t="n"/>
+      <c r="Q70" s="4" t="n"/>
       <c r="R70" s="7" t="n">
-        <v>1.6</v>
+        <v>4.9</v>
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>MCCB 30 A (125 AF) + DOL, NEMA size 1</t>
+          <t>MCCB 100 A (125 AF) + VFD (6-pulse + harmonic filter)</t>
         </is>
       </c>
       <c r="T70" s="4" t="inlineStr"/>
@@ -5623,32 +5629,32 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>CBL-A-103-M2</t>
+          <t>CBL-A-101-M6</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>MCC-101B</t>
+          <t>VFD-A-101-M6</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>A-103-M2</t>
+          <t>A-101-M6</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>Kero cooler - fan motor 2/2</t>
+          <t>Atm. overhead condenser - fan motor 6/6 (VFD)</t>
         </is>
       </c>
       <c r="F71" s="5" t="n">
         <v>0.48</v>
       </c>
       <c r="G71" s="7" t="n">
-        <v>17.1</v>
+        <v>82.3</v>
       </c>
       <c r="H71" s="6" t="n">
-        <v>175</v>
+        <v>150</v>
       </c>
       <c r="I71" s="4" t="inlineStr">
         <is>
@@ -5657,36 +5663,30 @@
       </c>
       <c r="J71" s="4" t="inlineStr">
         <is>
-          <t>3C x 6 + E6 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
+          <t>3C x 35 + 3E x 11.6667 mm2 Cu/XLPE/CWS/SWA/PVC 0.6/1 kV, symmetrical VFD cable</t>
         </is>
       </c>
       <c r="K71" s="4" t="n">
-        <v>6</v>
+        <v>35</v>
       </c>
       <c r="L71" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M71" s="7" t="n">
-        <v>39.3</v>
+      <c r="M71" s="6" t="n">
+        <v>115</v>
       </c>
       <c r="N71" s="5" t="n">
-        <v>3.67</v>
-      </c>
-      <c r="O71" s="5" t="n">
-        <v>10.25</v>
-      </c>
-      <c r="P71" s="5" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="Q71" s="5" t="n">
-        <v>10.51</v>
-      </c>
+        <v>2.76</v>
+      </c>
+      <c r="O71" s="4" t="n"/>
+      <c r="P71" s="4" t="n"/>
+      <c r="Q71" s="4" t="n"/>
       <c r="R71" s="7" t="n">
-        <v>1.6</v>
+        <v>4.9</v>
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>MCCB 30 A (125 AF) + DOL, NEMA size 1</t>
+          <t>MCCB 100 A (125 AF) + VFD (6-pulse + harmonic filter)</t>
         </is>
       </c>
       <c r="T71" s="4" t="inlineStr"/>
@@ -5699,7 +5699,7 @@
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>CBL-A-104-M1</t>
+          <t>CBL-A-103-M1</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
@@ -5709,22 +5709,22 @@
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>A-104-M1</t>
+          <t>A-103-M1</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>Diesel cooler - fan motor 1/2</t>
+          <t>Kero cooler - fan motor 1/2</t>
         </is>
       </c>
       <c r="F72" s="5" t="n">
         <v>0.48</v>
       </c>
       <c r="G72" s="7" t="n">
-        <v>28.8</v>
+        <v>17.1</v>
       </c>
       <c r="H72" s="6" t="n">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="I72" s="4" t="inlineStr">
         <is>
@@ -5733,36 +5733,36 @@
       </c>
       <c r="J72" s="4" t="inlineStr">
         <is>
-          <t>3C x 10 + E10 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
+          <t>3C x 6 + E6 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
         </is>
       </c>
       <c r="K72" s="4" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L72" s="4" t="n">
         <v>1</v>
       </c>
       <c r="M72" s="7" t="n">
-        <v>54.6</v>
+        <v>39.3</v>
       </c>
       <c r="N72" s="5" t="n">
-        <v>3.8</v>
+        <v>3.67</v>
       </c>
       <c r="O72" s="5" t="n">
-        <v>10.92</v>
+        <v>10.25</v>
       </c>
       <c r="P72" s="5" t="n">
-        <v>0.44</v>
+        <v>0.26</v>
       </c>
       <c r="Q72" s="5" t="n">
-        <v>11.37</v>
+        <v>10.51</v>
       </c>
       <c r="R72" s="7" t="n">
-        <v>2.7</v>
+        <v>1.6</v>
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>MCCB 60 A (125 AF) + DOL, NEMA size 2</t>
+          <t>MCCB 30 A (125 AF) + DOL, NEMA size 1</t>
         </is>
       </c>
       <c r="T72" s="4" t="inlineStr"/>
@@ -5775,7 +5775,7 @@
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>CBL-A-104-M2</t>
+          <t>CBL-A-103-M2</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
@@ -5785,22 +5785,22 @@
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>A-104-M2</t>
+          <t>A-103-M2</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>Diesel cooler - fan motor 2/2</t>
+          <t>Kero cooler - fan motor 2/2</t>
         </is>
       </c>
       <c r="F73" s="5" t="n">
         <v>0.48</v>
       </c>
       <c r="G73" s="7" t="n">
-        <v>28.8</v>
+        <v>17.1</v>
       </c>
       <c r="H73" s="6" t="n">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="I73" s="4" t="inlineStr">
         <is>
@@ -5809,36 +5809,36 @@
       </c>
       <c r="J73" s="4" t="inlineStr">
         <is>
-          <t>3C x 10 + E10 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
+          <t>3C x 6 + E6 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
         </is>
       </c>
       <c r="K73" s="4" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L73" s="4" t="n">
         <v>1</v>
       </c>
       <c r="M73" s="7" t="n">
-        <v>54.6</v>
+        <v>39.3</v>
       </c>
       <c r="N73" s="5" t="n">
-        <v>3.8</v>
+        <v>3.67</v>
       </c>
       <c r="O73" s="5" t="n">
-        <v>10.92</v>
+        <v>10.25</v>
       </c>
       <c r="P73" s="5" t="n">
-        <v>0.44</v>
+        <v>0.26</v>
       </c>
       <c r="Q73" s="5" t="n">
-        <v>11.37</v>
+        <v>10.51</v>
       </c>
       <c r="R73" s="7" t="n">
-        <v>2.7</v>
+        <v>1.6</v>
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>MCCB 60 A (125 AF) + DOL, NEMA size 2</t>
+          <t>MCCB 30 A (125 AF) + DOL, NEMA size 1</t>
         </is>
       </c>
       <c r="T73" s="4" t="inlineStr"/>
@@ -5851,7 +5851,7 @@
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>CBL-A-105-M1</t>
+          <t>CBL-A-104-M1</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
@@ -5861,22 +5861,22 @@
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>A-105-M1</t>
+          <t>A-104-M1</t>
         </is>
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>Ago cooler - fan motor 1/2</t>
+          <t>Diesel cooler - fan motor 1/2</t>
         </is>
       </c>
       <c r="F74" s="5" t="n">
         <v>0.48</v>
       </c>
       <c r="G74" s="7" t="n">
-        <v>46.7</v>
+        <v>28.8</v>
       </c>
       <c r="H74" s="6" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="I74" s="4" t="inlineStr">
         <is>
@@ -5885,36 +5885,36 @@
       </c>
       <c r="J74" s="4" t="inlineStr">
         <is>
-          <t>3C x 16 + E16 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
+          <t>3C x 10 + E10 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
         </is>
       </c>
       <c r="K74" s="4" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="L74" s="4" t="n">
         <v>1</v>
       </c>
       <c r="M74" s="7" t="n">
-        <v>72.8</v>
+        <v>54.6</v>
       </c>
       <c r="N74" s="5" t="n">
-        <v>4.15</v>
+        <v>3.8</v>
       </c>
       <c r="O74" s="5" t="n">
-        <v>12.37</v>
+        <v>10.92</v>
       </c>
       <c r="P74" s="5" t="n">
-        <v>0.71</v>
+        <v>0.44</v>
       </c>
       <c r="Q74" s="5" t="n">
-        <v>13.08</v>
+        <v>11.37</v>
       </c>
       <c r="R74" s="7" t="n">
-        <v>4.9</v>
+        <v>2.7</v>
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>MCCB 90 A (125 AF) + DOL, NEMA size 3</t>
+          <t>MCCB 60 A (125 AF) + DOL, NEMA size 2</t>
         </is>
       </c>
       <c r="T74" s="4" t="inlineStr"/>
@@ -5927,7 +5927,7 @@
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>CBL-A-105-M2</t>
+          <t>CBL-A-104-M2</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
@@ -5937,22 +5937,22 @@
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>A-105-M2</t>
+          <t>A-104-M2</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>Ago cooler - fan motor 2/2</t>
+          <t>Diesel cooler - fan motor 2/2</t>
         </is>
       </c>
       <c r="F75" s="5" t="n">
         <v>0.48</v>
       </c>
       <c r="G75" s="7" t="n">
-        <v>46.7</v>
+        <v>28.8</v>
       </c>
       <c r="H75" s="6" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="I75" s="4" t="inlineStr">
         <is>
@@ -5961,36 +5961,36 @@
       </c>
       <c r="J75" s="4" t="inlineStr">
         <is>
-          <t>3C x 16 + E16 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
+          <t>3C x 10 + E10 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
         </is>
       </c>
       <c r="K75" s="4" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="L75" s="4" t="n">
         <v>1</v>
       </c>
       <c r="M75" s="7" t="n">
-        <v>72.8</v>
+        <v>54.6</v>
       </c>
       <c r="N75" s="5" t="n">
-        <v>4.15</v>
+        <v>3.8</v>
       </c>
       <c r="O75" s="5" t="n">
-        <v>12.37</v>
+        <v>10.92</v>
       </c>
       <c r="P75" s="5" t="n">
-        <v>0.71</v>
+        <v>0.44</v>
       </c>
       <c r="Q75" s="5" t="n">
-        <v>13.08</v>
+        <v>11.37</v>
       </c>
       <c r="R75" s="7" t="n">
-        <v>4.9</v>
+        <v>2.7</v>
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>MCCB 90 A (125 AF) + DOL, NEMA size 3</t>
+          <t>MCCB 60 A (125 AF) + DOL, NEMA size 2</t>
         </is>
       </c>
       <c r="T75" s="4" t="inlineStr"/>
@@ -6003,7 +6003,7 @@
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>CBL-A-106-M1</t>
+          <t>CBL-A-105-M1</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
@@ -6013,22 +6013,22 @@
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>A-106-M1</t>
+          <t>A-105-M1</t>
         </is>
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>Stabiliser overhead condenser - fan motor 1/2</t>
+          <t>Ago cooler - fan motor 1/2</t>
         </is>
       </c>
       <c r="F76" s="5" t="n">
         <v>0.48</v>
       </c>
       <c r="G76" s="7" t="n">
-        <v>17.1</v>
+        <v>46.7</v>
       </c>
       <c r="H76" s="6" t="n">
-        <v>120</v>
+        <v>190</v>
       </c>
       <c r="I76" s="4" t="inlineStr">
         <is>
@@ -6037,36 +6037,36 @@
       </c>
       <c r="J76" s="4" t="inlineStr">
         <is>
-          <t>3C x 4 + E4 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
+          <t>3C x 16 + E16 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
         </is>
       </c>
       <c r="K76" s="4" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="L76" s="4" t="n">
         <v>1</v>
       </c>
       <c r="M76" s="7" t="n">
-        <v>30.6</v>
+        <v>72.8</v>
       </c>
       <c r="N76" s="5" t="n">
-        <v>3.75</v>
+        <v>4.15</v>
       </c>
       <c r="O76" s="5" t="n">
-        <v>10.33</v>
+        <v>12.37</v>
       </c>
       <c r="P76" s="5" t="n">
-        <v>0.26</v>
+        <v>0.71</v>
       </c>
       <c r="Q76" s="5" t="n">
-        <v>10.59</v>
+        <v>13.08</v>
       </c>
       <c r="R76" s="7" t="n">
-        <v>1.6</v>
+        <v>4.9</v>
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>MCCB 30 A (125 AF) + DOL, NEMA size 1</t>
+          <t>MCCB 90 A (125 AF) + DOL, NEMA size 3</t>
         </is>
       </c>
       <c r="T76" s="4" t="inlineStr"/>
@@ -6079,7 +6079,7 @@
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>CBL-A-106-M2</t>
+          <t>CBL-A-105-M2</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
@@ -6089,22 +6089,22 @@
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>A-106-M2</t>
+          <t>A-105-M2</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>Stabiliser overhead condenser - fan motor 2/2</t>
+          <t>Ago cooler - fan motor 2/2</t>
         </is>
       </c>
       <c r="F77" s="5" t="n">
         <v>0.48</v>
       </c>
       <c r="G77" s="7" t="n">
-        <v>17.1</v>
+        <v>46.7</v>
       </c>
       <c r="H77" s="6" t="n">
-        <v>120</v>
+        <v>190</v>
       </c>
       <c r="I77" s="4" t="inlineStr">
         <is>
@@ -6113,36 +6113,36 @@
       </c>
       <c r="J77" s="4" t="inlineStr">
         <is>
-          <t>3C x 4 + E4 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
+          <t>3C x 16 + E16 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
         </is>
       </c>
       <c r="K77" s="4" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="L77" s="4" t="n">
         <v>1</v>
       </c>
       <c r="M77" s="7" t="n">
-        <v>30.6</v>
+        <v>72.8</v>
       </c>
       <c r="N77" s="5" t="n">
-        <v>3.75</v>
+        <v>4.15</v>
       </c>
       <c r="O77" s="5" t="n">
-        <v>10.33</v>
+        <v>12.37</v>
       </c>
       <c r="P77" s="5" t="n">
-        <v>0.26</v>
+        <v>0.71</v>
       </c>
       <c r="Q77" s="5" t="n">
-        <v>10.59</v>
+        <v>13.08</v>
       </c>
       <c r="R77" s="7" t="n">
-        <v>1.6</v>
+        <v>4.9</v>
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>MCCB 30 A (125 AF) + DOL, NEMA size 1</t>
+          <t>MCCB 90 A (125 AF) + DOL, NEMA size 3</t>
         </is>
       </c>
       <c r="T77" s="4" t="inlineStr"/>
@@ -6155,7 +6155,7 @@
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>CBL-A-107-M1</t>
+          <t>CBL-A-106-M1</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
@@ -6165,22 +6165,22 @@
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>A-107-M1</t>
+          <t>A-106-M1</t>
         </is>
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>Splitter overhead condenser - fan motor 1/4</t>
+          <t>Stabiliser overhead condenser - fan motor 1/2</t>
         </is>
       </c>
       <c r="F78" s="5" t="n">
         <v>0.48</v>
       </c>
       <c r="G78" s="7" t="n">
-        <v>46.7</v>
+        <v>17.1</v>
       </c>
       <c r="H78" s="6" t="n">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="I78" s="4" t="inlineStr">
         <is>
@@ -6189,36 +6189,36 @@
       </c>
       <c r="J78" s="4" t="inlineStr">
         <is>
-          <t>3C x 16 + E16 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
+          <t>3C x 4 + E4 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
         </is>
       </c>
       <c r="K78" s="4" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="L78" s="4" t="n">
         <v>1</v>
       </c>
       <c r="M78" s="7" t="n">
-        <v>72.8</v>
+        <v>30.6</v>
       </c>
       <c r="N78" s="5" t="n">
-        <v>2.51</v>
+        <v>3.75</v>
       </c>
       <c r="O78" s="5" t="n">
-        <v>7.48</v>
+        <v>10.33</v>
       </c>
       <c r="P78" s="5" t="n">
-        <v>0.71</v>
+        <v>0.26</v>
       </c>
       <c r="Q78" s="5" t="n">
-        <v>8.199999999999999</v>
+        <v>10.59</v>
       </c>
       <c r="R78" s="7" t="n">
-        <v>4.9</v>
+        <v>1.6</v>
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>MCCB 90 A (125 AF) + DOL, NEMA size 3</t>
+          <t>MCCB 30 A (125 AF) + DOL, NEMA size 1</t>
         </is>
       </c>
       <c r="T78" s="4" t="inlineStr"/>
@@ -6231,7 +6231,7 @@
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>CBL-A-107-M2</t>
+          <t>CBL-A-106-M2</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
@@ -6241,22 +6241,22 @@
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>A-107-M2</t>
+          <t>A-106-M2</t>
         </is>
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>Splitter overhead condenser - fan motor 2/4</t>
+          <t>Stabiliser overhead condenser - fan motor 2/2</t>
         </is>
       </c>
       <c r="F79" s="5" t="n">
         <v>0.48</v>
       </c>
       <c r="G79" s="7" t="n">
-        <v>46.7</v>
+        <v>17.1</v>
       </c>
       <c r="H79" s="6" t="n">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="I79" s="4" t="inlineStr">
         <is>
@@ -6265,36 +6265,36 @@
       </c>
       <c r="J79" s="4" t="inlineStr">
         <is>
-          <t>3C x 16 + E16 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
+          <t>3C x 4 + E4 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
         </is>
       </c>
       <c r="K79" s="4" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="L79" s="4" t="n">
         <v>1</v>
       </c>
       <c r="M79" s="7" t="n">
-        <v>72.8</v>
+        <v>30.6</v>
       </c>
       <c r="N79" s="5" t="n">
-        <v>2.51</v>
+        <v>3.75</v>
       </c>
       <c r="O79" s="5" t="n">
-        <v>7.48</v>
+        <v>10.33</v>
       </c>
       <c r="P79" s="5" t="n">
-        <v>0.71</v>
+        <v>0.26</v>
       </c>
       <c r="Q79" s="5" t="n">
-        <v>8.199999999999999</v>
+        <v>10.59</v>
       </c>
       <c r="R79" s="7" t="n">
-        <v>4.9</v>
+        <v>1.6</v>
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>MCCB 90 A (125 AF) + DOL, NEMA size 3</t>
+          <t>MCCB 30 A (125 AF) + DOL, NEMA size 1</t>
         </is>
       </c>
       <c r="T79" s="4" t="inlineStr"/>
@@ -6307,7 +6307,7 @@
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>CBL-A-107-M3</t>
+          <t>CBL-A-107-M1</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
@@ -6317,12 +6317,12 @@
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>A-107-M3</t>
+          <t>A-107-M1</t>
         </is>
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>Splitter overhead condenser - fan motor 3/4</t>
+          <t>Splitter overhead condenser - fan motor 1/4</t>
         </is>
       </c>
       <c r="F80" s="5" t="n">
@@ -6332,7 +6332,7 @@
         <v>46.7</v>
       </c>
       <c r="H80" s="6" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="I80" s="4" t="inlineStr">
         <is>
@@ -6354,16 +6354,16 @@
         <v>72.8</v>
       </c>
       <c r="N80" s="5" t="n">
-        <v>2.62</v>
+        <v>2.4</v>
       </c>
       <c r="O80" s="5" t="n">
-        <v>7.81</v>
+        <v>7.16</v>
       </c>
       <c r="P80" s="5" t="n">
         <v>0.71</v>
       </c>
       <c r="Q80" s="5" t="n">
-        <v>8.52</v>
+        <v>7.87</v>
       </c>
       <c r="R80" s="7" t="n">
         <v>4.9</v>
@@ -6383,7 +6383,7 @@
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>CBL-A-107-M4</t>
+          <t>CBL-A-107-M2</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
@@ -6393,12 +6393,12 @@
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>A-107-M4</t>
+          <t>A-107-M2</t>
         </is>
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>Splitter overhead condenser - fan motor 4/4</t>
+          <t>Splitter overhead condenser - fan motor 2/4</t>
         </is>
       </c>
       <c r="F81" s="5" t="n">
@@ -6408,7 +6408,7 @@
         <v>46.7</v>
       </c>
       <c r="H81" s="6" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="I81" s="4" t="inlineStr">
         <is>
@@ -6430,16 +6430,16 @@
         <v>72.8</v>
       </c>
       <c r="N81" s="5" t="n">
-        <v>2.62</v>
+        <v>2.4</v>
       </c>
       <c r="O81" s="5" t="n">
-        <v>7.81</v>
+        <v>7.16</v>
       </c>
       <c r="P81" s="5" t="n">
         <v>0.71</v>
       </c>
       <c r="Q81" s="5" t="n">
-        <v>8.52</v>
+        <v>7.87</v>
       </c>
       <c r="R81" s="7" t="n">
         <v>4.9</v>
@@ -6459,7 +6459,7 @@
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>CBL-A-108-M1</t>
+          <t>CBL-A-107-M3</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
@@ -6469,12 +6469,12 @@
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>A-108-M1</t>
+          <t>A-107-M3</t>
         </is>
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>Heavy naphtha product cooler - fan motor 1/2</t>
+          <t>Splitter overhead condenser - fan motor 3/4</t>
         </is>
       </c>
       <c r="F82" s="5" t="n">
@@ -6484,7 +6484,7 @@
         <v>46.7</v>
       </c>
       <c r="H82" s="6" t="n">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="I82" s="4" t="inlineStr">
         <is>
@@ -6506,16 +6506,16 @@
         <v>72.8</v>
       </c>
       <c r="N82" s="5" t="n">
-        <v>2.84</v>
+        <v>2.51</v>
       </c>
       <c r="O82" s="5" t="n">
-        <v>8.460000000000001</v>
+        <v>7.48</v>
       </c>
       <c r="P82" s="5" t="n">
         <v>0.71</v>
       </c>
       <c r="Q82" s="5" t="n">
-        <v>9.18</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="R82" s="7" t="n">
         <v>4.9</v>
@@ -6535,7 +6535,7 @@
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>CBL-A-108-M2</t>
+          <t>CBL-A-107-M4</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
@@ -6545,12 +6545,12 @@
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>A-108-M2</t>
+          <t>A-107-M4</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>Heavy naphtha product cooler - fan motor 2/2</t>
+          <t>Splitter overhead condenser - fan motor 4/4</t>
         </is>
       </c>
       <c r="F83" s="5" t="n">
@@ -6560,7 +6560,7 @@
         <v>46.7</v>
       </c>
       <c r="H83" s="6" t="n">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="I83" s="4" t="inlineStr">
         <is>
@@ -6582,16 +6582,16 @@
         <v>72.8</v>
       </c>
       <c r="N83" s="5" t="n">
-        <v>2.84</v>
+        <v>2.51</v>
       </c>
       <c r="O83" s="5" t="n">
-        <v>8.460000000000001</v>
+        <v>7.48</v>
       </c>
       <c r="P83" s="5" t="n">
         <v>0.71</v>
       </c>
       <c r="Q83" s="5" t="n">
-        <v>9.18</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="R83" s="7" t="n">
         <v>4.9</v>
@@ -6611,7 +6611,7 @@
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>CBL-A-201-M1</t>
+          <t>CBL-A-108-M1</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
@@ -6621,22 +6621,22 @@
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>A-201-M1</t>
+          <t>A-108-M1</t>
         </is>
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>Lvgo cooler - fan motor 1/2</t>
+          <t>Heavy naphtha product cooler - fan motor 1/2</t>
         </is>
       </c>
       <c r="F84" s="5" t="n">
         <v>0.48</v>
       </c>
       <c r="G84" s="7" t="n">
-        <v>23.3</v>
+        <v>46.7</v>
       </c>
       <c r="H84" s="6" t="n">
-        <v>225</v>
+        <v>130</v>
       </c>
       <c r="I84" s="4" t="inlineStr">
         <is>
@@ -6645,36 +6645,36 @@
       </c>
       <c r="J84" s="4" t="inlineStr">
         <is>
-          <t>3C x 10 + E10 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
+          <t>3C x 16 + E16 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
         </is>
       </c>
       <c r="K84" s="4" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="L84" s="4" t="n">
         <v>1</v>
       </c>
       <c r="M84" s="7" t="n">
-        <v>54.6</v>
+        <v>72.8</v>
       </c>
       <c r="N84" s="5" t="n">
-        <v>3.86</v>
+        <v>2.84</v>
       </c>
       <c r="O84" s="5" t="n">
-        <v>11.07</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="P84" s="5" t="n">
-        <v>0.36</v>
+        <v>0.71</v>
       </c>
       <c r="Q84" s="5" t="n">
-        <v>11.43</v>
+        <v>9.18</v>
       </c>
       <c r="R84" s="7" t="n">
-        <v>2.7</v>
+        <v>4.9</v>
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>MCCB 45 A (125 AF) + DOL, NEMA size 2</t>
+          <t>MCCB 90 A (125 AF) + DOL, NEMA size 3</t>
         </is>
       </c>
       <c r="T84" s="4" t="inlineStr"/>
@@ -6687,7 +6687,7 @@
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>CBL-A-201-M2</t>
+          <t>CBL-A-108-M2</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
@@ -6697,22 +6697,22 @@
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>A-201-M2</t>
+          <t>A-108-M2</t>
         </is>
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>Lvgo cooler - fan motor 2/2</t>
+          <t>Heavy naphtha product cooler - fan motor 2/2</t>
         </is>
       </c>
       <c r="F85" s="5" t="n">
         <v>0.48</v>
       </c>
       <c r="G85" s="7" t="n">
-        <v>23.3</v>
+        <v>46.7</v>
       </c>
       <c r="H85" s="6" t="n">
-        <v>225</v>
+        <v>130</v>
       </c>
       <c r="I85" s="4" t="inlineStr">
         <is>
@@ -6721,36 +6721,36 @@
       </c>
       <c r="J85" s="4" t="inlineStr">
         <is>
-          <t>3C x 10 + E10 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
+          <t>3C x 16 + E16 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
         </is>
       </c>
       <c r="K85" s="4" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="L85" s="4" t="n">
         <v>1</v>
       </c>
       <c r="M85" s="7" t="n">
-        <v>54.6</v>
+        <v>72.8</v>
       </c>
       <c r="N85" s="5" t="n">
-        <v>3.86</v>
+        <v>2.84</v>
       </c>
       <c r="O85" s="5" t="n">
-        <v>11.07</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="P85" s="5" t="n">
-        <v>0.36</v>
+        <v>0.71</v>
       </c>
       <c r="Q85" s="5" t="n">
-        <v>11.43</v>
+        <v>9.18</v>
       </c>
       <c r="R85" s="7" t="n">
-        <v>2.7</v>
+        <v>4.9</v>
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>MCCB 45 A (125 AF) + DOL, NEMA size 2</t>
+          <t>MCCB 90 A (125 AF) + DOL, NEMA size 3</t>
         </is>
       </c>
       <c r="T85" s="4" t="inlineStr"/>
@@ -6763,7 +6763,7 @@
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>CBL-A-202-M1</t>
+          <t>CBL-A-201-M1</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
@@ -6773,22 +6773,22 @@
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>A-202-M1</t>
+          <t>A-201-M1</t>
         </is>
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>Hvgo Product cooler - fan motor 1/2</t>
+          <t>Lvgo cooler - fan motor 1/2</t>
         </is>
       </c>
       <c r="F86" s="5" t="n">
         <v>0.48</v>
       </c>
       <c r="G86" s="7" t="n">
-        <v>55.3</v>
+        <v>23.3</v>
       </c>
       <c r="H86" s="6" t="n">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="I86" s="4" t="inlineStr">
         <is>
@@ -6797,36 +6797,36 @@
       </c>
       <c r="J86" s="4" t="inlineStr">
         <is>
-          <t>3C x 25 + E16 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
+          <t>3C x 10 + E10 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
         </is>
       </c>
       <c r="K86" s="4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="L86" s="4" t="n">
         <v>1</v>
       </c>
       <c r="M86" s="7" t="n">
-        <v>92.5</v>
+        <v>54.6</v>
       </c>
       <c r="N86" s="5" t="n">
-        <v>3.88</v>
+        <v>3.86</v>
       </c>
       <c r="O86" s="5" t="n">
-        <v>12.1</v>
+        <v>11.07</v>
       </c>
       <c r="P86" s="5" t="n">
-        <v>0.85</v>
+        <v>0.36</v>
       </c>
       <c r="Q86" s="5" t="n">
-        <v>12.95</v>
+        <v>11.43</v>
       </c>
       <c r="R86" s="7" t="n">
-        <v>4.9</v>
+        <v>2.7</v>
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>MCCB 100 A (125 AF) + DOL, NEMA size 3</t>
+          <t>MCCB 45 A (125 AF) + DOL, NEMA size 2</t>
         </is>
       </c>
       <c r="T86" s="4" t="inlineStr"/>
@@ -6839,7 +6839,7 @@
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>CBL-A-202-M2</t>
+          <t>CBL-A-201-M2</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
@@ -6849,22 +6849,22 @@
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>A-202-M2</t>
+          <t>A-201-M2</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>Hvgo Product cooler - fan motor 2/2</t>
+          <t>Lvgo cooler - fan motor 2/2</t>
         </is>
       </c>
       <c r="F87" s="5" t="n">
         <v>0.48</v>
       </c>
       <c r="G87" s="7" t="n">
-        <v>55.3</v>
+        <v>23.3</v>
       </c>
       <c r="H87" s="6" t="n">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="I87" s="4" t="inlineStr">
         <is>
@@ -6873,36 +6873,36 @@
       </c>
       <c r="J87" s="4" t="inlineStr">
         <is>
-          <t>3C x 25 + E16 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
+          <t>3C x 10 + E10 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
         </is>
       </c>
       <c r="K87" s="4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="L87" s="4" t="n">
         <v>1</v>
       </c>
       <c r="M87" s="7" t="n">
-        <v>92.5</v>
+        <v>54.6</v>
       </c>
       <c r="N87" s="5" t="n">
-        <v>3.88</v>
+        <v>3.86</v>
       </c>
       <c r="O87" s="5" t="n">
-        <v>12.1</v>
+        <v>11.07</v>
       </c>
       <c r="P87" s="5" t="n">
-        <v>0.85</v>
+        <v>0.36</v>
       </c>
       <c r="Q87" s="5" t="n">
-        <v>12.95</v>
+        <v>11.43</v>
       </c>
       <c r="R87" s="7" t="n">
-        <v>4.9</v>
+        <v>2.7</v>
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>MCCB 100 A (125 AF) + DOL, NEMA size 3</t>
+          <t>MCCB 45 A (125 AF) + DOL, NEMA size 2</t>
         </is>
       </c>
       <c r="T87" s="4" t="inlineStr"/>
@@ -6915,7 +6915,7 @@
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>CBL-X-101-PA</t>
+          <t>CBL-A-202-M1</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
@@ -6925,22 +6925,22 @@
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>X-101-PA</t>
+          <t>A-202-M1</t>
         </is>
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>Demulsifier injection package - metering pump A</t>
+          <t>Hvgo Product cooler - fan motor 1/2</t>
         </is>
       </c>
       <c r="F88" s="5" t="n">
         <v>0.48</v>
       </c>
       <c r="G88" s="7" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H88" s="7" t="n">
-        <v>95</v>
+        <v>55.3</v>
+      </c>
+      <c r="H88" s="6" t="n">
+        <v>230</v>
       </c>
       <c r="I88" s="4" t="inlineStr">
         <is>
@@ -6949,36 +6949,36 @@
       </c>
       <c r="J88" s="4" t="inlineStr">
         <is>
-          <t>3C x 4 + E4 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
+          <t>3C x 25 + E16 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
         </is>
       </c>
       <c r="K88" s="4" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="L88" s="4" t="n">
         <v>1</v>
       </c>
       <c r="M88" s="7" t="n">
-        <v>30.6</v>
+        <v>92.5</v>
       </c>
       <c r="N88" s="5" t="n">
-        <v>0.23</v>
+        <v>3.88</v>
       </c>
       <c r="O88" s="5" t="n">
-        <v>0.71</v>
+        <v>12.1</v>
       </c>
       <c r="P88" s="5" t="n">
-        <v>0.02</v>
+        <v>0.85</v>
       </c>
       <c r="Q88" s="5" t="n">
-        <v>0.73</v>
+        <v>12.95</v>
       </c>
       <c r="R88" s="7" t="n">
-        <v>1.6</v>
+        <v>4.9</v>
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>MCCB 15 A (125 AF) + DOL, NEMA size 0</t>
+          <t>MCCB 100 A (125 AF) + DOL, NEMA size 3</t>
         </is>
       </c>
       <c r="T88" s="4" t="inlineStr"/>
@@ -6991,7 +6991,7 @@
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>CBL-X-101-PB</t>
+          <t>CBL-A-202-M2</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
@@ -7001,22 +7001,22 @@
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>X-101-PB</t>
+          <t>A-202-M2</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>Demulsifier injection package - metering pump B</t>
+          <t>Hvgo Product cooler - fan motor 2/2</t>
         </is>
       </c>
       <c r="F89" s="5" t="n">
         <v>0.48</v>
       </c>
       <c r="G89" s="7" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H89" s="7" t="n">
-        <v>95</v>
+        <v>55.3</v>
+      </c>
+      <c r="H89" s="6" t="n">
+        <v>230</v>
       </c>
       <c r="I89" s="4" t="inlineStr">
         <is>
@@ -7025,36 +7025,36 @@
       </c>
       <c r="J89" s="4" t="inlineStr">
         <is>
-          <t>3C x 4 + E4 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
+          <t>3C x 25 + E16 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
         </is>
       </c>
       <c r="K89" s="4" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="L89" s="4" t="n">
         <v>1</v>
       </c>
       <c r="M89" s="7" t="n">
-        <v>30.6</v>
+        <v>92.5</v>
       </c>
       <c r="N89" s="5" t="n">
-        <v>0.23</v>
+        <v>3.88</v>
       </c>
       <c r="O89" s="5" t="n">
-        <v>0.71</v>
+        <v>12.1</v>
       </c>
       <c r="P89" s="5" t="n">
-        <v>0.02</v>
+        <v>0.85</v>
       </c>
       <c r="Q89" s="5" t="n">
-        <v>0.73</v>
+        <v>12.95</v>
       </c>
       <c r="R89" s="7" t="n">
-        <v>1.6</v>
+        <v>4.9</v>
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>MCCB 15 A (125 AF) + DOL, NEMA size 0</t>
+          <t>MCCB 100 A (125 AF) + DOL, NEMA size 3</t>
         </is>
       </c>
       <c r="T89" s="4" t="inlineStr"/>
@@ -7067,7 +7067,7 @@
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>CBL-X-102-PA</t>
+          <t>CBL-X-101-PA</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
@@ -7077,12 +7077,12 @@
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>X-102-PA</t>
+          <t>X-101-PA</t>
         </is>
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>Caustic injection package (desalted crude) - metering pump A</t>
+          <t>Demulsifier injection package - metering pump A</t>
         </is>
       </c>
       <c r="F90" s="5" t="n">
@@ -7143,7 +7143,7 @@
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>CBL-X-102-PB</t>
+          <t>CBL-X-101-PB</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
@@ -7153,12 +7153,12 @@
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>X-102-PB</t>
+          <t>X-101-PB</t>
         </is>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>Caustic injection package (desalted crude) - metering pump B</t>
+          <t>Demulsifier injection package - metering pump B</t>
         </is>
       </c>
       <c r="F91" s="5" t="n">
@@ -7219,7 +7219,7 @@
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>CBL-X-103-PA</t>
+          <t>CBL-X-102-PA</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
@@ -7229,12 +7229,12 @@
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>X-103-PA</t>
+          <t>X-102-PA</t>
         </is>
       </c>
       <c r="E92" s="4" t="inlineStr">
         <is>
-          <t>Neutraliser / filming amine package (atm OH) - metering pump A</t>
+          <t>Caustic injection package (desalted crude) - metering pump A</t>
         </is>
       </c>
       <c r="F92" s="5" t="n">
@@ -7243,8 +7243,8 @@
       <c r="G92" s="7" t="n">
         <v>1.5</v>
       </c>
-      <c r="H92" s="6" t="n">
-        <v>160</v>
+      <c r="H92" s="7" t="n">
+        <v>95</v>
       </c>
       <c r="I92" s="4" t="inlineStr">
         <is>
@@ -7266,16 +7266,16 @@
         <v>30.6</v>
       </c>
       <c r="N92" s="5" t="n">
-        <v>0.39</v>
+        <v>0.23</v>
       </c>
       <c r="O92" s="5" t="n">
-        <v>1.19</v>
+        <v>0.71</v>
       </c>
       <c r="P92" s="5" t="n">
         <v>0.02</v>
       </c>
       <c r="Q92" s="5" t="n">
-        <v>1.22</v>
+        <v>0.73</v>
       </c>
       <c r="R92" s="7" t="n">
         <v>1.6</v>
@@ -7295,7 +7295,7 @@
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>CBL-X-103-PB</t>
+          <t>CBL-X-102-PB</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
@@ -7305,12 +7305,12 @@
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>X-103-PB</t>
+          <t>X-102-PB</t>
         </is>
       </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t>Neutraliser / filming amine package (atm OH) - metering pump B</t>
+          <t>Caustic injection package (desalted crude) - metering pump B</t>
         </is>
       </c>
       <c r="F93" s="5" t="n">
@@ -7319,8 +7319,8 @@
       <c r="G93" s="7" t="n">
         <v>1.5</v>
       </c>
-      <c r="H93" s="6" t="n">
-        <v>160</v>
+      <c r="H93" s="7" t="n">
+        <v>95</v>
       </c>
       <c r="I93" s="4" t="inlineStr">
         <is>
@@ -7342,16 +7342,16 @@
         <v>30.6</v>
       </c>
       <c r="N93" s="5" t="n">
-        <v>0.39</v>
+        <v>0.23</v>
       </c>
       <c r="O93" s="5" t="n">
-        <v>1.19</v>
+        <v>0.71</v>
       </c>
       <c r="P93" s="5" t="n">
         <v>0.02</v>
       </c>
       <c r="Q93" s="5" t="n">
-        <v>1.22</v>
+        <v>0.73</v>
       </c>
       <c r="R93" s="7" t="n">
         <v>1.6</v>
@@ -7371,7 +7371,7 @@
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>CBL-X-104-PA</t>
+          <t>CBL-X-103-PA</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
@@ -7381,12 +7381,12 @@
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>X-104-PA</t>
+          <t>X-103-PA</t>
         </is>
       </c>
       <c r="E94" s="4" t="inlineStr">
         <is>
-          <t>Corrosion inhibitor package (VDU OH) - metering pump A</t>
+          <t>Neutraliser / filming amine package (atm OH) - metering pump A</t>
         </is>
       </c>
       <c r="F94" s="5" t="n">
@@ -7396,7 +7396,7 @@
         <v>1.5</v>
       </c>
       <c r="H94" s="6" t="n">
-        <v>295</v>
+        <v>160</v>
       </c>
       <c r="I94" s="4" t="inlineStr">
         <is>
@@ -7418,16 +7418,16 @@
         <v>30.6</v>
       </c>
       <c r="N94" s="5" t="n">
-        <v>0.72</v>
+        <v>0.39</v>
       </c>
       <c r="O94" s="5" t="n">
-        <v>2.2</v>
+        <v>1.19</v>
       </c>
       <c r="P94" s="5" t="n">
         <v>0.02</v>
       </c>
       <c r="Q94" s="5" t="n">
-        <v>2.22</v>
+        <v>1.22</v>
       </c>
       <c r="R94" s="7" t="n">
         <v>1.6</v>
@@ -7447,7 +7447,7 @@
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>CBL-X-104-PB</t>
+          <t>CBL-X-103-PB</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
@@ -7457,12 +7457,12 @@
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>X-104-PB</t>
+          <t>X-103-PB</t>
         </is>
       </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
-          <t>Corrosion inhibitor package (VDU OH) - metering pump B</t>
+          <t>Neutraliser / filming amine package (atm OH) - metering pump B</t>
         </is>
       </c>
       <c r="F95" s="5" t="n">
@@ -7472,7 +7472,7 @@
         <v>1.5</v>
       </c>
       <c r="H95" s="6" t="n">
-        <v>295</v>
+        <v>160</v>
       </c>
       <c r="I95" s="4" t="inlineStr">
         <is>
@@ -7494,16 +7494,16 @@
         <v>30.6</v>
       </c>
       <c r="N95" s="5" t="n">
-        <v>0.72</v>
+        <v>0.39</v>
       </c>
       <c r="O95" s="5" t="n">
-        <v>2.2</v>
+        <v>1.19</v>
       </c>
       <c r="P95" s="5" t="n">
         <v>0.02</v>
       </c>
       <c r="Q95" s="5" t="n">
-        <v>2.22</v>
+        <v>1.22</v>
       </c>
       <c r="R95" s="7" t="n">
         <v>1.6</v>
@@ -7523,7 +7523,7 @@
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>CBL-DT-101A1</t>
+          <t>CBL-X-104-PA</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
@@ -7533,22 +7533,22 @@
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>DT-101A1</t>
+          <t>X-104-PA</t>
         </is>
       </c>
       <c r="E96" s="4" t="inlineStr">
         <is>
-          <t>D-101A 1st stage - HV transformer 1/2 (150 kVA, 480 V / 13-23 kV)</t>
+          <t>Corrosion inhibitor package (VDU OH) - metering pump A</t>
         </is>
       </c>
       <c r="F96" s="5" t="n">
         <v>0.48</v>
       </c>
-      <c r="G96" s="6" t="n">
-        <v>180.4</v>
-      </c>
-      <c r="H96" s="7" t="n">
-        <v>70</v>
+      <c r="G96" s="7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H96" s="6" t="n">
+        <v>295</v>
       </c>
       <c r="I96" s="4" t="inlineStr">
         <is>
@@ -7557,30 +7557,36 @@
       </c>
       <c r="J96" s="4" t="inlineStr">
         <is>
-          <t>3C x 120 + E70 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
+          <t>3C x 4 + E4 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
         </is>
       </c>
       <c r="K96" s="4" t="n">
-        <v>120</v>
+        <v>4</v>
       </c>
       <c r="L96" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M96" s="6" t="n">
-        <v>251.9</v>
+      <c r="M96" s="7" t="n">
+        <v>30.6</v>
       </c>
       <c r="N96" s="5" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="O96" s="4" t="n"/>
-      <c r="P96" s="4" t="n"/>
-      <c r="Q96" s="4" t="n"/>
+        <v>0.72</v>
+      </c>
+      <c r="O96" s="5" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="P96" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="Q96" s="5" t="n">
+        <v>2.22</v>
+      </c>
       <c r="R96" s="7" t="n">
-        <v>8.6</v>
+        <v>1.6</v>
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>MCCB 250 A (250 AF) - desalter transformer feeder</t>
+          <t>MCCB 15 A (125 AF) + DOL, NEMA size 0</t>
         </is>
       </c>
       <c r="T96" s="4" t="inlineStr"/>
@@ -7593,7 +7599,7 @@
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>CBL-DT-101A2</t>
+          <t>CBL-X-104-PB</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
@@ -7603,22 +7609,22 @@
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>DT-101A2</t>
+          <t>X-104-PB</t>
         </is>
       </c>
       <c r="E97" s="4" t="inlineStr">
         <is>
-          <t>D-101A 1st stage - HV transformer 2/2 (150 kVA, 480 V / 13-23 kV)</t>
+          <t>Corrosion inhibitor package (VDU OH) - metering pump B</t>
         </is>
       </c>
       <c r="F97" s="5" t="n">
         <v>0.48</v>
       </c>
-      <c r="G97" s="6" t="n">
-        <v>180.4</v>
-      </c>
-      <c r="H97" s="7" t="n">
-        <v>70</v>
+      <c r="G97" s="7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H97" s="6" t="n">
+        <v>295</v>
       </c>
       <c r="I97" s="4" t="inlineStr">
         <is>
@@ -7627,30 +7633,36 @@
       </c>
       <c r="J97" s="4" t="inlineStr">
         <is>
-          <t>3C x 120 + E70 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
+          <t>3C x 4 + E4 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
         </is>
       </c>
       <c r="K97" s="4" t="n">
-        <v>120</v>
+        <v>4</v>
       </c>
       <c r="L97" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M97" s="6" t="n">
-        <v>251.9</v>
+      <c r="M97" s="7" t="n">
+        <v>30.6</v>
       </c>
       <c r="N97" s="5" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="O97" s="4" t="n"/>
-      <c r="P97" s="4" t="n"/>
-      <c r="Q97" s="4" t="n"/>
+        <v>0.72</v>
+      </c>
+      <c r="O97" s="5" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="P97" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="Q97" s="5" t="n">
+        <v>2.22</v>
+      </c>
       <c r="R97" s="7" t="n">
-        <v>8.6</v>
+        <v>1.6</v>
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>MCCB 250 A (250 AF) - desalter transformer feeder</t>
+          <t>MCCB 15 A (125 AF) + DOL, NEMA size 0</t>
         </is>
       </c>
       <c r="T97" s="4" t="inlineStr"/>
@@ -7663,7 +7675,7 @@
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>CBL-DT-101B1</t>
+          <t>CBL-DT-101A1</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
@@ -7673,12 +7685,12 @@
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>DT-101B1</t>
+          <t>DT-101A1</t>
         </is>
       </c>
       <c r="E98" s="4" t="inlineStr">
         <is>
-          <t>D-101B 2nd stage - HV transformer 1/2 (150 kVA, 480 V / 13-23 kV)</t>
+          <t>D-101A 1st stage - HV transformer 1/2 (150 kVA, 480 V / 13-23 kV)</t>
         </is>
       </c>
       <c r="F98" s="5" t="n">
@@ -7688,7 +7700,7 @@
         <v>180.4</v>
       </c>
       <c r="H98" s="7" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="I98" s="4" t="inlineStr">
         <is>
@@ -7710,7 +7722,7 @@
         <v>251.9</v>
       </c>
       <c r="N98" s="5" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.95</v>
       </c>
       <c r="O98" s="4" t="n"/>
       <c r="P98" s="4" t="n"/>
@@ -7733,7 +7745,7 @@
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>CBL-DT-101B2</t>
+          <t>CBL-DT-101A2</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
@@ -7743,12 +7755,12 @@
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>DT-101B2</t>
+          <t>DT-101A2</t>
         </is>
       </c>
       <c r="E99" s="4" t="inlineStr">
         <is>
-          <t>D-101B 2nd stage - HV transformer 2/2 (150 kVA, 480 V / 13-23 kV)</t>
+          <t>D-101A 1st stage - HV transformer 2/2 (150 kVA, 480 V / 13-23 kV)</t>
         </is>
       </c>
       <c r="F99" s="5" t="n">
@@ -7758,7 +7770,7 @@
         <v>180.4</v>
       </c>
       <c r="H99" s="7" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="I99" s="4" t="inlineStr">
         <is>
@@ -7780,7 +7792,7 @@
         <v>251.9</v>
       </c>
       <c r="N99" s="5" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.95</v>
       </c>
       <c r="O99" s="4" t="n"/>
       <c r="P99" s="4" t="n"/>
@@ -7803,7 +7815,7 @@
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>CBL-MOV-A</t>
+          <t>CBL-DT-101B1</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
@@ -7813,54 +7825,54 @@
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>MOV-A</t>
+          <t>DT-101B1</t>
         </is>
       </c>
       <c r="E100" s="4" t="inlineStr">
         <is>
-          <t>MOV / electric valve actuators - allowance (18 x 1.5 kW), bus A</t>
+          <t>D-101B 2nd stage - HV transformer 1/2 (150 kVA, 480 V / 13-23 kV)</t>
         </is>
       </c>
       <c r="F100" s="5" t="n">
         <v>0.48</v>
       </c>
-      <c r="G100" s="7" t="n">
-        <v>43.3</v>
-      </c>
-      <c r="H100" s="6" t="n">
-        <v>170</v>
+      <c r="G100" s="6" t="n">
+        <v>180.4</v>
+      </c>
+      <c r="H100" s="7" t="n">
+        <v>60</v>
       </c>
       <c r="I100" s="4" t="inlineStr">
         <is>
-          <t>area:PLOT</t>
+          <t>layout</t>
         </is>
       </c>
       <c r="J100" s="4" t="inlineStr">
         <is>
-          <t>3C x 10 + E10 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
+          <t>3C x 120 + E70 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
         </is>
       </c>
       <c r="K100" s="4" t="n">
-        <v>10</v>
+        <v>120</v>
       </c>
       <c r="L100" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M100" s="7" t="n">
-        <v>54.6</v>
+      <c r="M100" s="6" t="n">
+        <v>251.9</v>
       </c>
       <c r="N100" s="5" t="n">
-        <v>4.82</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="O100" s="4" t="n"/>
       <c r="P100" s="4" t="n"/>
       <c r="Q100" s="4" t="n"/>
       <c r="R100" s="7" t="n">
-        <v>2.7</v>
+        <v>8.6</v>
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>MCCB 60 A (125 AF)</t>
+          <t>MCCB 250 A (250 AF) - desalter transformer feeder</t>
         </is>
       </c>
       <c r="T100" s="4" t="inlineStr"/>
@@ -7873,7 +7885,7 @@
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>CBL-MOV-B</t>
+          <t>CBL-DT-101B2</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
@@ -7883,54 +7895,54 @@
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>MOV-B</t>
+          <t>DT-101B2</t>
         </is>
       </c>
       <c r="E101" s="4" t="inlineStr">
         <is>
-          <t>MOV / electric valve actuators - allowance (18 x 1.5 kW), bus B</t>
+          <t>D-101B 2nd stage - HV transformer 2/2 (150 kVA, 480 V / 13-23 kV)</t>
         </is>
       </c>
       <c r="F101" s="5" t="n">
         <v>0.48</v>
       </c>
-      <c r="G101" s="7" t="n">
-        <v>43.3</v>
-      </c>
-      <c r="H101" s="6" t="n">
-        <v>170</v>
+      <c r="G101" s="6" t="n">
+        <v>180.4</v>
+      </c>
+      <c r="H101" s="7" t="n">
+        <v>60</v>
       </c>
       <c r="I101" s="4" t="inlineStr">
         <is>
-          <t>area:PLOT</t>
+          <t>layout</t>
         </is>
       </c>
       <c r="J101" s="4" t="inlineStr">
         <is>
-          <t>3C x 10 + E10 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
+          <t>3C x 120 + E70 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
         </is>
       </c>
       <c r="K101" s="4" t="n">
-        <v>10</v>
+        <v>120</v>
       </c>
       <c r="L101" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M101" s="7" t="n">
-        <v>54.6</v>
+      <c r="M101" s="6" t="n">
+        <v>251.9</v>
       </c>
       <c r="N101" s="5" t="n">
-        <v>4.82</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="O101" s="4" t="n"/>
       <c r="P101" s="4" t="n"/>
       <c r="Q101" s="4" t="n"/>
       <c r="R101" s="7" t="n">
-        <v>2.7</v>
+        <v>8.6</v>
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>MCCB 60 A (125 AF)</t>
+          <t>MCCB 250 A (250 AF) - desalter transformer feeder</t>
         </is>
       </c>
       <c r="T101" s="4" t="inlineStr"/>
@@ -7943,7 +7955,7 @@
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>CBL-HTP-101</t>
+          <t>CBL-MOV-A</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
@@ -7953,44 +7965,44 @@
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>HTP-101</t>
+          <t>MOV-A</t>
         </is>
       </c>
       <c r="E102" s="4" t="inlineStr">
         <is>
-          <t>Electric heat tracing panel - CDU slop &amp; HN lines (allowance)</t>
+          <t>MOV / electric valve actuators - allowance (18 x 1.5 kW), bus A</t>
         </is>
       </c>
       <c r="F102" s="5" t="n">
         <v>0.48</v>
       </c>
       <c r="G102" s="7" t="n">
-        <v>36.1</v>
+        <v>43.3</v>
       </c>
       <c r="H102" s="6" t="n">
         <v>170</v>
       </c>
       <c r="I102" s="4" t="inlineStr">
         <is>
-          <t>area:CDU_P</t>
+          <t>area:PLOT</t>
         </is>
       </c>
       <c r="J102" s="4" t="inlineStr">
         <is>
-          <t>3C x 16 + E16 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
+          <t>3C x 10 + E10 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
         </is>
       </c>
       <c r="K102" s="4" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="L102" s="4" t="n">
         <v>1</v>
       </c>
       <c r="M102" s="7" t="n">
-        <v>72.8</v>
+        <v>54.6</v>
       </c>
       <c r="N102" s="5" t="n">
-        <v>3.26</v>
+        <v>4.82</v>
       </c>
       <c r="O102" s="4" t="n"/>
       <c r="P102" s="4" t="n"/>
@@ -8000,7 +8012,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>MCCB 50 A (125 AF)</t>
+          <t>MCCB 60 A (125 AF)</t>
         </is>
       </c>
       <c r="T102" s="4" t="inlineStr"/>
@@ -8013,7 +8025,7 @@
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>CBL-HTP-102</t>
+          <t>CBL-MOV-B</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
@@ -8023,54 +8035,54 @@
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>HTP-102</t>
+          <t>MOV-B</t>
         </is>
       </c>
       <c r="E103" s="4" t="inlineStr">
         <is>
-          <t>Electric heat tracing panel - VDU slop wax / slop oil lines (allowance)</t>
+          <t>MOV / electric valve actuators - allowance (18 x 1.5 kW), bus B</t>
         </is>
       </c>
       <c r="F103" s="5" t="n">
         <v>0.48</v>
       </c>
       <c r="G103" s="7" t="n">
-        <v>48.1</v>
+        <v>43.3</v>
       </c>
       <c r="H103" s="6" t="n">
-        <v>250</v>
+        <v>170</v>
       </c>
       <c r="I103" s="4" t="inlineStr">
         <is>
-          <t>area:VDU_P</t>
+          <t>area:PLOT</t>
         </is>
       </c>
       <c r="J103" s="4" t="inlineStr">
         <is>
-          <t>3C x 25 + E16 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
+          <t>3C x 10 + E10 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
         </is>
       </c>
       <c r="K103" s="4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="L103" s="4" t="n">
         <v>1</v>
       </c>
       <c r="M103" s="7" t="n">
-        <v>92.5</v>
+        <v>54.6</v>
       </c>
       <c r="N103" s="5" t="n">
-        <v>4.04</v>
+        <v>4.82</v>
       </c>
       <c r="O103" s="4" t="n"/>
       <c r="P103" s="4" t="n"/>
       <c r="Q103" s="4" t="n"/>
       <c r="R103" s="7" t="n">
-        <v>4.9</v>
+        <v>2.7</v>
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>MCCB 70 A (125 AF)</t>
+          <t>MCCB 60 A (125 AF)</t>
         </is>
       </c>
       <c r="T103" s="4" t="inlineStr"/>
@@ -8083,64 +8095,64 @@
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>CBL-AH-101</t>
+          <t>CBL-HTP-101</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>MCC-101B</t>
+          <t>MCC-101A</t>
         </is>
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>AH-101</t>
+          <t>HTP-101</t>
         </is>
       </c>
       <c r="E104" s="4" t="inlineStr">
         <is>
-          <t>Analyser house AH-101 HVAC &amp; utilities (analysers on UPS)</t>
+          <t>Electric heat tracing panel - CDU slop &amp; HN lines (allowance)</t>
         </is>
       </c>
       <c r="F104" s="5" t="n">
         <v>0.48</v>
       </c>
       <c r="G104" s="7" t="n">
-        <v>21.2</v>
+        <v>36.1</v>
       </c>
       <c r="H104" s="6" t="n">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="I104" s="4" t="inlineStr">
         <is>
-          <t>area:CDU</t>
+          <t>area:CDU_P</t>
         </is>
       </c>
       <c r="J104" s="4" t="inlineStr">
         <is>
-          <t>3C x 6 + E6 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
+          <t>3C x 16 + E16 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
         </is>
       </c>
       <c r="K104" s="4" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="L104" s="4" t="n">
         <v>1</v>
       </c>
       <c r="M104" s="7" t="n">
-        <v>39.3</v>
+        <v>72.8</v>
       </c>
       <c r="N104" s="5" t="n">
-        <v>4.94</v>
+        <v>3.26</v>
       </c>
       <c r="O104" s="4" t="n"/>
       <c r="P104" s="4" t="n"/>
       <c r="Q104" s="4" t="n"/>
       <c r="R104" s="7" t="n">
-        <v>1.6</v>
+        <v>2.7</v>
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>MCCB 30 A (125 AF)</t>
+          <t>MCCB 50 A (125 AF)</t>
         </is>
       </c>
       <c r="T104" s="4" t="inlineStr"/>
@@ -8153,64 +8165,64 @@
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>CBL-BEF-101A</t>
+          <t>CBL-HTP-102</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>MCC-101A</t>
+          <t>MCC-101B</t>
         </is>
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>BEF-101A</t>
+          <t>HTP-102</t>
         </is>
       </c>
       <c r="E105" s="4" t="inlineStr">
         <is>
-          <t>SS-100 battery-room exhaust fan A</t>
+          <t>Electric heat tracing panel - VDU slop wax / slop oil lines (allowance)</t>
         </is>
       </c>
       <c r="F105" s="5" t="n">
         <v>0.48</v>
       </c>
       <c r="G105" s="7" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="H105" s="7" t="n">
-        <v>20</v>
+        <v>48.1</v>
+      </c>
+      <c r="H105" s="6" t="n">
+        <v>250</v>
       </c>
       <c r="I105" s="4" t="inlineStr">
         <is>
-          <t>inside SS-100</t>
+          <t>area:VDU_P</t>
         </is>
       </c>
       <c r="J105" s="4" t="inlineStr">
         <is>
-          <t>3C x 4 + E4 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
+          <t>3C x 25 + E16 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
         </is>
       </c>
       <c r="K105" s="4" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="L105" s="4" t="n">
         <v>1</v>
       </c>
       <c r="M105" s="7" t="n">
-        <v>30.6</v>
+        <v>92.5</v>
       </c>
       <c r="N105" s="5" t="n">
-        <v>0.06</v>
+        <v>4.04</v>
       </c>
       <c r="O105" s="4" t="n"/>
       <c r="P105" s="4" t="n"/>
       <c r="Q105" s="4" t="n"/>
       <c r="R105" s="7" t="n">
-        <v>1.6</v>
+        <v>4.9</v>
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>MCCB 15 A (125 AF)</t>
+          <t>MCCB 70 A (125 AF)</t>
         </is>
       </c>
       <c r="T105" s="4" t="inlineStr"/>
@@ -8223,7 +8235,7 @@
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>CBL-BEF-101B</t>
+          <t>CBL-AH-101</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr">
@@ -8233,44 +8245,44 @@
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>BEF-101B</t>
+          <t>AH-101</t>
         </is>
       </c>
       <c r="E106" s="4" t="inlineStr">
         <is>
-          <t>SS-100 battery-room exhaust fan B</t>
+          <t>Analyser house AH-101 HVAC &amp; utilities (analysers on UPS)</t>
         </is>
       </c>
       <c r="F106" s="5" t="n">
         <v>0.48</v>
       </c>
       <c r="G106" s="7" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="H106" s="7" t="n">
-        <v>20</v>
+        <v>21.2</v>
+      </c>
+      <c r="H106" s="6" t="n">
+        <v>190</v>
       </c>
       <c r="I106" s="4" t="inlineStr">
         <is>
-          <t>inside SS-100</t>
+          <t>area:CDU</t>
         </is>
       </c>
       <c r="J106" s="4" t="inlineStr">
         <is>
-          <t>3C x 4 + E4 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
+          <t>3C x 6 + E6 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
         </is>
       </c>
       <c r="K106" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L106" s="4" t="n">
         <v>1</v>
       </c>
       <c r="M106" s="7" t="n">
-        <v>30.6</v>
+        <v>39.3</v>
       </c>
       <c r="N106" s="5" t="n">
-        <v>0.06</v>
+        <v>4.94</v>
       </c>
       <c r="O106" s="4" t="n"/>
       <c r="P106" s="4" t="n"/>
@@ -8280,7 +8292,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>MCCB 15 A (125 AF)</t>
+          <t>MCCB 30 A (125 AF)</t>
         </is>
       </c>
       <c r="T106" s="4" t="inlineStr"/>
@@ -8293,7 +8305,7 @@
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>CBL-HVAC-101A</t>
+          <t>CBL-BEF-101A</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
@@ -8303,19 +8315,19 @@
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>HVAC-101A</t>
+          <t>BEF-101A</t>
         </is>
       </c>
       <c r="E107" s="4" t="inlineStr">
         <is>
-          <t>SS-100 HVAC package A (2 x 100 %)</t>
+          <t>SS-100 battery-room exhaust fan A</t>
         </is>
       </c>
       <c r="F107" s="5" t="n">
         <v>0.48</v>
       </c>
       <c r="G107" s="7" t="n">
-        <v>84.90000000000001</v>
+        <v>1.7</v>
       </c>
       <c r="H107" s="7" t="n">
         <v>20</v>
@@ -8327,30 +8339,30 @@
       </c>
       <c r="J107" s="4" t="inlineStr">
         <is>
-          <t>3C x 35 + E16 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
+          <t>3C x 4 + E4 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
         </is>
       </c>
       <c r="K107" s="4" t="n">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="L107" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M107" s="6" t="n">
-        <v>115</v>
+      <c r="M107" s="7" t="n">
+        <v>30.6</v>
       </c>
       <c r="N107" s="5" t="n">
-        <v>0.38</v>
+        <v>0.06</v>
       </c>
       <c r="O107" s="4" t="n"/>
       <c r="P107" s="4" t="n"/>
       <c r="Q107" s="4" t="n"/>
       <c r="R107" s="7" t="n">
-        <v>4.9</v>
+        <v>1.6</v>
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>MCCB 110 A (125 AF)</t>
+          <t>MCCB 15 A (125 AF)</t>
         </is>
       </c>
       <c r="T107" s="4" t="inlineStr"/>
@@ -8363,7 +8375,7 @@
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>CBL-HVAC-101B</t>
+          <t>CBL-BEF-101B</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr">
@@ -8373,19 +8385,19 @@
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>HVAC-101B</t>
+          <t>BEF-101B</t>
         </is>
       </c>
       <c r="E108" s="4" t="inlineStr">
         <is>
-          <t>SS-100 HVAC package B (2 x 100 %)</t>
+          <t>SS-100 battery-room exhaust fan B</t>
         </is>
       </c>
       <c r="F108" s="5" t="n">
         <v>0.48</v>
       </c>
       <c r="G108" s="7" t="n">
-        <v>84.90000000000001</v>
+        <v>1.7</v>
       </c>
       <c r="H108" s="7" t="n">
         <v>20</v>
@@ -8397,30 +8409,30 @@
       </c>
       <c r="J108" s="4" t="inlineStr">
         <is>
-          <t>3C x 35 + E16 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
+          <t>3C x 4 + E4 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
         </is>
       </c>
       <c r="K108" s="4" t="n">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="L108" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M108" s="6" t="n">
-        <v>115</v>
+      <c r="M108" s="7" t="n">
+        <v>30.6</v>
       </c>
       <c r="N108" s="5" t="n">
-        <v>0.38</v>
+        <v>0.06</v>
       </c>
       <c r="O108" s="4" t="n"/>
       <c r="P108" s="4" t="n"/>
       <c r="Q108" s="4" t="n"/>
       <c r="R108" s="7" t="n">
-        <v>4.9</v>
+        <v>1.6</v>
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>MCCB 110 A (125 AF)</t>
+          <t>MCCB 15 A (125 AF)</t>
         </is>
       </c>
       <c r="T108" s="4" t="inlineStr"/>
@@ -8433,7 +8445,7 @@
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>CBL-HVAC-102A</t>
+          <t>CBL-HVAC-101A</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
@@ -8443,54 +8455,54 @@
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>HVAC-102A</t>
+          <t>HVAC-101A</t>
         </is>
       </c>
       <c r="E109" s="4" t="inlineStr">
         <is>
-          <t>FAR-100 HVAC package A (2 x 100 %)</t>
+          <t>SS-100 HVAC package A (2 x 100 %)</t>
         </is>
       </c>
       <c r="F109" s="5" t="n">
         <v>0.48</v>
       </c>
       <c r="G109" s="7" t="n">
-        <v>35.4</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="H109" s="7" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="I109" s="4" t="inlineStr">
         <is>
-          <t>FAR-100</t>
+          <t>inside SS-100</t>
         </is>
       </c>
       <c r="J109" s="4" t="inlineStr">
         <is>
-          <t>3C x 10 + E10 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
+          <t>3C x 35 + E16 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
         </is>
       </c>
       <c r="K109" s="4" t="n">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="L109" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M109" s="7" t="n">
-        <v>54.6</v>
+      <c r="M109" s="6" t="n">
+        <v>115</v>
       </c>
       <c r="N109" s="5" t="n">
-        <v>1.3</v>
+        <v>0.38</v>
       </c>
       <c r="O109" s="4" t="n"/>
       <c r="P109" s="4" t="n"/>
       <c r="Q109" s="4" t="n"/>
       <c r="R109" s="7" t="n">
-        <v>2.7</v>
+        <v>4.9</v>
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>MCCB 45 A (125 AF)</t>
+          <t>MCCB 110 A (125 AF)</t>
         </is>
       </c>
       <c r="T109" s="4" t="inlineStr"/>
@@ -8503,7 +8515,7 @@
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>CBL-HVAC-102B</t>
+          <t>CBL-HVAC-101B</t>
         </is>
       </c>
       <c r="C110" s="4" t="inlineStr">
@@ -8513,54 +8525,54 @@
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>HVAC-102B</t>
+          <t>HVAC-101B</t>
         </is>
       </c>
       <c r="E110" s="4" t="inlineStr">
         <is>
-          <t>FAR-100 HVAC package B (2 x 100 %)</t>
+          <t>SS-100 HVAC package B (2 x 100 %)</t>
         </is>
       </c>
       <c r="F110" s="5" t="n">
         <v>0.48</v>
       </c>
       <c r="G110" s="7" t="n">
-        <v>35.4</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="H110" s="7" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="I110" s="4" t="inlineStr">
         <is>
-          <t>FAR-100</t>
+          <t>inside SS-100</t>
         </is>
       </c>
       <c r="J110" s="4" t="inlineStr">
         <is>
-          <t>3C x 10 + E10 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
+          <t>3C x 35 + E16 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
         </is>
       </c>
       <c r="K110" s="4" t="n">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="L110" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M110" s="7" t="n">
-        <v>54.6</v>
+      <c r="M110" s="6" t="n">
+        <v>115</v>
       </c>
       <c r="N110" s="5" t="n">
-        <v>1.3</v>
+        <v>0.38</v>
       </c>
       <c r="O110" s="4" t="n"/>
       <c r="P110" s="4" t="n"/>
       <c r="Q110" s="4" t="n"/>
       <c r="R110" s="7" t="n">
-        <v>2.7</v>
+        <v>4.9</v>
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>MCCB 45 A (125 AF)</t>
+          <t>MCCB 110 A (125 AF)</t>
         </is>
       </c>
       <c r="T110" s="4" t="inlineStr"/>
@@ -8573,7 +8585,7 @@
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>CBL-WR-A</t>
+          <t>CBL-HVAC-102A</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
@@ -8583,54 +8595,54 @@
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>WR-A</t>
+          <t>HVAC-102A</t>
         </is>
       </c>
       <c r="E111" s="4" t="inlineStr">
         <is>
-          <t>Welding receptacles 3 x 63 A, 480 V, bus A</t>
+          <t>FAR-100 HVAC package A (2 x 100 %)</t>
         </is>
       </c>
       <c r="F111" s="5" t="n">
         <v>0.48</v>
       </c>
-      <c r="G111" s="6" t="n">
-        <v>128.9</v>
-      </c>
-      <c r="H111" s="6" t="n">
-        <v>170</v>
+      <c r="G111" s="7" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="H111" s="7" t="n">
+        <v>50</v>
       </c>
       <c r="I111" s="4" t="inlineStr">
         <is>
-          <t>area:PLOT</t>
+          <t>FAR-100</t>
         </is>
       </c>
       <c r="J111" s="4" t="inlineStr">
         <is>
-          <t>3C x 70 + E35 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
+          <t>3C x 10 + E10 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
         </is>
       </c>
       <c r="K111" s="4" t="n">
-        <v>70</v>
+        <v>10</v>
       </c>
       <c r="L111" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M111" s="6" t="n">
-        <v>179.1</v>
+      <c r="M111" s="7" t="n">
+        <v>54.6</v>
       </c>
       <c r="N111" s="5" t="n">
-        <v>2.34</v>
+        <v>1.3</v>
       </c>
       <c r="O111" s="4" t="n"/>
       <c r="P111" s="4" t="n"/>
       <c r="Q111" s="4" t="n"/>
       <c r="R111" s="7" t="n">
-        <v>8.6</v>
+        <v>2.7</v>
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>MCCB 175 A (250 AF)</t>
+          <t>MCCB 45 A (125 AF)</t>
         </is>
       </c>
       <c r="T111" s="4" t="inlineStr"/>
@@ -8643,7 +8655,7 @@
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>CBL-WR-B</t>
+          <t>CBL-HVAC-102B</t>
         </is>
       </c>
       <c r="C112" s="4" t="inlineStr">
@@ -8653,54 +8665,54 @@
       </c>
       <c r="D112" s="4" t="inlineStr">
         <is>
-          <t>WR-B</t>
+          <t>HVAC-102B</t>
         </is>
       </c>
       <c r="E112" s="4" t="inlineStr">
         <is>
-          <t>Welding receptacles 3 x 63 A, 480 V, bus B</t>
+          <t>FAR-100 HVAC package B (2 x 100 %)</t>
         </is>
       </c>
       <c r="F112" s="5" t="n">
         <v>0.48</v>
       </c>
-      <c r="G112" s="6" t="n">
-        <v>128.9</v>
-      </c>
-      <c r="H112" s="6" t="n">
-        <v>170</v>
+      <c r="G112" s="7" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="H112" s="7" t="n">
+        <v>50</v>
       </c>
       <c r="I112" s="4" t="inlineStr">
         <is>
-          <t>area:PLOT</t>
+          <t>FAR-100</t>
         </is>
       </c>
       <c r="J112" s="4" t="inlineStr">
         <is>
-          <t>3C x 70 + E35 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
+          <t>3C x 10 + E10 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
         </is>
       </c>
       <c r="K112" s="4" t="n">
-        <v>70</v>
+        <v>10</v>
       </c>
       <c r="L112" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M112" s="6" t="n">
-        <v>179.1</v>
+      <c r="M112" s="7" t="n">
+        <v>54.6</v>
       </c>
       <c r="N112" s="5" t="n">
-        <v>2.34</v>
+        <v>1.3</v>
       </c>
       <c r="O112" s="4" t="n"/>
       <c r="P112" s="4" t="n"/>
       <c r="Q112" s="4" t="n"/>
       <c r="R112" s="7" t="n">
-        <v>8.6</v>
+        <v>2.7</v>
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>MCCB 175 A (250 AF)</t>
+          <t>MCCB 45 A (125 AF)</t>
         </is>
       </c>
       <c r="T112" s="4" t="inlineStr"/>
@@ -8713,7 +8725,7 @@
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>CBL-CP-101</t>
+          <t>CBL-WR-A</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr">
@@ -8723,54 +8735,54 @@
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>CP-101</t>
+          <t>WR-A</t>
         </is>
       </c>
       <c r="E113" s="4" t="inlineStr">
         <is>
-          <t>Cathodic protection transformer-rectifier (buried piping / tank bottoms in plot)</t>
+          <t>Welding receptacles 3 x 63 A, 480 V, bus A</t>
         </is>
       </c>
       <c r="F113" s="5" t="n">
         <v>0.48</v>
       </c>
-      <c r="G113" s="7" t="n">
-        <v>12</v>
-      </c>
-      <c r="H113" s="7" t="n">
-        <v>60</v>
+      <c r="G113" s="6" t="n">
+        <v>128.9</v>
+      </c>
+      <c r="H113" s="6" t="n">
+        <v>170</v>
       </c>
       <c r="I113" s="4" t="inlineStr">
         <is>
-          <t>area:DESALT</t>
+          <t>area:PLOT</t>
         </is>
       </c>
       <c r="J113" s="4" t="inlineStr">
         <is>
-          <t>3C x 4 + E4 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
+          <t>3C x 70 + E35 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
         </is>
       </c>
       <c r="K113" s="4" t="n">
-        <v>4</v>
+        <v>70</v>
       </c>
       <c r="L113" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M113" s="7" t="n">
-        <v>30.6</v>
+      <c r="M113" s="6" t="n">
+        <v>179.1</v>
       </c>
       <c r="N113" s="5" t="n">
-        <v>1.24</v>
+        <v>2.34</v>
       </c>
       <c r="O113" s="4" t="n"/>
       <c r="P113" s="4" t="n"/>
       <c r="Q113" s="4" t="n"/>
       <c r="R113" s="7" t="n">
-        <v>1.6</v>
+        <v>8.6</v>
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>MCCB 20 A (125 AF)</t>
+          <t>MCCB 175 A (250 AF)</t>
         </is>
       </c>
       <c r="T113" s="4" t="inlineStr"/>
@@ -8783,64 +8795,64 @@
       </c>
       <c r="B114" s="4" t="inlineStr">
         <is>
-          <t>CBL-BC-101A</t>
+          <t>CBL-WR-B</t>
         </is>
       </c>
       <c r="C114" s="4" t="inlineStr">
         <is>
-          <t>MCC-101A</t>
+          <t>MCC-101B</t>
         </is>
       </c>
       <c r="D114" s="4" t="inlineStr">
         <is>
-          <t>BC-101A</t>
+          <t>WR-B</t>
         </is>
       </c>
       <c r="E114" s="4" t="inlineStr">
         <is>
-          <t>125 V DC battery charger A (switchgear control), 2 x 100 %</t>
+          <t>Welding receptacles 3 x 63 A, 480 V, bus B</t>
         </is>
       </c>
       <c r="F114" s="5" t="n">
         <v>0.48</v>
       </c>
-      <c r="G114" s="7" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="H114" s="7" t="n">
-        <v>20</v>
+      <c r="G114" s="6" t="n">
+        <v>128.9</v>
+      </c>
+      <c r="H114" s="6" t="n">
+        <v>170</v>
       </c>
       <c r="I114" s="4" t="inlineStr">
         <is>
-          <t>inside SS-100</t>
+          <t>area:PLOT</t>
         </is>
       </c>
       <c r="J114" s="4" t="inlineStr">
         <is>
-          <t>3C x 4 + E4 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
+          <t>3C x 70 + E35 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
         </is>
       </c>
       <c r="K114" s="4" t="n">
-        <v>4</v>
+        <v>70</v>
       </c>
       <c r="L114" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M114" s="7" t="n">
-        <v>30.6</v>
+      <c r="M114" s="6" t="n">
+        <v>179.1</v>
       </c>
       <c r="N114" s="5" t="n">
-        <v>0.34</v>
+        <v>2.34</v>
       </c>
       <c r="O114" s="4" t="n"/>
       <c r="P114" s="4" t="n"/>
       <c r="Q114" s="4" t="n"/>
       <c r="R114" s="7" t="n">
-        <v>1.6</v>
+        <v>8.6</v>
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>MCCB 15 A (125 AF)</t>
+          <t>MCCB 175 A (250 AF)</t>
         </is>
       </c>
       <c r="T114" s="4" t="inlineStr"/>
@@ -8853,36 +8865,36 @@
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>CBL-BC-101B</t>
+          <t>CBL-CP-101</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>MCC-101B</t>
+          <t>MCC-101A</t>
         </is>
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>BC-101B</t>
+          <t>CP-101</t>
         </is>
       </c>
       <c r="E115" s="4" t="inlineStr">
         <is>
-          <t>125 V DC battery charger B (switchgear control), 2 x 100 %</t>
+          <t>Cathodic protection transformer-rectifier (buried piping / tank bottoms in plot)</t>
         </is>
       </c>
       <c r="F115" s="5" t="n">
         <v>0.48</v>
       </c>
       <c r="G115" s="7" t="n">
-        <v>9.4</v>
+        <v>12</v>
       </c>
       <c r="H115" s="7" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="I115" s="4" t="inlineStr">
         <is>
-          <t>inside SS-100</t>
+          <t>area:DESALT</t>
         </is>
       </c>
       <c r="J115" s="4" t="inlineStr">
@@ -8900,7 +8912,7 @@
         <v>30.6</v>
       </c>
       <c r="N115" s="5" t="n">
-        <v>0.34</v>
+        <v>1.24</v>
       </c>
       <c r="O115" s="4" t="n"/>
       <c r="P115" s="4" t="n"/>
@@ -8910,7 +8922,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>MCCB 15 A (125 AF)</t>
+          <t>MCCB 20 A (125 AF)</t>
         </is>
       </c>
       <c r="T115" s="4" t="inlineStr"/>
@@ -8923,7 +8935,7 @@
       </c>
       <c r="B116" s="4" t="inlineStr">
         <is>
-          <t>CBL-UPS-101A</t>
+          <t>CBL-BC-101A</t>
         </is>
       </c>
       <c r="C116" s="4" t="inlineStr">
@@ -8933,19 +8945,19 @@
       </c>
       <c r="D116" s="4" t="inlineStr">
         <is>
-          <t>UPS-101A</t>
+          <t>BC-101A</t>
         </is>
       </c>
       <c r="E116" s="4" t="inlineStr">
         <is>
-          <t>UPS-101A rectifier input (2 x 100 % 100 kVA, 50 % share + battery recharge)</t>
+          <t>125 V DC battery charger A (switchgear control), 2 x 100 %</t>
         </is>
       </c>
       <c r="F116" s="5" t="n">
         <v>0.48</v>
       </c>
       <c r="G116" s="7" t="n">
-        <v>43.1</v>
+        <v>9.4</v>
       </c>
       <c r="H116" s="7" t="n">
         <v>20</v>
@@ -8957,30 +8969,30 @@
       </c>
       <c r="J116" s="4" t="inlineStr">
         <is>
-          <t>3C x 10 + E10 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
+          <t>3C x 4 + E4 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
         </is>
       </c>
       <c r="K116" s="4" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="L116" s="4" t="n">
         <v>1</v>
       </c>
       <c r="M116" s="7" t="n">
-        <v>54.6</v>
+        <v>30.6</v>
       </c>
       <c r="N116" s="5" t="n">
-        <v>0.7</v>
+        <v>0.34</v>
       </c>
       <c r="O116" s="4" t="n"/>
       <c r="P116" s="4" t="n"/>
       <c r="Q116" s="4" t="n"/>
       <c r="R116" s="7" t="n">
-        <v>2.7</v>
+        <v>1.6</v>
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>MCCB 60 A (125 AF)</t>
+          <t>MCCB 15 A (125 AF)</t>
         </is>
       </c>
       <c r="T116" s="4" t="inlineStr"/>
@@ -8993,7 +9005,7 @@
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>CBL-UPS-101B</t>
+          <t>CBL-BC-101B</t>
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr">
@@ -9003,19 +9015,19 @@
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>UPS-101B</t>
+          <t>BC-101B</t>
         </is>
       </c>
       <c r="E117" s="4" t="inlineStr">
         <is>
-          <t>UPS-101B rectifier input (2 x 100 % 100 kVA, 50 % share + battery recharge)</t>
+          <t>125 V DC battery charger B (switchgear control), 2 x 100 %</t>
         </is>
       </c>
       <c r="F117" s="5" t="n">
         <v>0.48</v>
       </c>
       <c r="G117" s="7" t="n">
-        <v>43.1</v>
+        <v>9.4</v>
       </c>
       <c r="H117" s="7" t="n">
         <v>20</v>
@@ -9027,30 +9039,30 @@
       </c>
       <c r="J117" s="4" t="inlineStr">
         <is>
-          <t>3C x 10 + E10 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
+          <t>3C x 4 + E4 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
         </is>
       </c>
       <c r="K117" s="4" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="L117" s="4" t="n">
         <v>1</v>
       </c>
       <c r="M117" s="7" t="n">
-        <v>54.6</v>
+        <v>30.6</v>
       </c>
       <c r="N117" s="5" t="n">
-        <v>0.7</v>
+        <v>0.34</v>
       </c>
       <c r="O117" s="4" t="n"/>
       <c r="P117" s="4" t="n"/>
       <c r="Q117" s="4" t="n"/>
       <c r="R117" s="7" t="n">
-        <v>2.7</v>
+        <v>1.6</v>
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>MCCB 60 A (125 AF)</t>
+          <t>MCCB 15 A (125 AF)</t>
         </is>
       </c>
       <c r="T117" s="4" t="inlineStr"/>
@@ -9063,7 +9075,7 @@
       </c>
       <c r="B118" s="4" t="inlineStr">
         <is>
-          <t>CBL-HST-101</t>
+          <t>CBL-UPS-101A</t>
         </is>
       </c>
       <c r="C118" s="4" t="inlineStr">
@@ -9073,54 +9085,54 @@
       </c>
       <c r="D118" s="4" t="inlineStr">
         <is>
-          <t>HST-101</t>
+          <t>UPS-101A</t>
         </is>
       </c>
       <c r="E118" s="4" t="inlineStr">
         <is>
-          <t>Monorail hoists P-101/P-102 maintenance (2 x 7.5 kW)</t>
+          <t>UPS-101A rectifier input (2 x 100 % 100 kVA, 50 % share + battery recharge)</t>
         </is>
       </c>
       <c r="F118" s="5" t="n">
         <v>0.48</v>
       </c>
       <c r="G118" s="7" t="n">
-        <v>22.6</v>
+        <v>43.1</v>
       </c>
       <c r="H118" s="7" t="n">
-        <v>85</v>
+        <v>20</v>
       </c>
       <c r="I118" s="4" t="inlineStr">
         <is>
-          <t>area:DESALT_P</t>
+          <t>inside SS-100</t>
         </is>
       </c>
       <c r="J118" s="4" t="inlineStr">
         <is>
-          <t>3C x 4 + E4 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
+          <t>3C x 10 + E10 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
         </is>
       </c>
       <c r="K118" s="4" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="L118" s="4" t="n">
         <v>1</v>
       </c>
       <c r="M118" s="7" t="n">
-        <v>30.6</v>
+        <v>54.6</v>
       </c>
       <c r="N118" s="5" t="n">
-        <v>3.3</v>
+        <v>0.7</v>
       </c>
       <c r="O118" s="4" t="n"/>
       <c r="P118" s="4" t="n"/>
       <c r="Q118" s="4" t="n"/>
       <c r="R118" s="7" t="n">
-        <v>1.6</v>
+        <v>2.7</v>
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>MCCB 30 A (125 AF)</t>
+          <t>MCCB 60 A (125 AF)</t>
         </is>
       </c>
       <c r="T118" s="4" t="inlineStr"/>
@@ -9133,7 +9145,7 @@
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>CBL-SB-101</t>
+          <t>CBL-UPS-101B</t>
         </is>
       </c>
       <c r="C119" s="4" t="inlineStr">
@@ -9143,54 +9155,54 @@
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>SB-101</t>
+          <t>UPS-101B</t>
         </is>
       </c>
       <c r="E119" s="4" t="inlineStr">
         <is>
-          <t>H-101 convection sootblowers (8 x 0.75 kW, electric retract)</t>
+          <t>UPS-101B rectifier input (2 x 100 % 100 kVA, 50 % share + battery recharge)</t>
         </is>
       </c>
       <c r="F119" s="5" t="n">
         <v>0.48</v>
       </c>
       <c r="G119" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="H119" s="6" t="n">
-        <v>120</v>
+        <v>43.1</v>
+      </c>
+      <c r="H119" s="7" t="n">
+        <v>20</v>
       </c>
       <c r="I119" s="4" t="inlineStr">
         <is>
-          <t>area:H101</t>
+          <t>inside SS-100</t>
         </is>
       </c>
       <c r="J119" s="4" t="inlineStr">
         <is>
-          <t>3C x 4 + E4 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
+          <t>3C x 10 + E10 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
         </is>
       </c>
       <c r="K119" s="4" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="L119" s="4" t="n">
         <v>1</v>
       </c>
       <c r="M119" s="7" t="n">
-        <v>30.6</v>
+        <v>54.6</v>
       </c>
       <c r="N119" s="5" t="n">
-        <v>1.86</v>
+        <v>0.7</v>
       </c>
       <c r="O119" s="4" t="n"/>
       <c r="P119" s="4" t="n"/>
       <c r="Q119" s="4" t="n"/>
       <c r="R119" s="7" t="n">
-        <v>1.6</v>
+        <v>2.7</v>
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>MCCB 15 A (125 AF)</t>
+          <t>MCCB 60 A (125 AF)</t>
         </is>
       </c>
       <c r="T119" s="4" t="inlineStr"/>
@@ -9203,7 +9215,7 @@
       </c>
       <c r="B120" s="4" t="inlineStr">
         <is>
-          <t>CBL-LTR-101A</t>
+          <t>CBL-HST-101</t>
         </is>
       </c>
       <c r="C120" s="4" t="inlineStr">
@@ -9213,54 +9225,54 @@
       </c>
       <c r="D120" s="4" t="inlineStr">
         <is>
-          <t>LTR-101A (75 kVA 480-208Y/120 V)</t>
+          <t>HST-101</t>
         </is>
       </c>
       <c r="E120" s="4" t="inlineStr">
         <is>
-          <t>Lighting &amp; small-power transformer -&gt; LDB-101A</t>
+          <t>Monorail hoists P-101/P-102 maintenance (2 x 7.5 kW)</t>
         </is>
       </c>
       <c r="F120" s="5" t="n">
         <v>0.48</v>
       </c>
       <c r="G120" s="7" t="n">
-        <v>90.2</v>
+        <v>22.6</v>
       </c>
       <c r="H120" s="7" t="n">
-        <v>20</v>
+        <v>85</v>
       </c>
       <c r="I120" s="4" t="inlineStr">
         <is>
-          <t>inside SS-100</t>
+          <t>area:DESALT_P</t>
         </is>
       </c>
       <c r="J120" s="4" t="inlineStr">
         <is>
-          <t>3C x 35 + E16 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
+          <t>3C x 4 + E4 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
         </is>
       </c>
       <c r="K120" s="4" t="n">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="L120" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M120" s="6" t="n">
-        <v>115</v>
+      <c r="M120" s="7" t="n">
+        <v>30.6</v>
       </c>
       <c r="N120" s="5" t="n">
-        <v>0.43</v>
+        <v>3.3</v>
       </c>
       <c r="O120" s="4" t="n"/>
       <c r="P120" s="4" t="n"/>
       <c r="Q120" s="4" t="n"/>
       <c r="R120" s="7" t="n">
-        <v>4.9</v>
+        <v>1.6</v>
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>MCCB 125 A (125 AF)</t>
+          <t>MCCB 30 A (125 AF)</t>
         </is>
       </c>
       <c r="T120" s="4" t="inlineStr"/>
@@ -9273,7 +9285,7 @@
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>CBL-LTR-101B</t>
+          <t>CBL-SB-101</t>
         </is>
       </c>
       <c r="C121" s="4" t="inlineStr">
@@ -9283,68 +9295,208 @@
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>LTR-101B (75 kVA 480-208Y/120 V)</t>
+          <t>SB-101</t>
         </is>
       </c>
       <c r="E121" s="4" t="inlineStr">
         <is>
-          <t>Lighting &amp; small-power transformer -&gt; LDB-101B</t>
+          <t>H-101 convection sootblowers (8 x 0.75 kW, electric retract)</t>
         </is>
       </c>
       <c r="F121" s="5" t="n">
         <v>0.48</v>
       </c>
       <c r="G121" s="7" t="n">
-        <v>90.2</v>
-      </c>
-      <c r="H121" s="7" t="n">
-        <v>20</v>
+        <v>9</v>
+      </c>
+      <c r="H121" s="6" t="n">
+        <v>120</v>
       </c>
       <c r="I121" s="4" t="inlineStr">
         <is>
-          <t>inside SS-100</t>
+          <t>area:H101</t>
         </is>
       </c>
       <c r="J121" s="4" t="inlineStr">
         <is>
-          <t>3C x 35 + E16 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
+          <t>3C x 4 + E4 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
         </is>
       </c>
       <c r="K121" s="4" t="n">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="L121" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M121" s="6" t="n">
-        <v>115</v>
+      <c r="M121" s="7" t="n">
+        <v>30.6</v>
       </c>
       <c r="N121" s="5" t="n">
-        <v>0.43</v>
+        <v>1.86</v>
       </c>
       <c r="O121" s="4" t="n"/>
       <c r="P121" s="4" t="n"/>
       <c r="Q121" s="4" t="n"/>
       <c r="R121" s="7" t="n">
-        <v>4.9</v>
+        <v>1.6</v>
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>MCCB 125 A (125 AF)</t>
+          <t>MCCB 15 A (125 AF)</t>
         </is>
       </c>
       <c r="T121" s="4" t="inlineStr"/>
       <c r="U121" s="4" t="inlineStr"/>
       <c r="V121" s="4" t="inlineStr"/>
     </row>
+    <row r="122">
+      <c r="A122" s="4" t="n">
+        <v>118</v>
+      </c>
+      <c r="B122" s="4" t="inlineStr">
+        <is>
+          <t>CBL-LTR-101A</t>
+        </is>
+      </c>
+      <c r="C122" s="4" t="inlineStr">
+        <is>
+          <t>MCC-101A</t>
+        </is>
+      </c>
+      <c r="D122" s="4" t="inlineStr">
+        <is>
+          <t>LTR-101A (75 kVA 480-208Y/120 V)</t>
+        </is>
+      </c>
+      <c r="E122" s="4" t="inlineStr">
+        <is>
+          <t>Lighting &amp; small-power transformer -&gt; LDB-101A</t>
+        </is>
+      </c>
+      <c r="F122" s="5" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="G122" s="7" t="n">
+        <v>90.2</v>
+      </c>
+      <c r="H122" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="I122" s="4" t="inlineStr">
+        <is>
+          <t>inside SS-100</t>
+        </is>
+      </c>
+      <c r="J122" s="4" t="inlineStr">
+        <is>
+          <t>3C x 35 + E16 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
+        </is>
+      </c>
+      <c r="K122" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="L122" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M122" s="6" t="n">
+        <v>115</v>
+      </c>
+      <c r="N122" s="5" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="O122" s="4" t="n"/>
+      <c r="P122" s="4" t="n"/>
+      <c r="Q122" s="4" t="n"/>
+      <c r="R122" s="7" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="S122" s="4" t="inlineStr">
+        <is>
+          <t>MCCB 125 A (125 AF)</t>
+        </is>
+      </c>
+      <c r="T122" s="4" t="inlineStr"/>
+      <c r="U122" s="4" t="inlineStr"/>
+      <c r="V122" s="4" t="inlineStr"/>
+    </row>
     <row r="123">
-      <c r="B123" s="8" t="inlineStr">
+      <c r="A123" s="4" t="n">
+        <v>119</v>
+      </c>
+      <c r="B123" s="4" t="inlineStr">
+        <is>
+          <t>CBL-LTR-101B</t>
+        </is>
+      </c>
+      <c r="C123" s="4" t="inlineStr">
+        <is>
+          <t>MCC-101B</t>
+        </is>
+      </c>
+      <c r="D123" s="4" t="inlineStr">
+        <is>
+          <t>LTR-101B (75 kVA 480-208Y/120 V)</t>
+        </is>
+      </c>
+      <c r="E123" s="4" t="inlineStr">
+        <is>
+          <t>Lighting &amp; small-power transformer -&gt; LDB-101B</t>
+        </is>
+      </c>
+      <c r="F123" s="5" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="G123" s="7" t="n">
+        <v>90.2</v>
+      </c>
+      <c r="H123" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="I123" s="4" t="inlineStr">
+        <is>
+          <t>inside SS-100</t>
+        </is>
+      </c>
+      <c r="J123" s="4" t="inlineStr">
+        <is>
+          <t>3C x 35 + E16 mm2 Cu/XLPE/SWA/PVC 0.6/1 kV</t>
+        </is>
+      </c>
+      <c r="K123" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="L123" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M123" s="6" t="n">
+        <v>115</v>
+      </c>
+      <c r="N123" s="5" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="O123" s="4" t="n"/>
+      <c r="P123" s="4" t="n"/>
+      <c r="Q123" s="4" t="n"/>
+      <c r="R123" s="7" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="S123" s="4" t="inlineStr">
+        <is>
+          <t>MCCB 125 A (125 AF)</t>
+        </is>
+      </c>
+      <c r="T123" s="4" t="inlineStr"/>
+      <c r="U123" s="4" t="inlineStr"/>
+      <c r="V123" s="4" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="B125" s="8" t="inlineStr">
         <is>
           <t>TOTAL LENGTH (m)</t>
         </is>
       </c>
-      <c r="H123" s="8">
-        <f>SUM(H5:H121)</f>
+      <c r="H125" s="8">
+        <f>SUM(H5:H123)</f>
         <v/>
       </c>
     </row>
@@ -9483,10 +9635,10 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>1280</v>
+        <v>1405</v>
       </c>
       <c r="C11" s="6" t="n">
-        <v>1408</v>
+        <v>1545.5</v>
       </c>
     </row>
     <row r="12">
@@ -9574,10 +9726,10 @@
         </is>
       </c>
       <c r="B18" s="6" t="n">
-        <v>940</v>
+        <v>1265</v>
       </c>
       <c r="C18" s="6" t="n">
-        <v>1034</v>
+        <v>1391.5</v>
       </c>
     </row>
     <row r="19">
@@ -9701,7 +9853,7 @@
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t>6. Route length = Manhattan distance from SS-100 reference point (25, 12.5) m to the consumer + 15 m riser/termination allowance (+10 m for air-cooler fan motors on top of the pipe rack), rounded up to 5 m. Coordinates source: data/layout.json (139 tagged items).</t>
+          <t>6. Route length = Manhattan distance from SS-100 reference point (25, 12.5) m to the consumer + 15 m riser/termination allowance (+10 m for air-cooler fan motors on top of the pipe rack), rounded up to 5 m. Coordinates source: data/layout.json (141 tagged items).</t>
         </is>
       </c>
     </row>
